--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289A99C0-A535-BE4A-AC87-C4D59713C04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C361A8E-9DDE-5B49-8EBE-92F9352F01F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5540" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3870,6 +3870,9 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3905,9 +3908,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4216,7 +4216,7 @@
       <c r="C1" s="44">
         <v>45794</v>
       </c>
-      <c r="D1" s="358" t="s">
+      <c r="D1" s="346" t="s">
         <v>459</v>
       </c>
       <c r="E1" s="320" t="s">
@@ -4369,13 +4369,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>8.6508809985438244</v>
+        <v>10.626225516615497</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4502,7 +4502,7 @@
         <v>428</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.15">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>12.692318663238471</v>
+        <v>14.36771747016822</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4521,7 +4521,7 @@
         <v>441</v>
       </c>
       <c r="F30" s="342">
-        <v>0.22</v>
+        <v>0.16739999999999999</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.15">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>16.152629501301309</v>
+        <v>16.259250205162648</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4559,7 +4559,7 @@
         <v>442</v>
       </c>
       <c r="F32" s="342">
-        <v>0.12</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.15">
@@ -4577,22 +4577,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="349" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="232" t="s">
@@ -4604,13 +4604,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
@@ -4630,13 +4630,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
@@ -4665,13 +4665,13 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
@@ -4687,13 +4687,13 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
@@ -4757,13 +4757,13 @@
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
@@ -4779,13 +4779,13 @@
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="348" t="s">
         <v>340</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="351"/>
+      <c r="D61" s="351"/>
+      <c r="E61" s="351"/>
+      <c r="F61" s="351"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
@@ -4801,22 +4801,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
@@ -4885,22 +4885,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B77" s="232" t="s">
@@ -4944,22 +4944,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="347" t="s">
         <v>368</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="1" t="s">
@@ -5015,13 +5015,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="347" t="s">
         <v>346</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B96" s="47" t="s">
@@ -5152,13 +5152,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="347" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
@@ -5197,13 +5197,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B120" s="255" t="s">
@@ -5346,13 +5346,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A131" s="244" t="s">
@@ -5365,22 +5365,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="350" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="347" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="232" t="s">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.15">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.15">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>1.6842565597667636</v>
+        <v>1.9250796540737376</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.15">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>6.9666244387770604</v>
+        <v>8.7011458625417593</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.15">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>8.6508809985438244</v>
+        <v>10.626225516615497</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54746327251728155</v>
+        <v>0.44413091318768816</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.15">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="C149" s="326">
         <f>Scenarios!C90</f>
-        <v>0.22</v>
+        <v>0.16739999999999999</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.15">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="C150" s="238">
         <f>Scenarios!C91</f>
-        <v>2.1647759063533951</v>
+        <v>2.3520627768819593</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.15">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>10.527542756885076</v>
+        <v>12.01565469328626</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.15">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>12.692318663238471</v>
+        <v>14.36771747016822</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.33605139719334998</v>
+        <v>0.24840951500307817</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.15">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="C165" s="92">
         <f>F32</f>
-        <v>0.12</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.15">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C166" s="238">
         <f>Scenarios!C103</f>
-        <v>2.5459411443148712</v>
+        <v>2.5573593134949681</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.15">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>13.606688356986439</v>
+        <v>13.701890891667681</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.15">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>16.152629501301309</v>
+        <v>16.259250205162648</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15520661682081283</v>
+        <v>0.14963028232216602</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
@@ -5713,13 +5713,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="354" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B176" s="232" t="s">
@@ -5727,13 +5727,13 @@
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="351" t="s">
         <v>383</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="351"/>
+      <c r="D177" s="351"/>
+      <c r="E177" s="351"/>
+      <c r="F177" s="351"/>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B178" s="236" t="s">
@@ -5756,13 +5756,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="348" t="s">
         <v>384</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B185" s="1" t="s">
@@ -5770,22 +5770,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="353" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="353" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B189" s="1" t="s">
@@ -15441,10 +15441,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="355" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -15459,8 +15459,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.15">
@@ -15475,8 +15475,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="355"/>
+      <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.15">
@@ -15491,8 +15491,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="355"/>
+      <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.15">
@@ -16971,8 +16971,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354"/>
-      <c r="F6" s="354"/>
+      <c r="E6" s="355"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -18437,11 +18437,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="357" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 兴业银行(601166.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="357"/>
       <c r="H7" s="269">
         <v>4</v>
       </c>
@@ -18462,8 +18462,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="357"/>
+      <c r="F8" s="357"/>
       <c r="H8" s="269">
         <v>5</v>
       </c>
@@ -18484,8 +18484,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="357"/>
+      <c r="F9" s="357"/>
       <c r="H9" s="269">
         <v>6</v>
       </c>
@@ -18495,8 +18495,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="357"/>
+      <c r="F10" s="357"/>
       <c r="H10" s="269">
         <v>7</v>
       </c>
@@ -18509,8 +18509,8 @@
       <c r="B11" s="160" t="s">
         <v>455</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="357"/>
+      <c r="F11" s="357"/>
       <c r="H11" s="269">
         <v>8</v>
       </c>
@@ -18528,8 +18528,8 @@
         <v>-5.5054441259114184E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="357"/>
+      <c r="F12" s="357"/>
       <c r="H12" s="269">
         <v>9</v>
       </c>
@@ -18546,8 +18546,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.3520092995664894</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="357"/>
       <c r="H13" s="269">
         <v>10</v>
       </c>
@@ -18564,8 +18564,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.7745066708446342E-2</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="357"/>
     </row>
     <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
@@ -18591,21 +18591,21 @@
       <c r="C18" s="151">
         <v>30</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="357" t="s">
         <v>332</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="358"/>
+      <c r="F19" s="358"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="358"/>
+      <c r="F20" s="358"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
@@ -18619,8 +18619,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="358"/>
+      <c r="F21" s="358"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
@@ -18634,8 +18634,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="358"/>
+      <c r="F22" s="358"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="160" t="s">
@@ -18655,8 +18655,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="356"/>
+      <c r="F25" s="356"/>
     </row>
     <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="119" t="s">
@@ -18666,8 +18666,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="356"/>
+      <c r="F26" s="356"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
@@ -18681,8 +18681,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="356"/>
+      <c r="F27" s="356"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
@@ -18692,8 +18692,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="356"/>
+      <c r="F28" s="356"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="160" t="s">
@@ -18713,8 +18713,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="356"/>
+      <c r="F31" s="356"/>
     </row>
     <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="119" t="s">
@@ -18724,8 +18724,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="356"/>
+      <c r="F32" s="356"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
@@ -18739,8 +18739,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="356"/>
+      <c r="F33" s="356"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
@@ -18750,8 +18750,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="356"/>
+      <c r="F34" s="356"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="160" t="s">
@@ -18771,8 +18771,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="356"/>
+      <c r="F37" s="356"/>
     </row>
     <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="119" t="s">
@@ -18782,8 +18782,8 @@
         <v>0.04</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="356"/>
+      <c r="F38" s="356"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
@@ -18797,8 +18797,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="356"/>
+      <c r="F39" s="356"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
@@ -18809,8 +18809,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="356"/>
+      <c r="F40" s="356"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
@@ -18872,8 +18872,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="356"/>
+      <c r="F49" s="356"/>
     </row>
     <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="119" t="s">
@@ -18883,8 +18883,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="356"/>
+      <c r="F50" s="356"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
@@ -18898,8 +18898,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="356"/>
+      <c r="F51" s="356"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
@@ -18909,8 +18909,8 @@
         <v>0.01</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="356"/>
+      <c r="F52" s="356"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="160" t="s">
@@ -18930,8 +18930,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="356"/>
+      <c r="F55" s="356"/>
     </row>
     <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="119" t="s">
@@ -18941,8 +18941,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="356"/>
+      <c r="F56" s="356"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
@@ -18956,8 +18956,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="356"/>
+      <c r="F57" s="356"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
@@ -18967,8 +18967,8 @@
         <v>0.01</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="356"/>
+      <c r="F58" s="356"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.15">
@@ -19161,7 +19161,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6842565597667636</v>
+        <v>1.9250796540737376</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -19173,7 +19173,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>6.9666244387770604</v>
+        <v>8.7011458625417593</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -19183,7 +19183,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>8.6508809985438244</v>
+        <v>10.626225516615497</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19194,7 +19194,7 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.54746327251728155</v>
+        <v>0.44413091318768816</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.15">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.22</v>
+        <v>0.16739999999999999</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.15">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.1647759063533951</v>
+        <v>2.3520627768819593</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -19262,7 +19262,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>10.527542756885076</v>
+        <v>12.01565469328626</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -19272,7 +19272,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>12.692318663238471</v>
+        <v>14.36771747016822</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.33605139719334998</v>
+        <v>0.24840951500307817</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.15">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
-        <v>0.12</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.15">
@@ -19370,7 +19370,7 @@
       </c>
       <c r="C103" s="117">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>2.5459411443148712</v>
+        <v>2.5573593134949681</v>
       </c>
       <c r="D103" s="117"/>
     </row>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>13.606688356986439</v>
+        <v>13.701890891667681</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -19390,7 +19390,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>16.152629501301309</v>
+        <v>16.259250205162648</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -19400,7 +19400,7 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.15520661682081283</v>
+        <v>0.14963028232216602</v>
       </c>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.15">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C361A8E-9DDE-5B49-8EBE-92F9352F01F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AC33CC-C0BE-4751-9D01-012CA7CB7CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5540" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2498,7 +2487,7 @@
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3911,7 +3900,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4200,7 +4189,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4209,7 +4198,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4226,7 +4215,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="244" t="s">
         <v>268</v>
       </c>
@@ -4240,7 +4229,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>419</v>
       </c>
@@ -4249,7 +4238,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>316</v>
       </c>
@@ -4257,7 +4246,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4266,7 +4255,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>308</v>
       </c>
@@ -4276,7 +4265,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>269</v>
       </c>
@@ -4286,17 +4275,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>422</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>421</v>
       </c>
@@ -4306,7 +4295,7 @@
       <c r="D11" s="49"/>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
@@ -4316,7 +4305,7 @@
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>420</v>
       </c>
@@ -4326,7 +4315,7 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>424</v>
       </c>
@@ -4340,7 +4329,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>423</v>
       </c>
@@ -4354,7 +4343,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4364,11 +4353,11 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
       <c r="B18" s="347" t="s">
         <v>362</v>
       </c>
@@ -4377,14 +4366,14 @@
       <c r="E18" s="347"/>
       <c r="F18" s="347"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>350</v>
       </c>
@@ -4399,7 +4388,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4414,7 +4403,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>438</v>
       </c>
@@ -4422,7 +4411,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>439</v>
       </c>
@@ -4430,7 +4419,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>349</v>
       </c>
@@ -4446,28 +4435,28 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>19.11641746000425</v>
+        <v>26.888151196428591</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>-6.2569556617559918E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.10231184063464993</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>437</v>
       </c>
@@ -4486,13 +4475,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>429</v>
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>10.626225516615497</v>
+        <v>16.315003955335072</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4502,16 +4491,16 @@
         <v>428</v>
       </c>
       <c r="F29" s="332">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.23700000000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>430</v>
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>14.36771747016822</v>
+        <v>20.766144541233739</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4521,16 +4510,16 @@
         <v>441</v>
       </c>
       <c r="F30" s="342">
-        <v>0.16739999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.13700000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>431</v>
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>17.906951319035024</v>
+        <v>25.409202896038835</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4540,16 +4529,16 @@
         <v>440</v>
       </c>
       <c r="F31" s="342">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>432</v>
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>16.259250205162648</v>
+        <v>23.632551844105855</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4559,14 +4548,14 @@
         <v>442</v>
       </c>
       <c r="F32" s="342">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="244" t="s">
         <v>357</v>
       </c>
@@ -4576,7 +4565,7 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
       <c r="B36" s="347" t="s">
         <v>363</v>
       </c>
@@ -4585,7 +4574,7 @@
       <c r="E36" s="347"/>
       <c r="F36" s="347"/>
     </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
       <c r="B37" s="349" t="s">
         <v>341</v>
       </c>
@@ -4594,7 +4583,7 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
         <v>231</v>
       </c>
@@ -4603,7 +4592,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
       <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
@@ -4612,7 +4601,7 @@
       <c r="E40" s="348"/>
       <c r="F40" s="348"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
@@ -4625,11 +4614,11 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
       <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
@@ -4638,7 +4627,7 @@
       <c r="E43" s="348"/>
       <c r="F43" s="348"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
@@ -4651,7 +4640,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
@@ -4664,7 +4653,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6">
       <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
@@ -4673,7 +4662,7 @@
       <c r="E47" s="348"/>
       <c r="F47" s="348"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
@@ -4686,7 +4675,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
@@ -4695,7 +4684,7 @@
       <c r="E50" s="348"/>
       <c r="F50" s="348"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>342</v>
       </c>
@@ -4710,7 +4699,7 @@
       <c r="E51" s="311"/>
       <c r="F51" s="311"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>343</v>
       </c>
@@ -4725,7 +4714,7 @@
       <c r="E52" s="311"/>
       <c r="F52" s="311"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
@@ -4738,12 +4727,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
@@ -4756,7 +4745,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
@@ -4765,7 +4754,7 @@
       <c r="E58" s="348"/>
       <c r="F58" s="348"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
@@ -4778,7 +4767,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="348" t="s">
         <v>340</v>
       </c>
@@ -4787,7 +4776,7 @@
       <c r="E61" s="351"/>
       <c r="F61" s="351"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
@@ -4800,7 +4789,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
       <c r="B64" s="347" t="s">
         <v>345</v>
       </c>
@@ -4809,7 +4798,7 @@
       <c r="E64" s="347"/>
       <c r="F64" s="347"/>
     </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
       <c r="B65" s="347" t="s">
         <v>364</v>
       </c>
@@ -4818,7 +4807,7 @@
       <c r="E65" s="347"/>
       <c r="F65" s="347"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
@@ -4831,7 +4820,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
@@ -4844,7 +4833,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="249" t="s">
         <v>393</v>
       </c>
@@ -4854,7 +4843,7 @@
       </c>
       <c r="F69" s="344"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="249" t="s">
         <v>309</v>
       </c>
@@ -4870,7 +4859,7 @@
         <v>0.19198146616473824</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="13.9">
       <c r="A72" s="244" t="s">
         <v>358</v>
       </c>
@@ -4880,10 +4869,10 @@
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="231"/>
     </row>
-    <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
       <c r="B74" s="347" t="s">
         <v>365</v>
@@ -4893,7 +4882,7 @@
       <c r="E74" s="347"/>
       <c r="F74" s="347"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
@@ -4902,21 +4891,21 @@
       <c r="E75" s="349"/>
       <c r="F75" s="349"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
         <v>435</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
         <v>434</v>
       </c>
@@ -4925,25 +4914,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
       <c r="C80" s="258">
         <f>F31+C79</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="C81" s="122"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="B82" s="321" t="s">
         <v>359</v>
       </c>
       <c r="C82" s="122"/>
     </row>
-    <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" ht="24.5" customHeight="1">
       <c r="B83" s="347" t="s">
         <v>366</v>
       </c>
@@ -4952,7 +4941,7 @@
       <c r="E83" s="347"/>
       <c r="F83" s="347"/>
     </row>
-    <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6" ht="24.5" customHeight="1">
       <c r="B84" s="347" t="s">
         <v>367</v>
       </c>
@@ -4961,7 +4950,7 @@
       <c r="E84" s="347"/>
       <c r="F84" s="347"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
@@ -4969,20 +4958,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>69.017078912347984</v>
+        <v>92.022771883130645</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="13.9">
       <c r="A89" s="244" t="s">
         <v>360</v>
       </c>
@@ -4992,10 +4981,10 @@
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="231"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="B91" s="347" t="s">
         <v>368</v>
       </c>
@@ -5004,17 +4993,17 @@
       <c r="E91" s="347"/>
       <c r="F91" s="347"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="B94" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6" ht="24.5" customHeight="1">
       <c r="B95" s="347" t="s">
         <v>346</v>
       </c>
@@ -5023,7 +5012,7 @@
       <c r="E95" s="347"/>
       <c r="F95" s="347"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
@@ -5036,7 +5025,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
         <v>282</v>
       </c>
@@ -5049,7 +5038,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:6">
       <c r="B98" s="325" t="s">
         <v>407</v>
       </c>
@@ -5058,7 +5047,7 @@
         <v>10.758917470801054</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:6">
       <c r="B99" s="325" t="s">
         <v>408</v>
       </c>
@@ -5067,7 +5056,7 @@
         <v>10.649677544255834</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="325" t="s">
         <v>410</v>
       </c>
@@ -5076,12 +5065,12 @@
         <v>1577.3702399204408</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
@@ -5094,7 +5083,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
         <v>267</v>
       </c>
@@ -5107,7 +5096,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
         <v>283</v>
       </c>
@@ -5120,12 +5109,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>258</v>
       </c>
@@ -5138,7 +5127,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>284</v>
       </c>
@@ -5151,7 +5140,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6" ht="24.5" customHeight="1">
       <c r="B111" s="347" t="s">
         <v>369</v>
       </c>
@@ -5160,20 +5149,20 @@
       <c r="E111" s="347"/>
       <c r="F111" s="347"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>457</v>
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>13.25</v>
+        <v>17.666666666666668</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="325" t="s">
         <v>409</v>
       </c>
@@ -5186,7 +5175,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="13.9">
       <c r="A116" s="244" t="s">
         <v>361</v>
       </c>
@@ -5196,7 +5185,7 @@
       <c r="E116" s="36"/>
       <c r="F116" s="36"/>
     </row>
-    <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6" ht="24.5" customHeight="1">
       <c r="B118" s="348" t="s">
         <v>370</v>
       </c>
@@ -5205,7 +5194,7 @@
       <c r="E118" s="348"/>
       <c r="F118" s="348"/>
     </row>
-    <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
         <v>118</v>
       </c>
@@ -5222,7 +5211,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="B121" s="250" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5237,14 +5226,14 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>26.64 CNY</v>
+        <v>37.71 CNY</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
         <v>0.01</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="B122" s="240" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5259,14 +5248,14 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>21.16 CNY</v>
+        <v>29.79 CNY</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
         <v>0.19600000000000001</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="B123" s="240" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5281,14 +5270,14 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>19.03 CNY</v>
+        <v>26.75 CNY</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
         <v>0.58799999999999997</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="B124" s="240" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5303,14 +5292,14 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>17.21 CNY</v>
+        <v>24.19 CNY</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
         <v>0.19600000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="B125" s="240" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5325,27 +5314,27 @@
       </c>
       <c r="E125" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>14.32 CNY</v>
+        <v>20.16 CNY</v>
       </c>
       <c r="F125" s="243">
         <f>DCF!F78</f>
         <v>0.01</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="233" t="s">
         <v>259</v>
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>19.11641746000425</v>
+        <v>26.888151196428591</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6" ht="24.5" customHeight="1">
       <c r="B129" s="352" t="s">
         <v>373</v>
       </c>
@@ -5354,7 +5343,7 @@
       <c r="E129" s="352"/>
       <c r="F129" s="352"/>
     </row>
-    <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
         <v>405</v>
       </c>
@@ -5364,7 +5353,7 @@
       <c r="E131" s="36"/>
       <c r="F131" s="36"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:6">
       <c r="B133" s="350" t="s">
         <v>371</v>
       </c>
@@ -5373,7 +5362,7 @@
       <c r="E133" s="350"/>
       <c r="F133" s="350"/>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
       <c r="B134" s="347" t="s">
         <v>372</v>
       </c>
@@ -5382,12 +5371,12 @@
       <c r="E134" s="347"/>
       <c r="F134" s="347"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
@@ -5396,16 +5385,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.23700000000000002</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="234" t="s">
         <v>262</v>
       </c>
@@ -5418,7 +5407,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="232" t="s">
         <v>412</v>
       </c>
@@ -5431,49 +5420,49 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>411</v>
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.23700000000000002</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="B142" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>1.9250796540737376</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2.1096570925102589</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="B143" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>8.7011458625417593</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+        <v>14.205346862824813</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>10.626225516615497</v>
+        <v>16.315003955335072</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="281" t="s">
         <v>420</v>
       </c>
@@ -5486,63 +5475,63 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.44413091318768816</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.39322700783153486</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="232" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
         <v>414</v>
       </c>
       <c r="C149" s="326">
         <f>Scenarios!C90</f>
-        <v>0.16739999999999999</v>
-      </c>
-    </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.13700000000000001</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
       <c r="B150" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C150" s="238">
         <f>Scenarios!C91</f>
-        <v>2.3520627768819593</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+        <v>2.4733714409630472</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>12.01565469328626</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.15">
+        <v>18.292773100270693</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
       <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>14.36771747016822</v>
+        <v>20.766144541233739</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="281" t="s">
         <v>420</v>
       </c>
@@ -5555,63 +5544,63 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.24840951500307817</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.22768417993751855</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="232" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
         <v>413</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
       <c r="B158" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C158" s="238">
         <f>Scenarios!C97</f>
-        <v>2.731722806482753</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+        <v>2.8333926664293383</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
       <c r="B159" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>15.175228512552271</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.15">
+        <v>22.575810229609498</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
         <v>404</v>
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>17.906951319035024</v>
+        <v>25.409202896038835</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:6">
       <c r="B161" s="281" t="s">
         <v>420</v>
       </c>
@@ -5624,63 +5613,63 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6">
       <c r="B162" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>6.3268452025579403E-2</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+        <v>5.5003718537040891E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="B164" s="232" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
       <c r="B166" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C166" s="238">
         <f>Scenarios!C103</f>
-        <v>2.5573593134949681</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2.6975834619563113</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
       <c r="B167" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>13.701890891667681</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+        <v>20.934968382149542</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
         <v>404</v>
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>16.259250205162648</v>
+        <v>23.632551844105855</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6">
       <c r="B169" s="281" t="s">
         <v>420</v>
       </c>
@@ -5693,16 +5682,16 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6">
       <c r="B170" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.14963028232216602</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.1210155297728992</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
       <c r="A172" s="244" t="s">
         <v>377</v>
       </c>
@@ -5712,7 +5701,7 @@
       <c r="E172" s="36"/>
       <c r="F172" s="36"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:6">
       <c r="B174" s="354" t="s">
         <v>379</v>
       </c>
@@ -5721,12 +5710,12 @@
       <c r="E174" s="347"/>
       <c r="F174" s="347"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:6">
       <c r="B177" s="351" t="s">
         <v>383</v>
       </c>
@@ -5735,27 +5724,27 @@
       <c r="E177" s="351"/>
       <c r="F177" s="351"/>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:6">
       <c r="B178" s="236" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:6">
       <c r="B179" s="236" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:6">
       <c r="B180" s="236" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
       <c r="B183" s="348" t="s">
         <v>384</v>
       </c>
@@ -5764,12 +5753,12 @@
       <c r="E183" s="348"/>
       <c r="F183" s="348"/>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="2:6" ht="24.5" customHeight="1">
       <c r="B186" s="353" t="s">
         <v>385</v>
       </c>
@@ -5778,7 +5767,7 @@
       <c r="E186" s="353"/>
       <c r="F186" s="353"/>
     </row>
-    <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="2:6" ht="24.5" customHeight="1">
       <c r="B187" s="353" t="s">
         <v>386</v>
       </c>
@@ -5787,22 +5776,22 @@
       <c r="E187" s="353"/>
       <c r="F187" s="353"/>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:6">
       <c r="B190" s="236" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:6">
       <c r="B191" s="236" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:6">
       <c r="B192" s="236" t="s">
         <v>391</v>
       </c>
@@ -5863,15 +5852,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -5920,7 +5909,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5936,7 +5925,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5944,7 +5933,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5980,7 +5969,7 @@
       </c>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6016,7 +6005,7 @@
       </c>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6052,7 +6041,7 @@
       </c>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6088,7 +6077,7 @@
       </c>
       <c r="M7" s="188"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6124,7 +6113,7 @@
       </c>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -6140,7 +6129,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -6156,7 +6145,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -6172,7 +6161,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6208,7 +6197,7 @@
       </c>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6244,7 +6233,7 @@
       </c>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6280,7 +6269,7 @@
       </c>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6316,7 +6305,7 @@
       </c>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6352,13 +6341,13 @@
       </c>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6374,7 +6363,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6390,7 +6379,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6406,7 +6395,7 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>374</v>
       </c>
@@ -6442,7 +6431,7 @@
       </c>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>376</v>
       </c>
@@ -6478,7 +6467,7 @@
       </c>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>375</v>
       </c>
@@ -6514,7 +6503,7 @@
       </c>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6534,7 +6523,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6542,7 +6531,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6561,7 +6550,7 @@
       <c r="L28" s="181"/>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6580,7 +6569,7 @@
       <c r="L29" s="181"/>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6617,7 +6606,7 @@
       </c>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6654,7 +6643,7 @@
       </c>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6691,7 +6680,7 @@
       </c>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6707,12 +6696,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6761,7 +6750,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6810,7 +6799,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6859,7 +6848,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6908,7 +6897,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -6957,7 +6946,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7006,7 +6995,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7055,7 +7044,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -7104,7 +7093,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -7153,7 +7142,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7202,7 +7191,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7251,7 +7240,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7300,7 +7289,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7349,12 +7338,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7403,7 +7392,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7452,12 +7441,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -7506,7 +7495,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7555,7 +7544,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7604,7 +7593,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7653,13 +7642,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7708,7 +7697,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7757,7 +7746,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7806,7 +7795,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>396</v>
       </c>
@@ -7855,7 +7844,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7904,12 +7893,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7959,7 +7948,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8008,7 +7997,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8058,7 +8047,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -8107,7 +8096,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8157,7 +8146,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -8173,13 +8162,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8228,7 +8217,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -8262,7 +8251,7 @@
       <c r="L77" s="324"/>
       <c r="M77" s="324"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -8296,7 +8285,7 @@
       <c r="L78" s="324"/>
       <c r="M78" s="324"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8345,7 +8334,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8426,7 +8415,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8437,7 +8426,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8453,7 +8442,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -8464,7 +8453,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -8484,7 +8473,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8506,7 +8495,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8527,7 +8516,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8548,7 +8537,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8570,7 +8559,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8591,7 +8580,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8612,7 +8601,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8624,7 +8613,7 @@
       </c>
       <c r="H10" s="286"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8636,7 +8625,7 @@
       </c>
       <c r="H11" s="286"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8660,12 +8649,12 @@
         <v>859334.7</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8685,7 +8674,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8706,7 +8695,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8726,7 +8715,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8747,7 +8736,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8767,7 +8756,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8788,7 +8777,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8808,7 +8797,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8828,7 +8817,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8840,7 +8829,7 @@
       </c>
       <c r="H22" s="286"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8853,7 +8842,7 @@
       </c>
       <c r="H23" s="286"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8877,7 +8866,7 @@
         <v>6770949.1000000006</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8894,7 +8883,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8914,7 +8903,7 @@
         <v>-1919409.4999999991</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8929,7 +8918,7 @@
       </c>
       <c r="H28" s="207"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8948,7 +8937,7 @@
         <v>-1931112.4999999991</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8965,7 +8954,7 @@
       </c>
       <c r="H30" s="207"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -8982,7 +8971,7 @@
       </c>
       <c r="H31" s="207"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9002,7 +8991,7 @@
         <v>7694877.5000000009</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9013,7 +9002,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="214"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="215" t="s">
@@ -9026,7 +9015,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -9045,7 +9034,7 @@
         <v>64593.7</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9061,7 +9050,7 @@
       </c>
       <c r="H36" s="214"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9077,7 +9066,7 @@
       </c>
       <c r="H37" s="214"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9093,7 +9082,7 @@
       </c>
       <c r="H38" s="214"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9112,7 +9101,7 @@
         <v>4004.5</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -9132,7 +9121,7 @@
         <v>7630283.8000000007</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9152,7 +9141,7 @@
         <v>5484397.7000000011</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9171,7 +9160,7 @@
         <v>2145886.1</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -9182,7 +9171,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -9196,7 +9185,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -9210,7 +9199,7 @@
       </c>
       <c r="F46" s="275"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9225,10 +9214,10 @@
       </c>
       <c r="F47" s="275"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="275"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -9241,7 +9230,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="275"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -9255,7 +9244,7 @@
       </c>
       <c r="F50" s="275"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -9266,10 +9255,10 @@
       </c>
       <c r="F51" s="275"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="275"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -9281,7 +9270,7 @@
       </c>
       <c r="F53" s="275"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -9295,7 +9284,7 @@
       </c>
       <c r="F54" s="275"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -9309,10 +9298,10 @@
       </c>
       <c r="F55" s="275"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="275"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -9324,7 +9313,7 @@
       </c>
       <c r="F57" s="275"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -9335,7 +9324,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -9346,10 +9335,10 @@
       </c>
       <c r="F59" s="275"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="275"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -9361,7 +9350,7 @@
       </c>
       <c r="F61" s="275"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -9377,7 +9366,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -9388,7 +9377,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -9402,7 +9391,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -9418,7 +9407,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -9428,7 +9417,7 @@
       </c>
       <c r="F67" s="275"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -9438,7 +9427,7 @@
       </c>
       <c r="F68" s="275"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -9448,7 +9437,7 @@
       </c>
       <c r="F69" s="275"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -9458,10 +9447,10 @@
       </c>
       <c r="F70" s="275"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="275"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="277" t="s">
         <v>319</v>
       </c>
@@ -9473,7 +9462,7 @@
       </c>
       <c r="F72" s="275"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
@@ -9489,7 +9478,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="279" t="s">
         <v>323</v>
       </c>
@@ -9505,7 +9494,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
@@ -9518,7 +9507,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="281" t="s">
         <v>324</v>
       </c>
@@ -9531,10 +9520,10 @@
         <v>325</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="275"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -9546,7 +9535,7 @@
       </c>
       <c r="F78" s="275"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9560,7 +9549,7 @@
       </c>
       <c r="F79" s="275"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9574,7 +9563,7 @@
       </c>
       <c r="F80" s="275"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9588,7 +9577,7 @@
       </c>
       <c r="F81" s="275"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9602,7 +9591,7 @@
       </c>
       <c r="F82" s="275"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>289</v>
       </c>
@@ -9613,7 +9602,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>290</v>
       </c>
@@ -9621,7 +9610,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="260" t="s">
         <v>287</v>
       </c>
@@ -9638,7 +9627,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="260" t="s">
         <v>288</v>
       </c>
@@ -9655,7 +9644,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="261" t="s">
         <v>190</v>
       </c>
@@ -9672,7 +9661,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>292</v>
       </c>
@@ -9703,19 +9692,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9772,7 +9761,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9795,7 +9784,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9809,7 +9798,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9866,7 +9855,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9921,7 +9910,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -9976,7 +9965,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10031,7 +10020,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -10088,7 +10077,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10143,7 +10132,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -10198,7 +10187,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -10255,7 +10244,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10310,7 +10299,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -10365,7 +10354,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10420,7 +10409,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -10477,7 +10466,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -10534,7 +10523,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10560,7 +10549,7 @@
       <c r="P17" s="194"/>
       <c r="Q17" s="194"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10585,7 +10574,7 @@
       <c r="P18" s="195"/>
       <c r="Q18" s="195"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10642,7 +10631,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10661,7 +10650,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10684,7 +10673,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10705,7 +10694,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10762,7 +10751,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10819,7 +10808,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10876,18 +10865,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="293"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="293"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10946,7 +10935,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11006,7 +10995,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11061,18 +11050,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="293"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="293"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -11129,7 +11118,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11188,7 +11177,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11245,18 +11234,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="293"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="293"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11314,7 +11303,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11372,7 +11361,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11427,18 +11416,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="293"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="293"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -11496,10 +11485,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -11522,14 +11511,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="293"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11584,7 +11573,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>347</v>
@@ -11639,7 +11628,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="313" t="s">
         <v>344</v>
@@ -11696,7 +11685,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11751,11 +11740,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="293"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11765,7 +11754,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11792,7 +11781,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11819,7 +11808,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11874,11 +11863,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="293"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11888,7 +11877,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -11943,7 +11932,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -11998,7 +11987,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -12053,7 +12042,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -12108,7 +12097,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -12164,7 +12153,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -12219,11 +12208,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="293"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -12233,7 +12222,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -12258,7 +12247,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -12283,7 +12272,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -12308,7 +12297,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -12335,10 +12324,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -12361,7 +12350,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -12382,7 +12371,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12439,7 +12428,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12496,7 +12485,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12553,7 +12542,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12610,7 +12599,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12667,7 +12656,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12726,7 +12715,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12783,7 +12772,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12840,7 +12829,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12897,7 +12886,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12954,7 +12943,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13012,7 +13001,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -13069,7 +13058,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13095,7 +13084,7 @@
       <c r="P85" s="248"/>
       <c r="Q85" s="248"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -13119,7 +13108,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -13176,18 +13165,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="293"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="293"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13243,7 +13232,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13299,7 +13288,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
@@ -13354,7 +13343,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>310</v>
@@ -13409,11 +13398,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="293"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -13434,7 +13423,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -13491,7 +13480,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -13548,10 +13537,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13574,7 +13563,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13584,7 +13573,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13641,7 +13630,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13698,7 +13687,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13755,7 +13744,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13812,7 +13801,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13869,11 +13858,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="293"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13896,7 +13885,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -13953,7 +13942,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -14010,7 +13999,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14037,18 +14026,18 @@
       <c r="P110" s="223"/>
       <c r="Q110" s="223"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="293"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="293"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>394</v>
@@ -14100,7 +14089,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>395</v>
@@ -14152,11 +14141,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="293"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14210,7 +14199,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -14265,7 +14254,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -14319,7 +14308,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -14375,7 +14364,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -14432,7 +14421,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14451,7 +14440,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -14474,7 +14463,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -14495,7 +14484,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14553,7 +14542,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
@@ -14610,7 +14599,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>397</v>
       </c>
@@ -14660,688 +14649,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15363,16 +15352,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15384,7 +15373,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>164</v>
       </c>
@@ -15397,7 +15386,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
@@ -15418,24 +15407,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>229</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1433782.2800642187</v>
+        <v>1911709.7067522916</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15447,7 +15436,7 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
         <v>225</v>
       </c>
@@ -15463,7 +15452,7 @@
       <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
         <v>226</v>
       </c>
@@ -15479,7 +15468,7 @@
       <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="225" t="s">
         <v>191</v>
       </c>
@@ -15495,13 +15484,13 @@
       <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
         <v>228</v>
       </c>
       <c r="C10" s="230">
         <f>C6-C7+C8+C9</f>
-        <v>-5937000.6199357808</v>
+        <v>-5459073.1932477076</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15509,7 +15498,7 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="228" t="s">
         <v>167</v>
       </c>
@@ -15523,13 +15512,13 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>-285.78567749520096</v>
+        <v>-262.77998452441824</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15537,10 +15526,10 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>230</v>
       </c>
@@ -15550,13 +15539,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15566,7 +15555,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15576,13 +15565,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>-260.94323240848024</v>
+        <v>-228.15289802637383</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15590,10 +15579,10 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
         <v>108</v>
       </c>
@@ -15611,7 +15600,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15625,15 +15614,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <v>0.94339622641509424</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>109443.29180065617</v>
+        <v>111508.25957047987</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15647,15 +15636,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.88999644001423983</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>104425.14779533936</v>
+        <v>108402.89461417214</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15669,15 +15658,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.8396192830323016</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>99637.093445073886</v>
+        <v>105384.01017104799</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15691,15 +15680,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.79209366323802044</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>95068.578783715799</v>
+        <v>102449.19786744905</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15713,15 +15702,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.74725817286605689</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>90709.537577367228</v>
+        <v>99596.116399897961</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15735,15 +15724,15 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.70496054043967626</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>86550.365144505515</v>
+        <v>96822.489667278176</v>
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15757,15 +15746,15 @@
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.66505711362233599</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>82581.897193094017</v>
+        <v>94126.104955030081</v>
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15779,15 +15768,15 @@
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.62741237134182648</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>78795.389628043515</v>
+        <v>91504.811169915076</v>
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15801,15 +15790,15 @@
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.59189846353002495</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>75182.499284533231</v>
+        <v>88956.517123938975</v>
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15823,15 +15812,15 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.55839477691511785</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>71735.265544738562</v>
+        <v>86479.189866066517</v>
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15845,15 +15834,15 @@
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
-        <v>0.42888285933767062</v>
+        <v>0.52678752539162055</v>
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>68446.092797460296</v>
+        <v>84070.853060394918</v>
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15867,15 +15856,15 @@
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
-        <v>0.39711375864599124</v>
+        <v>0.4969693635770005</v>
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>65307.733702007041</v>
+        <v>81729.58540949384</v>
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15889,15 +15878,15 @@
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
-        <v>0.36769792467221413</v>
+        <v>0.46883902224245327</v>
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>62313.273219454299</v>
+        <v>79453.51912165276</v>
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15911,15 +15900,15 @@
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
-        <v>0.34046104136316119</v>
+        <v>0.44230096437967292</v>
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>59456.113376095134</v>
+        <v>77240.838420814121</v>
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15933,15 +15922,15 @@
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
-        <v>0.31524170496588994</v>
+        <v>0.41726506073554037</v>
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>56729.958725510143</v>
+        <v>75089.778098002629</v>
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15955,15 +15944,15 @@
       </c>
       <c r="E36" s="125">
         <f t="shared" si="0"/>
-        <v>0.29189046756100923</v>
+        <v>0.39364628371277405</v>
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>54128.80247722393</v>
+        <v>72998.622103095593</v>
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -15977,15 +15966,15 @@
       </c>
       <c r="E37" s="125">
         <f t="shared" si="0"/>
-        <v>0.27026895144537894</v>
+        <v>0.37136441859695657</v>
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>51646.913261384107</v>
+        <v>70965.702175810511</v>
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -15999,15 +15988,15 @@
       </c>
       <c r="E38" s="125">
         <f t="shared" si="0"/>
-        <v>0.25024902911609154</v>
+        <v>0.35034379112920433</v>
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>49278.822500300295</v>
+        <v>68989.396514818276</v>
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -16021,15 +16010,15 @@
       </c>
       <c r="E39" s="125">
         <f t="shared" si="0"/>
-        <v>0.23171206399638106</v>
+        <v>0.3305130104992493</v>
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>47019.312359017516</v>
+        <v>67068.128483919398</v>
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -16043,15 +16032,15 @@
       </c>
       <c r="E40" s="125">
         <f t="shared" si="0"/>
-        <v>0.21454820740405653</v>
+        <v>0.31180472688608429</v>
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>44863.404248374347</v>
+        <v>65200.365354252172</v>
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -16065,15 +16054,15 @@
       </c>
       <c r="E41" s="125">
         <f t="shared" si="0"/>
-        <v>0.19865574759634863</v>
+        <v>0.29415540272272095</v>
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>42806.347855213709</v>
+        <v>63384.617081528188</v>
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -16087,15 +16076,15 @@
       </c>
       <c r="E42" s="125">
         <f t="shared" si="0"/>
-        <v>0.18394050703365611</v>
+        <v>0.27750509690822728</v>
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>40843.610675575437</v>
+        <v>61619.435117320827</v>
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -16109,15 +16098,15 @@
       </c>
       <c r="E43" s="125">
         <f t="shared" si="0"/>
-        <v>0.17031528429042234</v>
+        <v>0.26179726123417668</v>
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>38970.86802780813</v>
+        <v>59903.411253457554</v>
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -16131,15 +16120,15 @@
       </c>
       <c r="E44" s="125">
         <f t="shared" si="0"/>
-        <v>0.1576993373059466</v>
+        <v>0.24697854833412897</v>
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>37183.993523595105</v>
+        <v>58235.176498594403</v>
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -16153,15 +16142,15 @@
       </c>
       <c r="E45" s="125">
         <f t="shared" si="0"/>
-        <v>0.1460179049129135</v>
+        <v>0.23299863050389524</v>
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>35479.049975898837</v>
+        <v>56613.399986076707</v>
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -16175,15 +16164,15 @@
       </c>
       <c r="E46" s="125">
         <f t="shared" si="0"/>
-        <v>0.13520176380825324</v>
+        <v>0.21981002877725966</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>33852.280723789918</v>
+        <v>55036.787912214371</v>
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -16197,15 +16186,15 @@
       </c>
       <c r="E47" s="125">
         <f t="shared" si="0"/>
-        <v>0.12518681834097523</v>
+        <v>0.20736795167666003</v>
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>32300.101355046092</v>
+        <v>53504.082504124774</v>
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -16219,15 +16208,15 @@
       </c>
       <c r="E48" s="125">
         <f t="shared" si="0"/>
-        <v>0.11591372068608817</v>
+        <v>0.1956301430911887</v>
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>30819.091808283007</v>
+        <v>52014.061016320193</v>
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -16241,15 +16230,15 @@
       </c>
       <c r="E49" s="125">
         <f t="shared" si="0"/>
-        <v>0.10732751915378534</v>
+        <v>0.18455673876527234</v>
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>29405.988837214321</v>
+        <v>50565.534755238688</v>
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -16263,21 +16252,21 @@
       </c>
       <c r="E50" s="125">
         <f t="shared" si="0"/>
-        <v>9.9377332549801231E-2</v>
+        <v>0.17411013091063426</v>
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>28057.678820437257</v>
+        <v>49157.348130940874</v>
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1477484.4393088585</v>
+        <v>1969979.2524118114</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16285,30 +16274,30 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>9.9377332549801231E-2</v>
+        <v>0.17411013091063426</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>146828.46246235305</v>
+        <v>342993.34552865388</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>1949866.9669291095</v>
+        <v>2631063.579932001</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
         <v>130</v>
       </c>
@@ -16318,10 +16307,10 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>1949866.9669291095</v>
+        <v>2631063.579932001</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16345,141 +16334,141 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1433782.2800642184</v>
+        <v>1911709.7067522909</v>
       </c>
       <c r="C56" s="124">
-        <v>1480043.6018848091</v>
+        <v>1968874.0875522024</v>
       </c>
       <c r="D56" s="124">
-        <v>1503690.0714352452</v>
+        <v>1998014.3064496904</v>
       </c>
       <c r="E56" s="124">
-        <v>1527690.4301062953</v>
+        <v>2027537.4569108186</v>
       </c>
       <c r="F56" s="124">
-        <v>1576783.5652253886</v>
+        <v>2087766.0566947917</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>1433782.2800642182</v>
+        <v>1911709.7067522909</v>
       </c>
       <c r="C57" s="124">
-        <v>1526347.5230723554</v>
+        <v>2022822.2763396518</v>
       </c>
       <c r="D57" s="124">
-        <v>1576042.6007558678</v>
+        <v>2082327.300124404</v>
       </c>
       <c r="E57" s="124">
-        <v>1628190.3097296776</v>
+        <v>2144673.0507178493</v>
       </c>
       <c r="F57" s="124">
-        <v>1740420.958714019</v>
+        <v>2278563.8621934908</v>
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>1433782.280064218</v>
+        <v>1911709.7067522905</v>
       </c>
       <c r="C58" s="124">
-        <v>1583661.4644162063</v>
+        <v>2095973.8538441975</v>
       </c>
       <c r="D58" s="124">
-        <v>1667927.9964837241</v>
+        <v>2199626.863069878</v>
       </c>
       <c r="E58" s="124">
-        <v>1759204.6477251006</v>
+        <v>2311958.1806159643</v>
       </c>
       <c r="F58" s="124">
-        <v>1965510.5067752679</v>
+        <v>2566089.782987583</v>
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>1433782.2800642177</v>
+        <v>1911709.7067522905</v>
       </c>
       <c r="C59" s="124">
-        <v>1642055.1793496069</v>
+        <v>2177729.7057453385</v>
       </c>
       <c r="D59" s="124">
-        <v>1764108.6104473544</v>
+        <v>2334315.2883597421</v>
       </c>
       <c r="E59" s="124">
-        <v>1900218.7932793819</v>
+        <v>2509472.5608553481</v>
       </c>
       <c r="F59" s="124">
-        <v>2222276.49861127</v>
+        <v>2925896.5784820877</v>
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>1433782.2800642177</v>
+        <v>1911709.7067522905</v>
       </c>
       <c r="C60" s="124">
-        <v>1696364.5745054719</v>
+        <v>2261174.8479017401</v>
       </c>
       <c r="D60" s="124">
-        <v>1856112.8014444185</v>
+        <v>2475707.9738625088</v>
       </c>
       <c r="E60" s="124">
-        <v>2039122.5238502626</v>
+        <v>2722988.8120144377</v>
       </c>
       <c r="F60" s="124">
-        <v>2491359.4511116408</v>
+        <v>3339715.8483383819</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>1433782.2800642182</v>
+        <v>1911709.70675229</v>
       </c>
       <c r="C61" s="124">
-        <v>1744273.0159140313</v>
+        <v>2341971.4002733147</v>
       </c>
       <c r="D61" s="124">
-        <v>1939673.0690846399</v>
+        <v>2616661.8419397096</v>
       </c>
       <c r="E61" s="124">
-        <v>2169207.0985259619</v>
+        <v>2942473.8289640578</v>
       </c>
       <c r="F61" s="124">
-        <v>2760408.2084358027</v>
+        <v>3793896.3810982425</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
         <v>131</v>
       </c>
@@ -16489,7 +16478,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>0</v>
@@ -16512,193 +16501,193 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>-285.78567749520096</v>
+        <v>-262.77998452441824</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>-285.78567749520096</v>
+        <v>-262.77998452441824</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>-285.78567749520096</v>
+        <v>-262.77998452441824</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>-285.78567749520096</v>
+        <v>-262.77998452441824</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>-285.78567749520096</v>
+        <v>-262.77998452441824</v>
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>-285.78567749520096</v>
+        <v>-262.77998452441835</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>-283.55882524358969</v>
+        <v>-260.02829855682057</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>-282.42056996058562</v>
+        <v>-258.62559410501149</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>-281.26527973880218</v>
+        <v>-257.20445671654727</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>-278.90211426543806</v>
+        <v>-254.30527036038407</v>
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>-285.78567749520101</v>
+        <v>-262.77998452441835</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>-281.32992241295295</v>
+        <v>-257.43142840819883</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>-278.93778160766647</v>
+        <v>-254.56707237636843</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>-276.42758002728266</v>
+        <v>-251.56597405873225</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>-271.02520362394938</v>
+        <v>-245.12095599027151</v>
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>-285.78567749520101</v>
+        <v>-262.77998452441835</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>-278.57103714319709</v>
+        <v>-253.91017677369831</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>-274.51475190781719</v>
+        <v>-248.92069683891299</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>-270.12102495974887</v>
+        <v>-243.51347461612264</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>-260.1902091363678</v>
+        <v>-231.28050096393201</v>
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>-285.78567749520101</v>
+        <v>-262.77998452441835</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>-275.76017548896937</v>
+        <v>-249.97474657577834</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>-269.88496598002024</v>
+        <v>-242.43728453422608</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>-263.33311542369211</v>
+        <v>-234.00584869770609</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>-247.83042552978083</v>
+        <v>-213.96070677821297</v>
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>-285.78567749520101</v>
+        <v>-262.77998452441835</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>-273.14591817579742</v>
+        <v>-245.95800007169785</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>-265.45621790675858</v>
+        <v>-235.63115345794014</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>-256.64679361087087</v>
+        <v>-223.72795074889362</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>-234.87774810803597</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+        <v>-194.04094796947462</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>-285.78567749520101</v>
+        <v>-262.77998452441835</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>-270.83977956100432</v>
+        <v>-242.06874707393808</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>-261.43392967942481</v>
+        <v>-228.84614546101528</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>-250.38499397747751</v>
+        <v>-213.16273806247972</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>-221.92671671805448</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>-172.1783443470226</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
         <v>118</v>
       </c>
@@ -16715,7 +16704,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16730,14 +16719,14 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>-221.92671671805448</v>
+        <v>-172.1783443470226</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
         <v>0.01</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16752,7 +16741,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>-250.38499397747751</v>
+        <v>-213.16273806247972</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16760,7 +16749,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16775,7 +16764,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>-261.43392967942481</v>
+        <v>-228.84614546101528</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16783,7 +16772,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16798,7 +16787,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>-270.83977956100432</v>
+        <v>-242.06874707393808</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16806,7 +16795,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16821,21 +16810,21 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>-285.78567749520101</v>
+        <v>-262.77998452441835</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
         <v>0.01</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
         <v>311</v>
       </c>
@@ -16843,23 +16832,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16893,16 +16882,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>451</v>
       </c>
@@ -16914,7 +16903,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>450</v>
       </c>
@@ -16927,7 +16916,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>448</v>
       </c>
@@ -16948,24 +16937,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>449</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>275259.62428774999</v>
+        <v>367012.83238366671</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16975,13 +16964,13 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="150" t="s">
         <v>452</v>
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>13.25</v>
+        <v>17.666666666666668</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -16989,10 +16978,10 @@
       </c>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>230</v>
       </c>
@@ -17002,13 +16991,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="153" t="s">
         <v>134</v>
       </c>
@@ -17018,7 +17007,7 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="119" t="s">
         <v>135</v>
       </c>
@@ -17028,13 +17017,13 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="141">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>19.120213087506169</v>
+        <v>26.886199522956279</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17042,10 +17031,10 @@
       </c>
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="129" t="s">
         <v>108</v>
       </c>
@@ -17063,7 +17052,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="123">
         <v>1</v>
       </c>
@@ -17077,15 +17066,15 @@
       </c>
       <c r="E16" s="125">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.92592592592592582</v>
+        <v>0.94339622641509424</v>
       </c>
       <c r="F16" s="126">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>21011.083621785241</v>
+        <v>21407.519161818927</v>
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="123">
         <v>2</v>
       </c>
@@ -17099,15 +17088,15 @@
       </c>
       <c r="E17" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.88999644001423983</v>
       </c>
       <c r="F17" s="126">
         <f t="shared" si="1"/>
-        <v>20047.692978218729</v>
+        <v>20811.346644530371</v>
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="123">
         <v>3</v>
       </c>
@@ -17121,15 +17110,15 @@
       </c>
       <c r="E18" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.8396192830323016</v>
       </c>
       <c r="F18" s="126">
         <f t="shared" si="1"/>
-        <v>19128.47528397831</v>
+        <v>20231.776782957477</v>
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="123">
         <v>4</v>
       </c>
@@ -17143,15 +17132,15 @@
       </c>
       <c r="E19" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.79209366323802044</v>
       </c>
       <c r="F19" s="126">
         <f t="shared" si="1"/>
-        <v>18251.405141095682</v>
+        <v>19668.347213994242</v>
       </c>
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="123">
         <v>5</v>
       </c>
@@ -17165,15 +17154,15 @@
       </c>
       <c r="E20" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.74725817286605689</v>
       </c>
       <c r="F20" s="126">
         <f t="shared" si="1"/>
-        <v>17414.550019228373</v>
+        <v>19120.60845076634</v>
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>6</v>
       </c>
@@ -17187,15 +17176,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.70496054043967626</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" si="1"/>
-        <v>16616.065997535621</v>
+        <v>18588.12352404428</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>7</v>
       </c>
@@ -17209,15 +17198,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.66505711362233599</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>15854.19370179587</v>
+        <v>18070.467633642707</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>8</v>
       </c>
@@ -17231,15 +17220,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.62741237134182648</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>15127.254427813601</v>
+        <v>17567.227809527809</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>9</v>
       </c>
@@ -17253,15 +17242,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.59189846353002495</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>14433.646442574072</v>
+        <v>17078.002582362446</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>10</v>
       </c>
@@ -17275,15 +17264,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.55839477691511785</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>13771.841454995736</v>
+        <v>16602.401663226221</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>11</v>
       </c>
@@ -17297,15 +17286,15 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.42888285933767062</v>
+        <v>0.52678752539162055</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>13140.381248504156</v>
+        <v>16140.045632254889</v>
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>12</v>
       </c>
@@ -17319,15 +17308,15 @@
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.39711375864599124</v>
+        <v>0.4969693635770005</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>12537.874468007598</v>
+        <v>15690.565635950825</v>
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>13</v>
       </c>
@@ -17341,15 +17330,15 @@
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.36769792467221413</v>
+        <v>0.46883902224245327</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>11962.993554194753</v>
+        <v>15253.60309292296</v>
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>14</v>
       </c>
@@ -17363,15 +17352,15 @@
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.34046104136316119</v>
+        <v>0.44230096437967292</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>11414.471818399648</v>
+        <v>14828.80940782154</v>
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>15</v>
       </c>
@@ -17385,15 +17374,15 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.31524170496588994</v>
+        <v>0.41726506073554037</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>10891.10065158852</v>
+        <v>14415.845693239391</v>
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>16</v>
       </c>
@@ -17407,15 +17396,15 @@
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
-        <v>0.29189046756100923</v>
+        <v>0.39364628371277405</v>
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>10391.726861318964</v>
+        <v>14014.382499357958</v>
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>17</v>
       </c>
@@ -17429,15 +17418,15 @@
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
-        <v>0.27026895144537894</v>
+        <v>0.37136441859695657</v>
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>9915.2501308035826</v>
+        <v>13624.099551122257</v>
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>18</v>
       </c>
@@ -17451,15 +17440,15 @@
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
-        <v>0.25024902911609154</v>
+        <v>0.35034379112920433</v>
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>9460.620594479542</v>
+        <v>13244.685492735292</v>
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>19</v>
       </c>
@@ -17473,15 +17462,15 @@
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
-        <v>0.23171206399638106</v>
+        <v>0.3305130104992493</v>
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>9026.8365247419788</v>
+        <v>12875.837639267887</v>
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>20</v>
       </c>
@@ -17495,15 +17484,15 @@
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
-        <v>0.21454820740405653</v>
+        <v>0.31180472688608429</v>
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>8612.9421247442515</v>
+        <v>12517.261735185932</v>
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>21</v>
       </c>
@@ -17517,15 +17506,15 @@
       </c>
       <c r="E36" s="125">
         <f t="shared" si="0"/>
-        <v>0.19865574759634863</v>
+        <v>0.29415540272272095</v>
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>8218.0254224017244</v>
+        <v>12168.671719602291</v>
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>22</v>
       </c>
@@ -17539,15 +17528,15 @@
       </c>
       <c r="E37" s="125">
         <f t="shared" si="0"/>
-        <v>0.18394050703365611</v>
+        <v>0.27750509690822728</v>
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>7841.2162609587267</v>
+        <v>11829.789498066211</v>
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>23</v>
       </c>
@@ -17561,15 +17550,15 @@
       </c>
       <c r="E38" s="125">
         <f t="shared" si="0"/>
-        <v>0.17031528429042234</v>
+        <v>0.26179726123417668</v>
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>7481.6843816911232</v>
+        <v>11500.344720708059</v>
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>24</v>
       </c>
@@ -17583,15 +17572,15 @@
       </c>
       <c r="E39" s="125">
         <f t="shared" si="0"/>
-        <v>0.1576993373059466</v>
+        <v>0.24697854833412897</v>
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>7138.6375945199188</v>
+        <v>11180.074566562458</v>
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>25</v>
       </c>
@@ -17605,15 +17594,15 @@
       </c>
       <c r="E40" s="125">
         <f t="shared" si="0"/>
-        <v>0.1460179049129135</v>
+        <v>0.23299863050389524</v>
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>6811.3200325050793</v>
+        <v>10868.723533897777</v>
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>26</v>
       </c>
@@ -17627,15 +17616,15 @@
       </c>
       <c r="E41" s="125">
         <f t="shared" si="0"/>
-        <v>0.13520176380825324</v>
+        <v>0.21981002877725966</v>
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>6499.0104863734941</v>
+        <v>10566.043236384656</v>
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>27</v>
       </c>
@@ -17649,15 +17638,15 @@
       </c>
       <c r="E42" s="125">
         <f t="shared" si="0"/>
-        <v>0.12518681834097523</v>
+        <v>0.20736795167666003</v>
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>6201.0208154113961</v>
+        <v>10271.792204940994</v>
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>28</v>
       </c>
@@ -17671,15 +17660,15 @@
       </c>
       <c r="E43" s="125">
         <f t="shared" si="0"/>
-        <v>0.11591372068608817</v>
+        <v>0.1956301430911887</v>
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>5916.6944312198439</v>
+        <v>9985.7356950953017</v>
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>29</v>
       </c>
@@ -17693,15 +17682,15 @@
       </c>
       <c r="E44" s="125">
         <f t="shared" si="0"/>
-        <v>0.10732751915378534</v>
+        <v>0.18455673876527234</v>
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>5645.4048509923305</v>
+        <v>9707.6454997147484</v>
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>30</v>
       </c>
@@ -17715,21 +17704,21 @@
       </c>
       <c r="E45" s="125">
         <f t="shared" si="0"/>
-        <v>9.9377332549801231E-2</v>
+        <v>0.17411013091063426</v>
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>5386.5543171268664</v>
+        <v>9437.2997669484812</v>
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C46" s="124">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>513792.04112394684</v>
+        <v>685056.05483192916</v>
       </c>
       <c r="D46" s="140">
         <f>Terminal_Growth</f>
@@ -17737,30 +17726,30 @@
       </c>
       <c r="E46" s="125">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>9.9377332549801231E-2</v>
+        <v>0.17411013091063426</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>51059.282532215613</v>
+        <v>119275.19938790983</v>
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="115"/>
       <c r="E47" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F47" s="138">
         <f>SUM(F16:F46)</f>
-        <v>397209.25817122031</v>
+        <v>558542.27767656068</v>
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="115"/>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="120" t="s">
         <v>130</v>
       </c>
@@ -17770,10 +17759,10 @@
       <c r="F49" s="118"/>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="134">
         <f>F47</f>
-        <v>397209.25817122031</v>
+        <v>558542.27767656068</v>
       </c>
       <c r="B50" s="132">
         <f>C73</f>
@@ -17797,141 +17786,141 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="144">
         <v>5</v>
       </c>
       <c r="B51" s="124">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>294757.8175345526</v>
+        <v>395557.34013975487</v>
       </c>
       <c r="C51" s="124">
-        <v>304029.09778932447</v>
+        <v>407102.73193324311</v>
       </c>
       <c r="D51" s="124">
-        <v>308763.76361570501</v>
+        <v>412982.55895910517</v>
       </c>
       <c r="E51" s="124">
-        <v>313566.36959432089</v>
+        <v>418935.90174799564</v>
       </c>
       <c r="F51" s="124">
-        <v>323381.30551804398</v>
+        <v>431069.5667946937</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="144">
         <v>10</v>
       </c>
       <c r="B52" s="124">
-        <v>303181.07679074019</v>
+        <v>411893.12148566649</v>
       </c>
       <c r="C52" s="124">
-        <v>321510.31690939749</v>
+        <v>434122.28128641954</v>
       </c>
       <c r="D52" s="124">
-        <v>331330.06530927867</v>
+        <v>445994.94588780403</v>
       </c>
       <c r="E52" s="124">
-        <v>341620.67346023262</v>
+        <v>458412.97738689464</v>
       </c>
       <c r="F52" s="124">
-        <v>363725.30705092638</v>
+        <v>485015.1374620148</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="144">
         <v>15</v>
       </c>
       <c r="B53" s="124">
-        <v>305271.76595888828</v>
+        <v>419979.67410095019</v>
       </c>
       <c r="C53" s="124">
-        <v>334646.03435178101</v>
+        <v>456414.31205559522</v>
       </c>
       <c r="D53" s="124">
-        <v>351123.76814343227</v>
+        <v>476843.43715630146</v>
       </c>
       <c r="E53" s="124">
-        <v>368947.31489207054</v>
+        <v>498938.63661218865</v>
       </c>
       <c r="F53" s="124">
-        <v>409154.45902432024</v>
+        <v>548786.53106863168</v>
       </c>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="145">
         <v>20</v>
       </c>
       <c r="B54" s="124">
-        <v>303957.95673586661</v>
+        <v>422622.87185119989</v>
       </c>
       <c r="C54" s="124">
-        <v>344516.45995201886</v>
+        <v>474805.98207637807</v>
       </c>
       <c r="D54" s="124">
-        <v>368235.43992908241</v>
+        <v>505423.61220162653</v>
       </c>
       <c r="E54" s="124">
-        <v>394653.05571360677</v>
+        <v>539606.66257942491</v>
       </c>
       <c r="F54" s="124">
-        <v>457056.13282183616</v>
+        <v>620664.55681896757</v>
       </c>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="145">
         <v>25</v>
       </c>
       <c r="B55" s="124">
-        <v>301007.39445565315</v>
+        <v>421793.28497020365</v>
       </c>
       <c r="C55" s="124">
-        <v>351933.2837347443</v>
+        <v>489979.72419327294</v>
       </c>
       <c r="D55" s="124">
-        <v>382859.46026137949</v>
+        <v>531713.9127819913</v>
       </c>
       <c r="E55" s="124">
-        <v>418251.41279293416</v>
+        <v>579735.05517070927</v>
       </c>
       <c r="F55" s="124">
-        <v>505587.47654576774</v>
+        <v>699230.82487934455</v>
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="145">
         <v>30</v>
       </c>
       <c r="B56" s="124">
-        <v>297454.06928013661</v>
+        <v>418859.3668527056</v>
       </c>
       <c r="C56" s="124">
-        <v>357506.42487900006</v>
+        <v>502498.56829877582</v>
       </c>
       <c r="D56" s="124">
-        <v>395241.55802528514</v>
+        <v>555752.50737602054</v>
       </c>
       <c r="E56" s="124">
-        <v>439529.78198205412</v>
+        <v>618820.83568369201</v>
       </c>
       <c r="F56" s="124">
-        <v>553473.32676061383</v>
+        <v>783315.11625751655</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="115"/>
       <c r="D57" s="115"/>
       <c r="E57" s="115"/>
       <c r="F57" s="115"/>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="120" t="s">
         <v>131</v>
       </c>
@@ -17941,7 +17930,7 @@
       <c r="F58" s="115"/>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="133">
         <f>B50</f>
         <v>0</v>
@@ -17964,193 +17953,193 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="144">
         <v>0</v>
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>13.25</v>
+        <v>17.666666666666668</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>13.25</v>
+        <v>17.666666666666668</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>13.25</v>
+        <v>17.666666666666668</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>13.25</v>
+        <v>17.666666666666668</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>13.25</v>
+        <v>17.666666666666668</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="144">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>14.188572306739982</v>
+        <v>19.040695744657388</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>14.634858113071347</v>
+        <v>19.596449032701553</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>14.862767754239648</v>
+        <v>19.879482580735569</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>15.093947787930817</v>
+        <v>20.166054910974374</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>15.566403206431939</v>
+        <v>20.750125539875192</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>14.594037457807008</v>
+        <v>19.82704101194242</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>15.476340600524106</v>
+        <v>20.897072143904136</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>15.949027674173564</v>
+        <v>21.468579157965497</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>16.444380228522771</v>
+        <v>22.066338156542585</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>17.508417120364619</v>
+        <v>23.346869661689411</v>
       </c>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>14.694675651837979</v>
+        <v>20.216298326485944</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>16.108646397503744</v>
+        <v>21.970129656264923</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>16.901824740692728</v>
+        <v>22.953513646142746</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>17.759785638628777</v>
+        <v>24.017096412950778</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>19.695211733650211</v>
+        <v>26.416593263449329</v>
       </c>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>14.631433640772675</v>
+        <v>20.343532279817936</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>16.583772887782008</v>
+        <v>22.855437948049211</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>17.725518559742799</v>
+        <v>24.329259618078993</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>18.997166772046651</v>
+        <v>25.974707687979542</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>22.00102458019246</v>
+        <v>29.876540735427092</v>
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>14.489404273719702</v>
+        <v>20.303598976117318</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>16.940791885302616</v>
+        <v>23.585846861340038</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>18.429465860057267</v>
+        <v>25.59477933820213</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>20.133106095186253</v>
+        <v>27.906342969435457</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>24.337147453301789</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+        <v>33.658435935253991</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>14.318360086990827</v>
+        <v>20.162370798692315</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>17.209062687286252</v>
+        <v>24.188458613162062</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>19.025495138947228</v>
+        <v>26.751910098643489</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>21.157369615436895</v>
+        <v>29.787790686793507</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>26.642198609963373</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>37.705948764800347</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="172" t="s">
         <v>118</v>
       </c>
@@ -18167,7 +18156,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18182,14 +18171,14 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>26.642198609963373</v>
+        <v>37.705948764800347</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
         <v>0.01</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18204,7 +18193,7 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>21.157369615436895</v>
+        <v>29.787790686793507</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18212,7 +18201,7 @@
       </c>
       <c r="H70" s="121"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18227,7 +18216,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>19.025495138947228</v>
+        <v>26.751910098643489</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18235,7 +18224,7 @@
       </c>
       <c r="H71" s="121"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18250,7 +18239,7 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>17.209062687286252</v>
+        <v>24.188458613162062</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18258,7 +18247,7 @@
       </c>
       <c r="H72" s="121"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18273,21 +18262,21 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>14.318360086990827</v>
+        <v>20.162370798692315</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
         <v>0.01</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="156"/>
       <c r="C74" s="156"/>
       <c r="D74" s="156"/>
       <c r="E74" s="156"/>
       <c r="F74" s="157"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="156" t="s">
         <v>311</v>
       </c>
@@ -18295,23 +18284,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="116"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="116"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="116"/>
     </row>
   </sheetData>
@@ -18341,7 +18330,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18351,7 +18340,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>146</v>
       </c>
@@ -18364,7 +18353,7 @@
       </c>
       <c r="I2" s="271"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
@@ -18376,7 +18365,7 @@
         <v>-22.7</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
         <v>147</v>
       </c>
@@ -18396,7 +18385,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="269">
         <v>2</v>
       </c>
@@ -18405,7 +18394,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
         <v>96</v>
       </c>
@@ -18422,10 +18411,10 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>20.176417460004249</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>27.94815119642859</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
@@ -18450,7 +18439,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18472,7 +18461,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18494,7 +18483,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="357"/>
       <c r="F10" s="357"/>
       <c r="H10" s="269">
@@ -18505,7 +18494,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
         <v>455</v>
       </c>
@@ -18519,7 +18508,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
         <v>145</v>
       </c>
@@ -18538,7 +18527,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
         <v>153</v>
       </c>
@@ -18556,7 +18545,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18567,7 +18556,7 @@
       <c r="E14" s="357"/>
       <c r="F14" s="357"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>163</v>
       </c>
@@ -18576,7 +18565,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>152</v>
       </c>
@@ -18584,7 +18573,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
         <v>134</v>
       </c>
@@ -18596,18 +18585,18 @@
       </c>
       <c r="F18" s="358"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="358"/>
       <c r="F19" s="358"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
       <c r="E20" s="358"/>
       <c r="F20" s="358"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>278</v>
       </c>
@@ -18622,13 +18611,13 @@
       <c r="E21" s="358"/>
       <c r="F21" s="358"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>279</v>
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>13.25</v>
+        <v>17.666666666666668</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18637,7 +18626,7 @@
       <c r="E22" s="358"/>
       <c r="F22" s="358"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
         <v>116</v>
       </c>
@@ -18646,7 +18635,7 @@
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
         <v>134</v>
       </c>
@@ -18658,7 +18647,7 @@
       <c r="E25" s="356"/>
       <c r="F25" s="356"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
@@ -18669,13 +18658,13 @@
       <c r="E26" s="356"/>
       <c r="F26" s="356"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>19.025495138947228</v>
+        <v>26.751910098643489</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -18684,7 +18673,7 @@
       <c r="E27" s="356"/>
       <c r="F27" s="356"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>148</v>
       </c>
@@ -18695,7 +18684,7 @@
       <c r="E28" s="356"/>
       <c r="F28" s="356"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
         <v>117</v>
       </c>
@@ -18704,7 +18693,7 @@
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
         <v>134</v>
       </c>
@@ -18716,7 +18705,7 @@
       <c r="E31" s="356"/>
       <c r="F31" s="356"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
@@ -18727,13 +18716,13 @@
       <c r="E32" s="356"/>
       <c r="F32" s="356"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>17.209062687286252</v>
+        <v>24.188458613162062</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18742,7 +18731,7 @@
       <c r="E33" s="356"/>
       <c r="F33" s="356"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>148</v>
       </c>
@@ -18753,7 +18742,7 @@
       <c r="E34" s="356"/>
       <c r="F34" s="356"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
@@ -18762,7 +18751,7 @@
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
         <v>134</v>
       </c>
@@ -18774,7 +18763,7 @@
       <c r="E37" s="356"/>
       <c r="F37" s="356"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
@@ -18785,13 +18774,13 @@
       <c r="E38" s="356"/>
       <c r="F38" s="356"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>21.157369615436895</v>
+        <v>29.787790686793507</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18800,7 +18789,7 @@
       <c r="E39" s="356"/>
       <c r="F39" s="356"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>148</v>
       </c>
@@ -18812,20 +18801,20 @@
       <c r="E40" s="356"/>
       <c r="F40" s="356"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>19.088583543912968</v>
+        <v>26.846395919177208</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>162</v>
       </c>
@@ -18834,12 +18823,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
         <v>134</v>
       </c>
@@ -18849,12 +18838,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
         <v>166</v>
       </c>
@@ -18863,7 +18852,7 @@
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
         <v>134</v>
       </c>
@@ -18875,7 +18864,7 @@
       <c r="E49" s="356"/>
       <c r="F49" s="356"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
         <v>135</v>
       </c>
@@ -18886,13 +18875,13 @@
       <c r="E50" s="356"/>
       <c r="F50" s="356"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>14.318360086990827</v>
+        <v>20.162370798692315</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18901,7 +18890,7 @@
       <c r="E51" s="356"/>
       <c r="F51" s="356"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>148</v>
       </c>
@@ -18912,7 +18901,7 @@
       <c r="E52" s="356"/>
       <c r="F52" s="356"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
         <v>317</v>
       </c>
@@ -18921,7 +18910,7 @@
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
         <v>134</v>
       </c>
@@ -18933,7 +18922,7 @@
       <c r="E55" s="356"/>
       <c r="F55" s="356"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
@@ -18944,13 +18933,13 @@
       <c r="E56" s="356"/>
       <c r="F56" s="356"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>26.642198609963373</v>
+        <v>37.705948764800347</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -18959,7 +18948,7 @@
       <c r="E57" s="356"/>
       <c r="F57" s="356"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>148</v>
       </c>
@@ -18970,13 +18959,13 @@
       <c r="E58" s="356"/>
       <c r="F58" s="356"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>19.11641746000425</v>
+        <v>26.888151196428591</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -18990,7 +18979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>351</v>
       </c>
@@ -18999,7 +18988,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>305</v>
       </c>
@@ -19007,7 +18996,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
         <v>134</v>
       </c>
@@ -19020,7 +19009,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
         <v>135</v>
       </c>
@@ -19032,13 +19021,13 @@
         <v>313</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>19.120213087506169</v>
+        <v>26.886199522956279</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -19048,7 +19037,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>352</v>
       </c>
@@ -19056,7 +19045,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>306</v>
       </c>
@@ -19066,7 +19055,7 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>294</v>
       </c>
@@ -19078,7 +19067,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>293</v>
       </c>
@@ -19088,7 +19077,7 @@
       </c>
       <c r="E71" s="273"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>285</v>
       </c>
@@ -19101,10 +19090,10 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>-18.560107151346447</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+        <v>-13.19550584997735</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>128</v>
       </c>
@@ -19113,12 +19102,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="268" t="s">
         <v>298</v>
       </c>
@@ -19128,7 +19117,7 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>112</v>
       </c>
@@ -19141,49 +19130,49 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
         <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.23700000000000002</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.9250796540737376</v>
+        <v>2.1096570925102589</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>8.7011458625417593</v>
+        <v>14.205346862824813</v>
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>10.626225516615497</v>
+        <v>16.315003955335072</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19194,18 +19183,18 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.44413091318768816</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.39322700783153486</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
         <v>301</v>
       </c>
@@ -19218,61 +19207,61 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>299</v>
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-6.2569556617559918E-3</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.10231184063464993</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
         <v>417</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.16739999999999999</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.13700000000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.3520627768819593</v>
+        <v>2.4733714409630472</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>12.01565469328626</v>
+        <v>18.292773100270693</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>14.36771747016822</v>
+        <v>20.766144541233739</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19283,58 +19272,58 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.24840951500307817</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.22768417993751855</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>400</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="306"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
         <v>406</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="306"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.731722806482753</v>
+        <v>2.8333926664293383</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="306"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>15.175228512552271</v>
+        <v>22.575810229609498</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="306"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
         <v>401</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>17.906951319035024</v>
+        <v>25.409202896038835</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -19344,53 +19333,53 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>6.3268452025579403E-2</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+        <v>5.5003718537040891E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
         <v>425</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C103" s="117">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>2.5573593134949681</v>
+        <v>2.6975834619563113</v>
       </c>
       <c r="D103" s="117"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>13.701890891667681</v>
+        <v>20.934968382149542</v>
       </c>
       <c r="D104" s="117"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
         <v>401</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>16.259250205162648</v>
+        <v>23.632551844105855</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -19400,19 +19389,19 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.14963028232216602</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.1210155297728992</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="310" t="s">
         <v>326</v>
       </c>
       <c r="F107" s="307"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="303" t="s">
         <v>327</v>
       </c>
@@ -19420,7 +19409,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="304" t="s">
         <v>327</v>
       </c>
@@ -19428,7 +19417,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="305" t="s">
         <v>327</v>
       </c>

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AC33CC-C0BE-4751-9D01-012CA7CB7CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC1EB92-E563-4A77-BD48-B6B6220A5675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3862,29 +3862,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4300,7 +4300,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>22.7</v>
+        <v>22.52</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>471576.86576089996</v>
+        <v>467837.48973283998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4358,13 +4358,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="347" t="s">
+      <c r="B18" s="349" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="347"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10231184063464993</v>
+        <v>0.10536678638212904</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>16.315003955335072</v>
+        <v>13.079690025486418</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4491,7 +4491,7 @@
         <v>428</v>
       </c>
       <c r="F29" s="332">
-        <v>0.23700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>20.766144541233739</v>
+        <v>18.356272555350223</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4510,7 +4510,7 @@
         <v>441</v>
       </c>
       <c r="F30" s="342">
-        <v>0.13700000000000001</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4566,22 +4566,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="347" t="s">
+      <c r="B36" s="349" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="347"/>
-      <c r="D36" s="347"/>
-      <c r="E36" s="347"/>
-      <c r="F36" s="347"/>
+      <c r="C36" s="349"/>
+      <c r="D36" s="349"/>
+      <c r="E36" s="349"/>
+      <c r="F36" s="349"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="349" t="s">
+      <c r="B37" s="352" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="349"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
@@ -4593,13 +4593,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="348" t="s">
+      <c r="B40" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="348"/>
-      <c r="D40" s="348"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4619,13 +4619,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="348" t="s">
+      <c r="B43" s="350" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="348"/>
-      <c r="D43" s="348"/>
-      <c r="E43" s="348"/>
-      <c r="F43" s="348"/>
+      <c r="C43" s="350"/>
+      <c r="D43" s="350"/>
+      <c r="E43" s="350"/>
+      <c r="F43" s="350"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4654,13 +4654,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="348" t="s">
+      <c r="B47" s="350" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4676,13 +4676,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="348" t="s">
+      <c r="B50" s="350" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="348"/>
-      <c r="D50" s="348"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4746,13 +4746,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="348" t="s">
+      <c r="B58" s="350" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="348"/>
-      <c r="D58" s="348"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="C58" s="350"/>
+      <c r="D58" s="350"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4768,7 +4768,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="348" t="s">
+      <c r="B61" s="350" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="351"/>
@@ -4790,22 +4790,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="347" t="s">
+      <c r="B64" s="349" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="347"/>
-      <c r="D64" s="347"/>
-      <c r="E64" s="347"/>
-      <c r="F64" s="347"/>
+      <c r="C64" s="349"/>
+      <c r="D64" s="349"/>
+      <c r="E64" s="349"/>
+      <c r="F64" s="349"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="347" t="s">
+      <c r="B65" s="349" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="347"/>
-      <c r="D65" s="347"/>
-      <c r="E65" s="347"/>
-      <c r="F65" s="347"/>
+      <c r="C65" s="349"/>
+      <c r="D65" s="349"/>
+      <c r="E65" s="349"/>
+      <c r="F65" s="349"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.24323199616686514</v>
+        <v>0.24517612402255057</v>
       </c>
       <c r="F69" s="344"/>
     </row>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.6696035242290754E-2</v>
+        <v>4.7069271758436948E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>456</v>
@@ -4874,22 +4874,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="347" t="s">
+      <c r="B74" s="349" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="347"/>
-      <c r="D74" s="347"/>
-      <c r="E74" s="347"/>
-      <c r="F74" s="347"/>
+      <c r="C74" s="349"/>
+      <c r="D74" s="349"/>
+      <c r="E74" s="349"/>
+      <c r="F74" s="349"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="349" t="s">
+      <c r="B75" s="352" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="349"/>
-      <c r="D75" s="349"/>
-      <c r="E75" s="349"/>
-      <c r="F75" s="349"/>
+      <c r="C75" s="352"/>
+      <c r="D75" s="352"/>
+      <c r="E75" s="352"/>
+      <c r="F75" s="352"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
@@ -4933,22 +4933,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="347" t="s">
+      <c r="B83" s="349" t="s">
         <v>366</v>
       </c>
-      <c r="C83" s="347"/>
-      <c r="D83" s="347"/>
-      <c r="E83" s="347"/>
-      <c r="F83" s="347"/>
+      <c r="C83" s="349"/>
+      <c r="D83" s="349"/>
+      <c r="E83" s="349"/>
+      <c r="F83" s="349"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="347" t="s">
+      <c r="B84" s="349" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="347"/>
-      <c r="D84" s="347"/>
-      <c r="E84" s="347"/>
-      <c r="F84" s="347"/>
+      <c r="C84" s="349"/>
+      <c r="D84" s="349"/>
+      <c r="E84" s="349"/>
+      <c r="F84" s="349"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4985,13 +4985,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="347" t="s">
+      <c r="B91" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C91" s="347"/>
-      <c r="D91" s="347"/>
-      <c r="E91" s="347"/>
-      <c r="F91" s="347"/>
+      <c r="C91" s="349"/>
+      <c r="D91" s="349"/>
+      <c r="E91" s="349"/>
+      <c r="F91" s="349"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5004,13 +5004,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="347" t="s">
+      <c r="B95" s="349" t="s">
         <v>346</v>
       </c>
-      <c r="C95" s="347"/>
-      <c r="D95" s="347"/>
-      <c r="E95" s="347"/>
-      <c r="F95" s="347"/>
+      <c r="C95" s="349"/>
+      <c r="D95" s="349"/>
+      <c r="E95" s="349"/>
+      <c r="F95" s="349"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5141,13 +5141,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="347" t="s">
+      <c r="B111" s="349" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="347"/>
-      <c r="D111" s="347"/>
-      <c r="E111" s="347"/>
-      <c r="F111" s="347"/>
+      <c r="C111" s="349"/>
+      <c r="D111" s="349"/>
+      <c r="E111" s="349"/>
+      <c r="F111" s="349"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5186,13 +5186,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="348" t="s">
+      <c r="B118" s="350" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="348"/>
-      <c r="D118" s="348"/>
-      <c r="E118" s="348"/>
-      <c r="F118" s="348"/>
+      <c r="C118" s="350"/>
+      <c r="D118" s="350"/>
+      <c r="E118" s="350"/>
+      <c r="F118" s="350"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
@@ -5335,13 +5335,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
@@ -5354,22 +5354,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="350" t="s">
+      <c r="B133" s="354" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="350"/>
-      <c r="D133" s="350"/>
-      <c r="E133" s="350"/>
-      <c r="F133" s="350"/>
+      <c r="C133" s="354"/>
+      <c r="D133" s="354"/>
+      <c r="E133" s="354"/>
+      <c r="F133" s="354"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="347" t="s">
+      <c r="B134" s="349" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="347"/>
-      <c r="D134" s="347"/>
-      <c r="E134" s="347"/>
-      <c r="F134" s="347"/>
+      <c r="C134" s="349"/>
+      <c r="D134" s="349"/>
+      <c r="E134" s="349"/>
+      <c r="F134" s="349"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.23700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.23700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>2.1096570925102589</v>
+        <v>1.829322250329541</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>14.205346862824813</v>
+        <v>11.250367775156876</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>16.315003955335072</v>
+        <v>13.079690025486418</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.39322700783153486</v>
+        <v>0.51355190135855366</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="C149" s="326">
         <f>Scenarios!C90</f>
-        <v>0.13700000000000001</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C150" s="238">
         <f>Scenarios!C91</f>
-        <v>2.4733714409630472</v>
+        <v>2.279132885208865</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>18.292773100270693</v>
+        <v>16.07713967014136</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>20.766144541233739</v>
+        <v>18.356272555350223</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.22768417993751855</v>
+        <v>0.3173099771252258</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5702,13 +5702,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="354" t="s">
+      <c r="B174" s="348" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="347"/>
-      <c r="D174" s="347"/>
-      <c r="E174" s="347"/>
-      <c r="F174" s="347"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
@@ -5745,13 +5745,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="348" t="s">
+      <c r="B183" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C183" s="348"/>
-      <c r="D183" s="348"/>
-      <c r="E183" s="348"/>
-      <c r="F183" s="348"/>
+      <c r="C183" s="350"/>
+      <c r="D183" s="350"/>
+      <c r="E183" s="350"/>
+      <c r="F183" s="350"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5759,22 +5759,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="353" t="s">
+      <c r="B186" s="347" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="353"/>
-      <c r="D186" s="353"/>
-      <c r="E186" s="353"/>
-      <c r="F186" s="353"/>
+      <c r="C186" s="347"/>
+      <c r="D186" s="347"/>
+      <c r="E186" s="347"/>
+      <c r="F186" s="347"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="353" t="s">
+      <c r="B187" s="347" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="353"/>
-      <c r="D187" s="353"/>
-      <c r="E187" s="353"/>
-      <c r="F187" s="353"/>
+      <c r="C187" s="347"/>
+      <c r="D187" s="347"/>
+      <c r="E187" s="347"/>
+      <c r="F187" s="347"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5798,17 +5798,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5825,6 +5814,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -13350,12 +13350,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.6696035242290754E-2</v>
+        <v>4.7069271758436948E-2</v>
       </c>
       <c r="E93" s="293"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.6696035242290754E-2</v>
+        <v>4.7069271758436948E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14549,50 +14549,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.24323199616686514</v>
+        <v>0.24517612402255057</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="290"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.29151345195483119</v>
+        <v>0.29384348842693908</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29285787753214831</v>
+        <v>0.29519865985700561</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.29674483665395007</v>
+        <v>0.29911668703573119</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.31718901171848385</v>
+        <v>0.31972427024909339</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.30103894043008123</v>
+        <v>0.30344511313334122</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.26236868044907941</v>
+        <v>0.26446576581678966</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.2266035672203244</v>
+        <v>0.22841478578602858</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.19671660493845119</v>
+        <v>0.19828894014666262</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.22177296554031115</v>
+        <v>0.22354557361301344</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.20152176007756889</v>
+        <v>0.2031325023872475</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14606,43 +14606,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16432315837836217</v>
+        <v>0.16563657616291391</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16466880722552729</v>
+        <v>0.16598498774509191</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19596805252710586</v>
+        <v>0.19753440463433852</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17773560597541396</v>
+        <v>0.1791562280480416</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14352061119621543</v>
+        <v>0.14466775640115853</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14144459756815003</v>
+        <v>0.14257514941372137</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12987278309587941</v>
+        <v>0.13091084264105074</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12242966988391865</v>
+        <v>0.1234082374051933</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11520285226957042</v>
+        <v>0.11612365659499327</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.107405608030146</v>
+        <v>0.10826408979948109</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18362,7 +18362,7 @@
       </c>
       <c r="I3" s="125">
         <f>-Market_Price</f>
-        <v>-22.7</v>
+        <v>-22.52</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18602,7 +18602,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>22.7</v>
+        <v>22.52</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.23700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19150,7 +19150,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.1096570925102589</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -19162,7 +19162,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>14.205346862824813</v>
+        <v>11.250367775156876</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -19172,7 +19172,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>16.315003955335072</v>
+        <v>13.079690025486418</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19183,7 +19183,7 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.39322700783153486</v>
+        <v>0.51355190135855366</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19200,7 +19200,7 @@
       </c>
       <c r="C86" s="117">
         <f>Market_Price</f>
-        <v>22.7</v>
+        <v>22.52</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10231184063464993</v>
+        <v>0.10536678638212904</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19230,7 +19230,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.13700000000000001</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.4733714409630472</v>
+        <v>2.279132885208865</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>18.292773100270693</v>
+        <v>16.07713967014136</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>20.766144541233739</v>
+        <v>18.356272555350223</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19272,7 +19272,7 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.22768417993751855</v>
+        <v>0.3173099771252258</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DF15A3-5F84-43DD-9465-2A321E4660CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDE0514-DEC8-4464-AD4B-E6A9279EB71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="463">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2466,6 +2466,9 @@
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -3865,29 +3868,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4215,7 +4218,7 @@
         <v>354</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4363,13 +4366,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4571,22 +4574,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4598,13 +4601,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4624,13 +4627,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4659,13 +4662,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4681,13 +4684,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4751,13 +4754,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4773,7 +4776,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4795,22 +4798,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4879,22 +4882,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4938,22 +4941,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4990,13 +4993,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5009,13 +5012,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5146,13 +5149,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5191,13 +5194,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5340,13 +5343,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5359,22 +5362,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5707,13 +5710,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5750,13 +5753,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5764,22 +5767,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5803,6 +5806,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5819,17 +5833,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDE0514-DEC8-4464-AD4B-E6A9279EB71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9319D063-5649-4CBB-AABC-DBBCCCDE7DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3868,29 +3868,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4366,13 +4366,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="347" t="s">
+      <c r="B18" s="349" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="347"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4574,22 +4574,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="347" t="s">
+      <c r="B36" s="349" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="347"/>
-      <c r="D36" s="347"/>
-      <c r="E36" s="347"/>
-      <c r="F36" s="347"/>
+      <c r="C36" s="349"/>
+      <c r="D36" s="349"/>
+      <c r="E36" s="349"/>
+      <c r="F36" s="349"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="349" t="s">
+      <c r="B37" s="352" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="349"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4601,13 +4601,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="348" t="s">
+      <c r="B40" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="348"/>
-      <c r="D40" s="348"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4627,13 +4627,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="348" t="s">
+      <c r="B43" s="350" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="348"/>
-      <c r="D43" s="348"/>
-      <c r="E43" s="348"/>
-      <c r="F43" s="348"/>
+      <c r="C43" s="350"/>
+      <c r="D43" s="350"/>
+      <c r="E43" s="350"/>
+      <c r="F43" s="350"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4662,13 +4662,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="348" t="s">
+      <c r="B47" s="350" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4684,13 +4684,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="348" t="s">
+      <c r="B50" s="350" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="348"/>
-      <c r="D50" s="348"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4754,13 +4754,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="348" t="s">
+      <c r="B58" s="350" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="348"/>
-      <c r="D58" s="348"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="C58" s="350"/>
+      <c r="D58" s="350"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4776,7 +4776,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="348" t="s">
+      <c r="B61" s="350" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4798,22 +4798,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="347" t="s">
+      <c r="B64" s="349" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="347"/>
-      <c r="D64" s="347"/>
-      <c r="E64" s="347"/>
-      <c r="F64" s="347"/>
+      <c r="C64" s="349"/>
+      <c r="D64" s="349"/>
+      <c r="E64" s="349"/>
+      <c r="F64" s="349"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="347" t="s">
+      <c r="B65" s="349" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="347"/>
-      <c r="D65" s="347"/>
-      <c r="E65" s="347"/>
-      <c r="F65" s="347"/>
+      <c r="C65" s="349"/>
+      <c r="D65" s="349"/>
+      <c r="E65" s="349"/>
+      <c r="F65" s="349"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4882,22 +4882,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="347" t="s">
+      <c r="B74" s="349" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="347"/>
-      <c r="D74" s="347"/>
-      <c r="E74" s="347"/>
-      <c r="F74" s="347"/>
+      <c r="C74" s="349"/>
+      <c r="D74" s="349"/>
+      <c r="E74" s="349"/>
+      <c r="F74" s="349"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="349" t="s">
+      <c r="B75" s="352" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="349"/>
-      <c r="D75" s="349"/>
-      <c r="E75" s="349"/>
-      <c r="F75" s="349"/>
+      <c r="C75" s="352"/>
+      <c r="D75" s="352"/>
+      <c r="E75" s="352"/>
+      <c r="F75" s="352"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4941,22 +4941,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="347" t="s">
+      <c r="B83" s="349" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="347"/>
-      <c r="D83" s="347"/>
-      <c r="E83" s="347"/>
-      <c r="F83" s="347"/>
+      <c r="C83" s="349"/>
+      <c r="D83" s="349"/>
+      <c r="E83" s="349"/>
+      <c r="F83" s="349"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="347" t="s">
+      <c r="B84" s="349" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="347"/>
-      <c r="D84" s="347"/>
-      <c r="E84" s="347"/>
-      <c r="F84" s="347"/>
+      <c r="C84" s="349"/>
+      <c r="D84" s="349"/>
+      <c r="E84" s="349"/>
+      <c r="F84" s="349"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4993,13 +4993,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="347" t="s">
+      <c r="B91" s="349" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="347"/>
-      <c r="D91" s="347"/>
-      <c r="E91" s="347"/>
-      <c r="F91" s="347"/>
+      <c r="C91" s="349"/>
+      <c r="D91" s="349"/>
+      <c r="E91" s="349"/>
+      <c r="F91" s="349"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5012,13 +5012,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="347" t="s">
+      <c r="B95" s="349" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="347"/>
-      <c r="D95" s="347"/>
-      <c r="E95" s="347"/>
-      <c r="F95" s="347"/>
+      <c r="C95" s="349"/>
+      <c r="D95" s="349"/>
+      <c r="E95" s="349"/>
+      <c r="F95" s="349"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5149,13 +5149,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="347" t="s">
+      <c r="B111" s="349" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="347"/>
-      <c r="D111" s="347"/>
-      <c r="E111" s="347"/>
-      <c r="F111" s="347"/>
+      <c r="C111" s="349"/>
+      <c r="D111" s="349"/>
+      <c r="E111" s="349"/>
+      <c r="F111" s="349"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5194,13 +5194,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="348" t="s">
+      <c r="B118" s="350" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="348"/>
-      <c r="D118" s="348"/>
-      <c r="E118" s="348"/>
-      <c r="F118" s="348"/>
+      <c r="C118" s="350"/>
+      <c r="D118" s="350"/>
+      <c r="E118" s="350"/>
+      <c r="F118" s="350"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5343,13 +5343,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5362,22 +5362,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="350" t="s">
+      <c r="B133" s="354" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="350"/>
-      <c r="D133" s="350"/>
-      <c r="E133" s="350"/>
-      <c r="F133" s="350"/>
+      <c r="C133" s="354"/>
+      <c r="D133" s="354"/>
+      <c r="E133" s="354"/>
+      <c r="F133" s="354"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="347" t="s">
+      <c r="B134" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="347"/>
-      <c r="D134" s="347"/>
-      <c r="E134" s="347"/>
-      <c r="F134" s="347"/>
+      <c r="C134" s="349"/>
+      <c r="D134" s="349"/>
+      <c r="E134" s="349"/>
+      <c r="F134" s="349"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5710,13 +5710,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="354" t="s">
+      <c r="B174" s="348" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="347"/>
-      <c r="D174" s="347"/>
-      <c r="E174" s="347"/>
-      <c r="F174" s="347"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5753,13 +5753,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="348" t="s">
+      <c r="B183" s="350" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="348"/>
-      <c r="D183" s="348"/>
-      <c r="E183" s="348"/>
-      <c r="F183" s="348"/>
+      <c r="C183" s="350"/>
+      <c r="D183" s="350"/>
+      <c r="E183" s="350"/>
+      <c r="F183" s="350"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5767,22 +5767,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="353" t="s">
+      <c r="B186" s="347" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="353"/>
-      <c r="D186" s="353"/>
-      <c r="E186" s="353"/>
-      <c r="F186" s="353"/>
+      <c r="C186" s="347"/>
+      <c r="D186" s="347"/>
+      <c r="E186" s="347"/>
+      <c r="F186" s="347"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="353" t="s">
+      <c r="B187" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="353"/>
-      <c r="D187" s="353"/>
-      <c r="E187" s="353"/>
-      <c r="F187" s="353"/>
+      <c r="C187" s="347"/>
+      <c r="D187" s="347"/>
+      <c r="E187" s="347"/>
+      <c r="F187" s="347"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5806,17 +5806,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5833,6 +5822,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -14381,51 +14381,51 @@
         <v>223</v>
       </c>
       <c r="C120" s="102">
-        <f>C8/C105</f>
-        <v>6.7515395401354728E-3</v>
+        <f>C13/C105</f>
+        <v>0.17249144202566888</v>
       </c>
       <c r="D120" s="103"/>
       <c r="E120" s="273"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
-        <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
-        <v>-8.0683876988980668E-4</v>
+        <f>IF(G$4="","",G13/G105)</f>
+        <v>0.16493306371564362</v>
       </c>
       <c r="H120" s="102">
-        <f t="shared" si="48"/>
-        <v>-1.4670943731669057E-3</v>
+        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
+        <v>0.17991157816022652</v>
       </c>
       <c r="I120" s="102">
         <f t="shared" si="48"/>
-        <v>1.2556483709187136E-2</v>
+        <v>0.20438717651439725</v>
       </c>
       <c r="J120" s="102">
         <f t="shared" si="48"/>
-        <v>2.3808220677576486E-2</v>
+        <v>0.23363022794246852</v>
       </c>
       <c r="K120" s="102">
         <f t="shared" si="48"/>
-        <v>1.3538667387960685E-2</v>
+        <v>0.24323506769333694</v>
       </c>
       <c r="L120" s="102">
         <f t="shared" si="48"/>
-        <v>5.3441086360096937E-2</v>
+        <v>0.2408105492202339</v>
       </c>
       <c r="M120" s="102">
         <f t="shared" si="48"/>
-        <v>3.9487159954632402E-2</v>
+        <v>0.24189985272459499</v>
       </c>
       <c r="N120" s="102">
         <f t="shared" si="48"/>
-        <v>2.80755620316403E-2</v>
+        <v>0.2373022481265612</v>
       </c>
       <c r="O120" s="102">
         <f t="shared" si="48"/>
-        <v>6.5997009113738323E-3</v>
+        <v>0.32351795942552414</v>
       </c>
       <c r="P120" s="102">
         <f t="shared" si="48"/>
-        <v>-3.7066328057798768E-2</v>
+        <v>0.34050986681454548</v>
       </c>
       <c r="Q120" s="102" t="str">
         <f t="shared" si="48"/>

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9319D063-5649-4CBB-AABC-DBBCCCDE7DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383CC823-FBB2-480A-93E2-219913D2A0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3868,29 +3868,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4308,7 +4308,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>22.52</v>
+        <v>22.71</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>467837.48973283998</v>
+        <v>471784.60887356999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4366,13 +4366,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="E26" s="304">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10536678638212904</v>
+        <v>0.10214309565132695</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4499,7 +4499,7 @@
         <v>426</v>
       </c>
       <c r="F29" s="305">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4574,22 +4574,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4601,13 +4601,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4627,13 +4627,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4662,13 +4662,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4684,13 +4684,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4754,13 +4754,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4776,7 +4776,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4798,22 +4798,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.24517612402255057</v>
+        <v>0.24312489268990922</v>
       </c>
       <c r="F69" s="317"/>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.7069271758436948E-2</v>
+        <v>4.6675473359753417E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>454</v>
@@ -4882,22 +4882,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4941,22 +4941,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4993,13 +4993,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5012,13 +5012,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5149,13 +5149,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5194,13 +5194,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5343,13 +5343,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5362,22 +5362,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="C137" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="C141" s="299">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="C142" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5710,13 +5710,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5753,13 +5753,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5767,22 +5767,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5806,6 +5806,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5822,17 +5833,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.7069271758436948E-2</v>
+        <v>4.6675473359753417E-2</v>
       </c>
       <c r="E93" s="270"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.7069271758436948E-2</v>
+        <v>4.6675473359753417E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14560,50 +14560,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.24517612402255057</v>
+        <v>0.24312489268990922</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="267"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.29384348842693908</v>
+        <v>0.29138508847972994</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29519865985700561</v>
+        <v>0.29272892205987522</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.29911668703573119</v>
+        <v>0.29661416961887566</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.31972427024909339</v>
+        <v>0.31704934240464916</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.30344511313334122</v>
+        <v>0.3009063825523049</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.26446576581678966</v>
+        <v>0.26225315042686492</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.22841478578602858</v>
+        <v>0.22650378581688083</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.19828894014666262</v>
+        <v>0.19662998380021321</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.22354557361301344</v>
+        <v>0.22167531121818856</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.2031325023872475</v>
+        <v>0.20143302306300367</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14617,43 +14617,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16563657616291391</v>
+        <v>0.16425080119721799</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16598498774509191</v>
+        <v>0.1645962978432175</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19753440463433852</v>
+        <v>0.19588176100243518</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1791562280480416</v>
+        <v>0.17765734282879334</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14466775640115853</v>
+        <v>0.14345741409749405</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14257514941372137</v>
+        <v>0.14138231461017195</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13091084264105074</v>
+        <v>0.12981559560882705</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1234082374051933</v>
+        <v>0.12237575985754967</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11612365659499327</v>
+        <v>0.11515212446143762</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10826408979948109</v>
+        <v>0.10735831361886015</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18373,7 +18373,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.52</v>
+        <v>-22.71</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.52</v>
+        <v>22.71</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19161,7 +19161,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19211,7 +19211,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.52</v>
+        <v>22.71</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19224,7 +19224,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10536678638212904</v>
+        <v>0.10214309565132695</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCCADE71-822E-4E0C-AC98-AC283B4822A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02AFE0CA-E061-479F-A697-575DDA303FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3149,7 +3149,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="359">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3875,6 +3875,7 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4379,13 +4380,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="350" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="350"/>
+      <c r="D18" s="350"/>
+      <c r="E18" s="350"/>
+      <c r="F18" s="350"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4587,22 +4588,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="350" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="350"/>
+      <c r="D36" s="350"/>
+      <c r="E36" s="350"/>
+      <c r="F36" s="350"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="353" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="353"/>
+      <c r="D37" s="353"/>
+      <c r="E37" s="353"/>
+      <c r="F37" s="353"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4614,13 +4615,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="351" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="351"/>
+      <c r="D40" s="351"/>
+      <c r="E40" s="351"/>
+      <c r="F40" s="351"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4640,13 +4641,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="351" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="351"/>
+      <c r="D43" s="351"/>
+      <c r="E43" s="351"/>
+      <c r="F43" s="351"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4675,13 +4676,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="351" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="351"/>
+      <c r="D47" s="351"/>
+      <c r="E47" s="351"/>
+      <c r="F47" s="351"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4697,13 +4698,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="351" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="351"/>
+      <c r="D50" s="351"/>
+      <c r="E50" s="351"/>
+      <c r="F50" s="351"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4767,13 +4768,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="351" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="351"/>
+      <c r="D58" s="351"/>
+      <c r="E58" s="351"/>
+      <c r="F58" s="351"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4789,13 +4790,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="351" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="351"/>
-      <c r="D61" s="351"/>
-      <c r="E61" s="351"/>
-      <c r="F61" s="351"/>
+      <c r="C61" s="352"/>
+      <c r="D61" s="352"/>
+      <c r="E61" s="352"/>
+      <c r="F61" s="352"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4811,22 +4812,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="350" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="350"/>
+      <c r="D64" s="350"/>
+      <c r="E64" s="350"/>
+      <c r="F64" s="350"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="350" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="350"/>
+      <c r="D65" s="350"/>
+      <c r="E65" s="350"/>
+      <c r="F65" s="350"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4923,11 +4924,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="343">
+      <c r="C75" s="345">
         <f>Normalized_FCF!C118</f>
         <v>2.0567862383133143E-2</v>
       </c>
-      <c r="D75" s="343">
+      <c r="D75" s="345">
         <f>Normalized_FCF!G118</f>
         <v>1.9984681998245511E-2</v>
       </c>
@@ -4937,11 +4938,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="343">
+      <c r="C76" s="345">
         <f>Normalized_FCF!C119</f>
         <v>11.758917470801054</v>
       </c>
-      <c r="D76" s="343">
+      <c r="D76" s="345">
         <f>Normalized_FCF!G119</f>
         <v>11.758917470801054</v>
       </c>
@@ -4961,22 +4962,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="349" t="s">
+      <c r="B80" s="350" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="349"/>
-      <c r="D80" s="349"/>
-      <c r="E80" s="349"/>
-      <c r="F80" s="349"/>
+      <c r="C80" s="350"/>
+      <c r="D80" s="350"/>
+      <c r="E80" s="350"/>
+      <c r="F80" s="350"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="352" t="s">
+      <c r="B81" s="353" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="352"/>
-      <c r="D81" s="352"/>
-      <c r="E81" s="352"/>
-      <c r="F81" s="352"/>
+      <c r="C81" s="353"/>
+      <c r="D81" s="353"/>
+      <c r="E81" s="353"/>
+      <c r="F81" s="353"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5020,22 +5021,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="349" t="s">
+      <c r="B89" s="350" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="349"/>
-      <c r="D89" s="349"/>
-      <c r="E89" s="349"/>
-      <c r="F89" s="349"/>
+      <c r="C89" s="350"/>
+      <c r="D89" s="350"/>
+      <c r="E89" s="350"/>
+      <c r="F89" s="350"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="349" t="s">
+      <c r="B90" s="350" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="349"/>
-      <c r="D90" s="349"/>
-      <c r="E90" s="349"/>
-      <c r="F90" s="349"/>
+      <c r="C90" s="350"/>
+      <c r="D90" s="350"/>
+      <c r="E90" s="350"/>
+      <c r="F90" s="350"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5072,13 +5073,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="349" t="s">
+      <c r="B97" s="350" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="349"/>
-      <c r="D97" s="349"/>
-      <c r="E97" s="349"/>
-      <c r="F97" s="349"/>
+      <c r="C97" s="350"/>
+      <c r="D97" s="350"/>
+      <c r="E97" s="350"/>
+      <c r="F97" s="350"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5091,13 +5092,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="349" t="s">
+      <c r="B101" s="350" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="349"/>
-      <c r="D101" s="349"/>
-      <c r="E101" s="349"/>
-      <c r="F101" s="349"/>
+      <c r="C101" s="350"/>
+      <c r="D101" s="350"/>
+      <c r="E101" s="350"/>
+      <c r="F101" s="350"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5129,7 +5130,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="345" t="str">
+      <c r="C104" s="346" t="str">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>nm</v>
       </c>
@@ -5138,7 +5139,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="346" t="str">
+      <c r="C105" s="347" t="str">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>nm</v>
       </c>
@@ -5219,13 +5220,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="349" t="s">
+      <c r="B116" s="350" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="349"/>
-      <c r="D116" s="349"/>
-      <c r="E116" s="349"/>
-      <c r="F116" s="349"/>
+      <c r="C116" s="350"/>
+      <c r="D116" s="350"/>
+      <c r="E116" s="350"/>
+      <c r="F116" s="350"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5264,13 +5265,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="350" t="s">
+      <c r="B123" s="351" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="350"/>
-      <c r="D123" s="350"/>
-      <c r="E123" s="350"/>
-      <c r="F123" s="350"/>
+      <c r="C123" s="351"/>
+      <c r="D123" s="351"/>
+      <c r="E123" s="351"/>
+      <c r="F123" s="351"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5413,13 +5414,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="354" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="354"/>
+      <c r="D134" s="354"/>
+      <c r="E134" s="354"/>
+      <c r="F134" s="354"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5432,22 +5433,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="354" t="s">
+      <c r="B138" s="355" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="354"/>
-      <c r="D138" s="354"/>
-      <c r="E138" s="354"/>
-      <c r="F138" s="354"/>
+      <c r="C138" s="355"/>
+      <c r="D138" s="355"/>
+      <c r="E138" s="355"/>
+      <c r="F138" s="355"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="349" t="s">
+      <c r="B139" s="350" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="349"/>
-      <c r="D139" s="349"/>
-      <c r="E139" s="349"/>
-      <c r="F139" s="349"/>
+      <c r="C139" s="350"/>
+      <c r="D139" s="350"/>
+      <c r="E139" s="350"/>
+      <c r="F139" s="350"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5780,13 +5781,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="348" t="s">
+      <c r="B179" s="349" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="349"/>
-      <c r="D179" s="349"/>
-      <c r="E179" s="349"/>
-      <c r="F179" s="349"/>
+      <c r="C179" s="350"/>
+      <c r="D179" s="350"/>
+      <c r="E179" s="350"/>
+      <c r="F179" s="350"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5794,13 +5795,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="351" t="s">
+      <c r="B182" s="352" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="351"/>
-      <c r="D182" s="351"/>
-      <c r="E182" s="351"/>
-      <c r="F182" s="351"/>
+      <c r="C182" s="352"/>
+      <c r="D182" s="352"/>
+      <c r="E182" s="352"/>
+      <c r="F182" s="352"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5823,13 +5824,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="350" t="s">
+      <c r="B188" s="351" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="350"/>
-      <c r="D188" s="350"/>
-      <c r="E188" s="350"/>
-      <c r="F188" s="350"/>
+      <c r="C188" s="351"/>
+      <c r="D188" s="351"/>
+      <c r="E188" s="351"/>
+      <c r="F188" s="351"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5837,22 +5838,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="347" t="s">
+      <c r="B191" s="348" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="347"/>
-      <c r="D191" s="347"/>
-      <c r="E191" s="347"/>
-      <c r="F191" s="347"/>
+      <c r="C191" s="348"/>
+      <c r="D191" s="348"/>
+      <c r="E191" s="348"/>
+      <c r="F191" s="348"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="347" t="s">
+      <c r="B192" s="348" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="347"/>
-      <c r="D192" s="347"/>
-      <c r="E192" s="347"/>
-      <c r="F192" s="347"/>
+      <c r="C192" s="348"/>
+      <c r="D192" s="348"/>
+      <c r="E192" s="348"/>
+      <c r="F192" s="348"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -14291,47 +14292,47 @@
       </c>
       <c r="E117" s="268"/>
       <c r="G117" s="23">
-        <f>IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
+        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
         <v>0.7018481216398329</v>
       </c>
       <c r="H117" s="23">
-        <f>IF(H4="","",IF(valuation_method="DDM",H13/(H4+H12),H81))</f>
+        <f t="shared" si="45"/>
         <v>0.69692871393492939</v>
       </c>
       <c r="I117" s="23">
-        <f>IF(I4="","",IF(valuation_method="DDM",I13/(I4+I12),I81))</f>
+        <f t="shared" si="45"/>
         <v>0.70324767374236696</v>
       </c>
       <c r="J117" s="23">
-        <f>IF(J4="","",IF(valuation_method="DDM",J13/(J4+J12),J81))</f>
+        <f t="shared" si="45"/>
         <v>0.74058229732135927</v>
       </c>
       <c r="K117" s="23">
-        <f>IF(K4="","",IF(valuation_method="DDM",K13/(K4+K12),K81))</f>
+        <f t="shared" si="45"/>
         <v>0.75589775728546493</v>
       </c>
       <c r="L117" s="23">
-        <f>IF(L4="","",IF(valuation_method="DDM",L13/(L4+L12),L81))</f>
+        <f t="shared" si="45"/>
         <v>0.73717920156834793</v>
       </c>
       <c r="M117" s="23">
-        <f>IF(M4="","",IF(valuation_method="DDM",M13/(M4+M12),M81))</f>
+        <f t="shared" si="45"/>
         <v>0.7287017382823705</v>
       </c>
       <c r="N117" s="23">
-        <f>IF(N4="","",IF(valuation_method="DDM",N13/(N4+N12),N81))</f>
+        <f t="shared" si="45"/>
         <v>0.72172661870503596</v>
       </c>
       <c r="O117" s="23">
-        <f>IF(O4="","",IF(valuation_method="DDM",O13/(O4+O12),O81))</f>
+        <f t="shared" si="45"/>
         <v>0.75735337829358029</v>
       </c>
       <c r="P117" s="23">
-        <f>IF(P4="","",IF(valuation_method="DDM",P13/(P4+P12),P81))</f>
+        <f t="shared" si="45"/>
         <v>0.76432355208532243</v>
       </c>
       <c r="Q117" s="23" t="str">
-        <f>IF(Q4="","",IF(valuation_method="DDM",Q13/(Q4+Q12),Q81))</f>
+        <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
@@ -14345,47 +14346,47 @@
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="42">
-        <f>IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
+        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
         <v>1.9984681998245511E-2</v>
       </c>
       <c r="H118" s="42">
-        <f>IF(H4="","",IF(valuation_method="DDM",(H4+H12)/H101,H4/H101))</f>
+        <f t="shared" si="46"/>
         <v>2.0526216622699447E-2</v>
       </c>
       <c r="I118" s="42">
-        <f>IF(I4="","",IF(valuation_method="DDM",(I4+I12)/I101,I4/I101))</f>
+        <f t="shared" si="46"/>
         <v>2.3751355799725704E-2</v>
       </c>
       <c r="J118" s="42">
-        <f>IF(J4="","",IF(valuation_method="DDM",(J4+J12)/J101,J4/J101))</f>
+        <f t="shared" si="46"/>
         <v>2.5459536088705551E-2</v>
       </c>
       <c r="K118" s="42">
-        <f>IF(K4="","",IF(valuation_method="DDM",(K4+K12)/K101,K4/K101))</f>
+        <f t="shared" si="46"/>
         <v>2.546883709146187E-2</v>
       </c>
       <c r="L118" s="42">
-        <f>IF(L4="","",IF(valuation_method="DDM",(L4+L12)/L101,L4/L101))</f>
+        <f t="shared" si="46"/>
         <v>2.5127346154971093E-2</v>
       </c>
       <c r="M118" s="42">
-        <f>IF(M4="","",IF(valuation_method="DDM",(M4+M12)/M101,M4/M101))</f>
+        <f t="shared" si="46"/>
         <v>2.3374108659009244E-2</v>
       </c>
       <c r="N118" s="42">
-        <f>IF(N4="","",IF(valuation_method="DDM",(N4+N12)/N101,N4/N101))</f>
+        <f t="shared" si="46"/>
         <v>2.1661745762167745E-2</v>
       </c>
       <c r="O118" s="42">
-        <f>IF(O4="","",IF(valuation_method="DDM",(O4+O12)/O101,O4/O101))</f>
+        <f t="shared" si="46"/>
         <v>2.4876045347479704E-2</v>
       </c>
       <c r="P118" s="42">
-        <f>IF(P4="","",IF(valuation_method="DDM",(P4+P12)/P101,P4/P101))</f>
+        <f t="shared" si="46"/>
         <v>2.6683563319041006E-2</v>
       </c>
       <c r="Q118" s="42" t="str">
-        <f>IF(Q4="","",IF(valuation_method="DDM",(Q4+Q12)/Q101,Q4/Q101))</f>
+        <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
@@ -14401,47 +14402,47 @@
       <c r="E119" s="272"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="45">IF(G$4="","",G101/G105)</f>
+        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
         <v>11.758917470801054</v>
       </c>
       <c r="H119" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>12.576559422274331</v>
       </c>
       <c r="I119" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>12.236492107466281</v>
       </c>
       <c r="J119" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>12.39096756724058</v>
       </c>
       <c r="K119" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>12.634382357319026</v>
       </c>
       <c r="L119" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>13.000372963256751</v>
       </c>
       <c r="M119" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>14.202040272205576</v>
       </c>
       <c r="N119" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>15.178738361971085</v>
       </c>
       <c r="O119" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>17.171905420275952</v>
       </c>
       <c r="P119" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>16.695853826836853</v>
       </c>
       <c r="Q119" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
@@ -14462,43 +14463,43 @@
         <v>0.16493306371564362</v>
       </c>
       <c r="H120" s="102">
-        <f t="shared" ref="H120:Q120" si="46">IF(H$4="","",H13/H105)</f>
+        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
         <v>0.17991157816022652</v>
       </c>
       <c r="I120" s="102">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.20438717651439725</v>
       </c>
       <c r="J120" s="102">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.23363022794246852</v>
       </c>
       <c r="K120" s="102">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.24323506769333694</v>
       </c>
       <c r="L120" s="102">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.2408105492202339</v>
       </c>
       <c r="M120" s="102">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.24189985272459499</v>
       </c>
       <c r="N120" s="102">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.2373022481265612</v>
       </c>
       <c r="O120" s="102">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.32351795942552414</v>
       </c>
       <c r="P120" s="102">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.34050986681454548</v>
       </c>
       <c r="Q120" s="102" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
@@ -14579,47 +14580,47 @@
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
-        <f t="shared" ref="G124:Q124" si="47">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
         <v>6.6173553593746677</v>
       </c>
       <c r="H124" s="177">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>6.6478738199797665</v>
       </c>
       <c r="I124" s="177">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>6.7361077920446659</v>
       </c>
       <c r="J124" s="177">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>7.2001905660095833</v>
       </c>
       <c r="K124" s="177">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>6.8335839477628442</v>
       </c>
       <c r="L124" s="177">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>5.9557690461941029</v>
       </c>
       <c r="M124" s="177">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>5.1439009759013636</v>
       </c>
       <c r="N124" s="177">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>4.4654669321028422</v>
       </c>
       <c r="O124" s="177">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>5.0342463177650627</v>
       </c>
       <c r="P124" s="177">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>4.5745439537608137</v>
       </c>
       <c r="Q124" s="177" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
@@ -14636,47 +14637,47 @@
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
-        <f t="shared" ref="G125" si="48">IF(G$4="","",G124/Market_Price)</f>
+        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
         <v>0.29138508847972994</v>
       </c>
       <c r="H125" s="77">
-        <f t="shared" ref="H125" si="49">IF(H$4="","",H124/Market_Price)</f>
+        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
         <v>0.29272892205987522</v>
       </c>
       <c r="I125" s="77">
-        <f t="shared" ref="I125" si="50">IF(I$4="","",I124/Market_Price)</f>
+        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
         <v>0.29661416961887566</v>
       </c>
       <c r="J125" s="77">
-        <f t="shared" ref="J125" si="51">IF(J$4="","",J124/Market_Price)</f>
+        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
         <v>0.31704934240464916</v>
       </c>
       <c r="K125" s="77">
-        <f t="shared" ref="K125" si="52">IF(K$4="","",K124/Market_Price)</f>
+        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
         <v>0.3009063825523049</v>
       </c>
       <c r="L125" s="77">
-        <f t="shared" ref="L125" si="53">IF(L$4="","",L124/Market_Price)</f>
+        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
         <v>0.26225315042686492</v>
       </c>
       <c r="M125" s="77">
-        <f t="shared" ref="M125" si="54">IF(M$4="","",M124/Market_Price)</f>
+        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
         <v>0.22650378581688083</v>
       </c>
       <c r="N125" s="77">
-        <f t="shared" ref="N125" si="55">IF(N$4="","",N124/Market_Price)</f>
+        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
         <v>0.19662998380021321</v>
       </c>
       <c r="O125" s="77">
-        <f t="shared" ref="O125" si="56">IF(O$4="","",O124/Market_Price)</f>
+        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
         <v>0.22167531121818856</v>
       </c>
       <c r="P125" s="77">
-        <f t="shared" ref="P125" si="57">IF(P$4="","",P124/Market_Price)</f>
+        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
         <v>0.20143302306300367</v>
       </c>
       <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="58">IF(Q$4="","",Q124/Market_Price)</f>
+        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
@@ -15511,10 +15512,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="355" t="s">
+      <c r="E6" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="355"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -15529,8 +15530,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="355"/>
-      <c r="F7" s="355"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -15545,8 +15546,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="355"/>
-      <c r="F8" s="355"/>
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -15561,8 +15562,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="355"/>
-      <c r="F9" s="355"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -17041,8 +17042,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="355"/>
-      <c r="F6" s="355"/>
+      <c r="E6" s="356"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18507,11 +18508,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="357" t="str">
+      <c r="E7" s="358" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 兴业银行(601166.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="357"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18532,8 +18533,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="357"/>
-      <c r="F8" s="357"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18554,8 +18555,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="357"/>
-      <c r="F9" s="357"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18565,8 +18566,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="357"/>
-      <c r="F10" s="357"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18579,8 +18580,8 @@
       <c r="B11" s="159" t="s">
         <v>452</v>
       </c>
-      <c r="E11" s="357"/>
-      <c r="F11" s="357"/>
+      <c r="E11" s="358"/>
+      <c r="F11" s="358"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18598,8 +18599,8 @@
         <v>-5.5054441259114184E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="357"/>
-      <c r="F12" s="357"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="358"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18616,8 +18617,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.3520092995664894</v>
       </c>
-      <c r="E13" s="357"/>
-      <c r="F13" s="357"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18634,8 +18635,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.7745066708446342E-2</v>
       </c>
-      <c r="E14" s="357"/>
-      <c r="F14" s="357"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="358"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18661,21 +18662,21 @@
       <c r="C18" s="150">
         <v>30</v>
       </c>
-      <c r="E18" s="357" t="s">
+      <c r="E18" s="358" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="358"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="358"/>
-      <c r="F19" s="358"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="358"/>
-      <c r="F20" s="358"/>
+      <c r="E20" s="359"/>
+      <c r="F20" s="359"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18689,8 +18690,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="358"/>
-      <c r="F21" s="358"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="359"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18704,8 +18705,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="358"/>
-      <c r="F22" s="358"/>
+      <c r="E22" s="359"/>
+      <c r="F22" s="359"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18725,8 +18726,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="356"/>
-      <c r="F25" s="356"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18736,8 +18737,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="356"/>
-      <c r="F26" s="356"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18751,8 +18752,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="356"/>
-      <c r="F27" s="356"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18762,8 +18763,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="356"/>
-      <c r="F28" s="356"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18783,8 +18784,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="356"/>
-      <c r="F31" s="356"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18794,8 +18795,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="356"/>
-      <c r="F32" s="356"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18809,8 +18810,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="356"/>
-      <c r="F33" s="356"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18820,8 +18821,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="356"/>
-      <c r="F34" s="356"/>
+      <c r="E34" s="357"/>
+      <c r="F34" s="357"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18841,8 +18842,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="356"/>
-      <c r="F37" s="356"/>
+      <c r="E37" s="357"/>
+      <c r="F37" s="357"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18852,8 +18853,8 @@
         <v>0.04</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="356"/>
-      <c r="F38" s="356"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="357"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18867,8 +18868,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="356"/>
-      <c r="F39" s="356"/>
+      <c r="E39" s="357"/>
+      <c r="F39" s="357"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18879,8 +18880,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="356"/>
-      <c r="F40" s="356"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18942,8 +18943,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="356"/>
-      <c r="F49" s="356"/>
+      <c r="E49" s="357"/>
+      <c r="F49" s="357"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18953,8 +18954,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="356"/>
-      <c r="F50" s="356"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -18968,8 +18969,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="356"/>
-      <c r="F51" s="356"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="357"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -18979,8 +18980,8 @@
         <v>0.01</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="356"/>
-      <c r="F52" s="356"/>
+      <c r="E52" s="357"/>
+      <c r="F52" s="357"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19000,8 +19001,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="356"/>
-      <c r="F55" s="356"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="357"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19011,8 +19012,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="356"/>
-      <c r="F56" s="356"/>
+      <c r="E56" s="357"/>
+      <c r="F56" s="357"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19026,8 +19027,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="356"/>
-      <c r="F57" s="356"/>
+      <c r="E57" s="357"/>
+      <c r="F57" s="357"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19037,8 +19038,8 @@
         <v>0.01</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="356"/>
-      <c r="F58" s="356"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02AFE0CA-E061-479F-A697-575DDA303FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856DA910-7405-48AF-A214-949533DC2750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3882,29 +3882,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4322,7 +4322,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>22.71</v>
+        <v>22.9</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>471784.60887356999</v>
+        <v>475731.7280143</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4380,13 +4380,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10214309565132695</v>
+        <v>9.8956167773784021E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4513,7 +4513,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4588,22 +4588,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4615,13 +4615,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4641,13 +4641,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4676,13 +4676,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4698,13 +4698,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4768,13 +4768,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4790,7 +4790,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4812,22 +4812,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.24312489268990922</v>
+        <v>0.24110769925711084</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.6675473359753417E-2</v>
+        <v>4.6288209606986902E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>453</v>
@@ -4962,22 +4962,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5021,22 +5021,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5073,13 +5073,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5092,13 +5092,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5220,13 +5220,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5265,13 +5265,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5414,13 +5414,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5433,22 +5433,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5781,13 +5781,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5824,13 +5824,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5838,22 +5838,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5877,6 +5877,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5893,17 +5904,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.6675473359753417E-2</v>
+        <v>4.6288209606986902E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.6675473359753417E-2</v>
+        <v>4.6288209606986902E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14631,50 +14631,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.24312489268990922</v>
+        <v>0.24110769925711084</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.29138508847972994</v>
+        <v>0.28896748294212526</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29272892205987522</v>
+        <v>0.29030016681134352</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.29661416961887566</v>
+        <v>0.29415317869190682</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.31704934240464916</v>
+        <v>0.31441880200915212</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.3009063825523049</v>
+        <v>0.29840977937829016</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.26225315042686492</v>
+        <v>0.26007725092550671</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.22650378581688083</v>
+        <v>0.2246244967642517</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.19662998380021321</v>
+        <v>0.19499855598702368</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.22167531121818856</v>
+        <v>0.21983608374519925</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.20143302306300367</v>
+        <v>0.1997617447057124</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14688,43 +14688,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16425080119721799</v>
+        <v>0.16288802162396598</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1645962978432175</v>
+        <v>0.16323065170390696</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19588176100243518</v>
+        <v>0.19425654115132329</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17765734282879334</v>
+        <v>0.17618332994069419</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14345741409749405</v>
+        <v>0.14226715607659782</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14138231461017195</v>
+        <v>0.14020927357192162</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12981559560882705</v>
+        <v>0.1287385229815049</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12237575985754967</v>
+        <v>0.12136041512510712</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11515212446143762</v>
+        <v>0.11419671382180124</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10735831361886015</v>
+        <v>0.10646756778534122</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18444,7 +18444,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.71</v>
+        <v>-22.9</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.71</v>
+        <v>22.9</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19223,7 +19223,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19232,7 +19232,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19282,7 +19282,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.71</v>
+        <v>22.9</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10214309565132695</v>
+        <v>9.8956167773784021E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856DA910-7405-48AF-A214-949533DC2750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0733131-E52E-417C-8CFE-86F2FDD44A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2483,7 +2483,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2501,6 +2501,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3149,7 +3150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3821,36 +3822,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3865,10 +3843,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3880,6 +3854,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4380,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4513,7 +4529,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4588,22 +4604,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4615,19 +4631,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>6033.25</v>
       </c>
@@ -4641,19 +4657,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
@@ -4666,7 +4682,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
       </c>
@@ -4676,19 +4692,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4698,19 +4714,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>343835</v>
       </c>
@@ -4725,7 +4741,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-195728</v>
       </c>
@@ -4740,7 +4756,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>148107</v>
       </c>
@@ -4758,7 +4774,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>-902.60509486250271</v>
       </c>
@@ -4768,19 +4784,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-38535.0625</v>
       </c>
@@ -4790,19 +4806,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4812,28 +4828,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>137471</v>
       </c>
@@ -4846,7 +4862,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>114702.58240513749</v>
       </c>
@@ -4885,10 +4901,10 @@
       <c r="B72" s="210" t="s">
         <v>455</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>457</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>458</v>
       </c>
     </row>
@@ -4910,11 +4926,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>0.71319953730480046</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>0.7018481216398329</v>
       </c>
@@ -4924,11 +4940,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>2.0567862383133143E-2</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>1.9984681998245511E-2</v>
       </c>
@@ -4938,11 +4954,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>11.758917470801054</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>11.758917470801054</v>
       </c>
@@ -4962,22 +4978,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5021,22 +5037,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5073,13 +5089,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5092,19 +5108,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>9516669</v>
       </c>
@@ -5130,7 +5146,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346" t="str">
+      <c r="C104" s="331" t="str">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>nm</v>
       </c>
@@ -5139,7 +5155,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347" t="str">
+      <c r="C105" s="332" t="str">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>nm</v>
       </c>
@@ -5153,7 +5169,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>6736706</v>
       </c>
@@ -5166,7 +5182,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>0</v>
       </c>
@@ -5197,7 +5213,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>2145886.1</v>
       </c>
@@ -5220,13 +5236,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5265,13 +5281,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5414,13 +5430,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5433,22 +5449,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5470,7 +5486,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5505,7 +5521,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5515,7 +5531,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.829322250329541</v>
+        <v>1.8293222503295408</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5781,13 +5797,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5795,13 +5811,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5824,13 +5840,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5838,22 +5854,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6019,409 +6035,409 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>61890</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>62009</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>74823</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>73350</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>57536</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>76564</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>61222</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>50549</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>39074</v>
       </c>
-      <c r="L4" s="334">
+      <c r="L4" s="321">
         <v>21559</v>
       </c>
-      <c r="M4" s="334"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
-        <v>0</v>
-      </c>
-      <c r="D5" s="334">
-        <v>0</v>
-      </c>
-      <c r="E5" s="334">
-        <v>0</v>
-      </c>
-      <c r="F5" s="334">
-        <v>0</v>
-      </c>
-      <c r="G5" s="334">
-        <v>0</v>
-      </c>
-      <c r="H5" s="334">
-        <v>0</v>
-      </c>
-      <c r="I5" s="334">
-        <v>0</v>
-      </c>
-      <c r="J5" s="334">
-        <v>0</v>
-      </c>
-      <c r="K5" s="334">
-        <v>0</v>
-      </c>
-      <c r="L5" s="334">
-        <v>0</v>
-      </c>
-      <c r="M5" s="334"/>
+      <c r="C5" s="321">
+        <v>0</v>
+      </c>
+      <c r="D5" s="321">
+        <v>0</v>
+      </c>
+      <c r="E5" s="321">
+        <v>0</v>
+      </c>
+      <c r="F5" s="321">
+        <v>0</v>
+      </c>
+      <c r="G5" s="321">
+        <v>0</v>
+      </c>
+      <c r="H5" s="321">
+        <v>0</v>
+      </c>
+      <c r="I5" s="321">
+        <v>0</v>
+      </c>
+      <c r="J5" s="321">
+        <v>0</v>
+      </c>
+      <c r="K5" s="321">
+        <v>0</v>
+      </c>
+      <c r="L5" s="321">
+        <v>0</v>
+      </c>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <v>62611</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <v>63194</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <v>65314</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <v>56820</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <v>49077</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <v>47190</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <v>42561</v>
       </c>
-      <c r="J6" s="334">
+      <c r="J6" s="321">
         <v>38680</v>
       </c>
-      <c r="K6" s="334">
+      <c r="K6" s="321">
         <v>36735</v>
       </c>
-      <c r="L6" s="334">
+      <c r="L6" s="321">
         <v>33323</v>
       </c>
-      <c r="M6" s="334"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
-        <v>0</v>
-      </c>
-      <c r="D7" s="335">
-        <v>0</v>
-      </c>
-      <c r="E7" s="335">
-        <v>0</v>
-      </c>
-      <c r="F7" s="335">
-        <v>0</v>
-      </c>
-      <c r="G7" s="335">
-        <v>0</v>
-      </c>
-      <c r="H7" s="335">
-        <v>0</v>
-      </c>
-      <c r="I7" s="335">
-        <v>0</v>
-      </c>
-      <c r="J7" s="335">
-        <v>0</v>
-      </c>
-      <c r="K7" s="335">
-        <v>0</v>
-      </c>
-      <c r="L7" s="335">
-        <v>0</v>
-      </c>
-      <c r="M7" s="335"/>
+      <c r="C7" s="322">
+        <v>0</v>
+      </c>
+      <c r="D7" s="322">
+        <v>0</v>
+      </c>
+      <c r="E7" s="322">
+        <v>0</v>
+      </c>
+      <c r="F7" s="322">
+        <v>0</v>
+      </c>
+      <c r="G7" s="322">
+        <v>0</v>
+      </c>
+      <c r="H7" s="322">
+        <v>0</v>
+      </c>
+      <c r="I7" s="322">
+        <v>0</v>
+      </c>
+      <c r="J7" s="322">
+        <v>0</v>
+      </c>
+      <c r="K7" s="322">
+        <v>0</v>
+      </c>
+      <c r="L7" s="322">
+        <v>0</v>
+      </c>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334">
-        <v>0</v>
-      </c>
-      <c r="D8" s="334">
-        <v>0</v>
-      </c>
-      <c r="E8" s="334">
-        <v>0</v>
-      </c>
-      <c r="F8" s="334">
-        <v>0</v>
-      </c>
-      <c r="G8" s="334">
-        <v>0</v>
-      </c>
-      <c r="H8" s="334">
-        <v>0</v>
-      </c>
-      <c r="I8" s="334">
-        <v>0</v>
-      </c>
-      <c r="J8" s="334">
-        <v>0</v>
-      </c>
-      <c r="K8" s="334">
-        <v>0</v>
-      </c>
-      <c r="L8" s="334">
-        <v>0</v>
-      </c>
-      <c r="M8" s="334"/>
+      <c r="C8" s="321">
+        <v>0</v>
+      </c>
+      <c r="D8" s="321">
+        <v>0</v>
+      </c>
+      <c r="E8" s="321">
+        <v>0</v>
+      </c>
+      <c r="F8" s="321">
+        <v>0</v>
+      </c>
+      <c r="G8" s="321">
+        <v>0</v>
+      </c>
+      <c r="H8" s="321">
+        <v>0</v>
+      </c>
+      <c r="I8" s="321">
+        <v>0</v>
+      </c>
+      <c r="J8" s="321">
+        <v>0</v>
+      </c>
+      <c r="K8" s="321">
+        <v>0</v>
+      </c>
+      <c r="L8" s="321">
+        <v>0</v>
+      </c>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="321"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="321"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>195728</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>202576</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>183473</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>169479</v>
       </c>
-      <c r="G12" s="334">
+      <c r="G12" s="321">
         <v>159963</v>
       </c>
-      <c r="H12" s="334">
+      <c r="H12" s="321">
         <v>166689</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="321">
         <v>174921</v>
       </c>
-      <c r="J12" s="334">
+      <c r="J12" s="321">
         <v>164193</v>
       </c>
-      <c r="K12" s="334">
+      <c r="K12" s="321">
         <v>123960</v>
       </c>
-      <c r="L12" s="334">
+      <c r="L12" s="321">
         <v>136138</v>
       </c>
-      <c r="M12" s="334"/>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334">
+      <c r="C13" s="321">
         <v>343835</v>
       </c>
-      <c r="D13" s="334">
+      <c r="D13" s="321">
         <v>349079</v>
       </c>
-      <c r="E13" s="334">
+      <c r="E13" s="321">
         <v>328746</v>
       </c>
-      <c r="F13" s="334">
+      <c r="F13" s="321">
         <v>315158</v>
       </c>
-      <c r="G13" s="334">
+      <c r="G13" s="321">
         <v>303478</v>
       </c>
-      <c r="H13" s="334">
+      <c r="H13" s="321">
         <v>269677</v>
       </c>
-      <c r="I13" s="334">
+      <c r="I13" s="321">
         <v>270578</v>
       </c>
-      <c r="J13" s="334">
+      <c r="J13" s="321">
         <v>252644</v>
       </c>
-      <c r="K13" s="334">
+      <c r="K13" s="321">
         <v>236279</v>
       </c>
-      <c r="L13" s="334">
+      <c r="L13" s="321">
         <v>255972</v>
       </c>
-      <c r="M13" s="334"/>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>9629</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>6675</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>13807</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>11494</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>8956</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>7801</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>6832</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>7018</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>9598</v>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="321">
         <v>12594</v>
       </c>
-      <c r="M14" s="334"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>77491</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>77654</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>92414</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>83816</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>67681</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>66702</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>61245</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>57735</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>54327</v>
       </c>
-      <c r="L15" s="336">
+      <c r="L15" s="323">
         <v>50650</v>
       </c>
-      <c r="M15" s="336"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>286</v>
       </c>
-      <c r="D16" s="334">
+      <c r="D16" s="321">
         <v>538</v>
       </c>
-      <c r="E16" s="334">
+      <c r="E16" s="321">
         <v>1037</v>
       </c>
-      <c r="F16" s="334">
+      <c r="F16" s="321">
         <v>1136</v>
       </c>
-      <c r="G16" s="334">
+      <c r="G16" s="321">
         <v>1055</v>
       </c>
-      <c r="H16" s="334">
+      <c r="H16" s="321">
         <v>834</v>
       </c>
-      <c r="I16" s="334">
+      <c r="I16" s="321">
         <v>625</v>
       </c>
-      <c r="J16" s="334">
+      <c r="J16" s="321">
         <v>535</v>
       </c>
-      <c r="K16" s="334">
+      <c r="K16" s="321">
         <v>477</v>
       </c>
-      <c r="L16" s="334">
+      <c r="L16" s="321">
         <v>443</v>
       </c>
-      <c r="M16" s="334"/>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6433,157 +6449,157 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334"/>
-      <c r="D19" s="334"/>
-      <c r="E19" s="334"/>
-      <c r="F19" s="334"/>
-      <c r="G19" s="334"/>
-      <c r="H19" s="334"/>
-      <c r="I19" s="334"/>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="C19" s="321"/>
+      <c r="D19" s="321"/>
+      <c r="E19" s="321"/>
+      <c r="F19" s="321"/>
+      <c r="G19" s="321"/>
+      <c r="H19" s="321"/>
+      <c r="I19" s="321"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334"/>
-      <c r="F20" s="334"/>
-      <c r="G20" s="334"/>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>-237258</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>433617</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>-344587</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>-389771</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>-34228</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>-588009</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>-356099</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>-162642</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>203017</v>
       </c>
-      <c r="L22" s="334">
+      <c r="L22" s="321">
         <v>818693</v>
       </c>
-      <c r="M22" s="334"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>23438</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>-116901</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>-2059</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>79654</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>234002</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>602337</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>422390</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>268261</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>-366131</v>
       </c>
-      <c r="L23" s="334">
+      <c r="L23" s="321">
         <v>-1078507</v>
       </c>
-      <c r="M23" s="334"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>194894</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-190955</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>-22248</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>124588</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>29636</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>166667</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>10436</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>-67067</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>282268</v>
       </c>
-      <c r="L24" s="334">
+      <c r="L24" s="321">
         <v>213791</v>
       </c>
-      <c r="M24" s="334"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6617,150 +6633,150 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>0</v>
       </c>
-      <c r="D28" s="334"/>
-      <c r="E28" s="334"/>
-      <c r="F28" s="334"/>
-      <c r="G28" s="334"/>
-      <c r="H28" s="334"/>
-      <c r="I28" s="334"/>
-      <c r="J28" s="334"/>
-      <c r="K28" s="334"/>
-      <c r="L28" s="334"/>
-      <c r="M28" s="334"/>
+      <c r="D28" s="321"/>
+      <c r="E28" s="321"/>
+      <c r="F28" s="321"/>
+      <c r="G28" s="321"/>
+      <c r="H28" s="321"/>
+      <c r="I28" s="321"/>
+      <c r="J28" s="321"/>
+      <c r="K28" s="321"/>
+      <c r="L28" s="321"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>0</v>
       </c>
-      <c r="D29" s="334"/>
-      <c r="E29" s="334"/>
-      <c r="F29" s="334"/>
-      <c r="G29" s="334"/>
-      <c r="H29" s="334"/>
-      <c r="I29" s="334"/>
-      <c r="J29" s="334"/>
-      <c r="K29" s="334"/>
-      <c r="L29" s="334"/>
-      <c r="M29" s="334"/>
+      <c r="D29" s="321"/>
+      <c r="E29" s="321"/>
+      <c r="F29" s="321"/>
+      <c r="G29" s="321"/>
+      <c r="H29" s="321"/>
+      <c r="I29" s="321"/>
+      <c r="J29" s="321"/>
+      <c r="K29" s="321"/>
+      <c r="L29" s="321"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>9614287</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>9350607</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>8509373</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>7908726</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>7269197</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>6596029</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>6239073</v>
       </c>
-      <c r="J30" s="336">
+      <c r="J30" s="323">
         <v>5994090</v>
       </c>
-      <c r="K30" s="336">
+      <c r="K30" s="323">
         <v>5731485</v>
       </c>
-      <c r="L30" s="336">
+      <c r="L30" s="323">
         <v>4981503</v>
       </c>
-      <c r="M30" s="336"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>893611</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>807719</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>757298</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>694298</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>624803</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>549652</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>472584</v>
       </c>
-      <c r="J31" s="336">
+      <c r="J31" s="323">
         <v>422752</v>
       </c>
-      <c r="K31" s="336">
+      <c r="K31" s="323">
         <v>354410</v>
       </c>
-      <c r="L31" s="336">
+      <c r="L31" s="323">
         <v>317377</v>
       </c>
-      <c r="M31" s="336"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>11703</v>
       </c>
-      <c r="D32" s="334">
+      <c r="D32" s="321">
         <v>11495</v>
       </c>
-      <c r="E32" s="334">
+      <c r="E32" s="321">
         <v>11111</v>
       </c>
-      <c r="F32" s="334">
+      <c r="F32" s="321">
         <v>10187</v>
       </c>
-      <c r="G32" s="334">
+      <c r="G32" s="321">
         <v>9217</v>
       </c>
-      <c r="H32" s="334">
+      <c r="H32" s="321">
         <v>8292</v>
       </c>
-      <c r="I32" s="334">
+      <c r="I32" s="321">
         <v>6631</v>
       </c>
-      <c r="J32" s="334">
+      <c r="J32" s="321">
         <v>5857</v>
       </c>
-      <c r="K32" s="334">
+      <c r="K32" s="321">
         <v>4281</v>
       </c>
-      <c r="L32" s="334">
+      <c r="L32" s="321">
         <v>3729</v>
       </c>
-      <c r="M32" s="334"/>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6787,47 +6803,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>61890</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>62009</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>74823</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>73350</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>57536</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>76564</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>61222</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>50549</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>39074</v>
       </c>
-      <c r="L36" s="323">
+      <c r="L36" s="318">
         <f t="shared" si="1"/>
         <v>21559</v>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6836,47 +6852,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>0</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L37" s="323">
+      <c r="L37" s="318">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6885,47 +6901,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>61890</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>62009</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>74823</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>73350</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>57536</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>76564</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>61222</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>50549</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>39074</v>
       </c>
-      <c r="L38" s="319">
+      <c r="L38" s="317">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v>21559</v>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6934,47 +6950,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-62611</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-63194</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-65314</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-56820</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-49077</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-47190</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-42561</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>-38680</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>-36735</v>
       </c>
-      <c r="L39" s="323">
+      <c r="L39" s="318">
         <f t="shared" si="13"/>
         <v>-33323</v>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -6983,47 +6999,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>0</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L40" s="333">
+      <c r="L40" s="320">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -7032,47 +7048,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-62611</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-63194</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-65314</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-56820</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-49077</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>-47190</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>-42561</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>-38680</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>-36735</v>
       </c>
-      <c r="L41" s="333">
+      <c r="L41" s="320">
         <f t="shared" si="15"/>
         <v>-33323</v>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7081,47 +7097,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L42" s="323">
+      <c r="L42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7130,47 +7146,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>-721</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>-1185</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>9509</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>16530</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>8459</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>29374</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>18661</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>11869</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>2339</v>
       </c>
-      <c r="L43" s="324">
+      <c r="L43" s="319">
         <f t="shared" si="17"/>
         <v>-11764</v>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7277,47 +7293,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-9629</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-6675</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-13807</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-11494</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-8956</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-7801</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>-6832</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>-7018</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>-9598</v>
       </c>
-      <c r="L46" s="323">
+      <c r="L46" s="318">
         <f t="shared" si="20"/>
         <v>-12594</v>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7326,47 +7342,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>77491</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>77654</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>92414</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>83816</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>67681</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>66702</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>61245</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>57735</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>54327</v>
       </c>
-      <c r="L47" s="324">
+      <c r="L47" s="319">
         <f t="shared" si="21"/>
         <v>50650</v>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7375,47 +7391,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>-286</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>-538</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>-1037</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>-1136</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>-1055</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>-834</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>-625</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>-535</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>-477</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="318">
         <f t="shared" si="22"/>
         <v>-443</v>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7429,47 +7445,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-195728</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-202576</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-183473</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-169479</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>-159963</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>-166689</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>-174921</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>-164193</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>-123960</v>
       </c>
-      <c r="L51" s="323">
+      <c r="L51" s="318">
         <f t="shared" si="23"/>
         <v>-136138</v>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7478,47 +7494,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>343835</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>349079</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>328746</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>315158</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>303478</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>269677</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>270578</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>252644</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>236279</v>
       </c>
-      <c r="L52" s="323">
+      <c r="L52" s="318">
         <f t="shared" si="24"/>
         <v>255972</v>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7734,47 +7750,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>0</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L61" s="323">
+      <c r="L61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7783,47 +7799,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>0</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>0</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L62" s="323">
+      <c r="L62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7832,47 +7848,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323">
+      <c r="L63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7881,47 +7897,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>-18926</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>125761</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>-368894</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>-185529</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>229410</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>180995</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>76727</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>38552</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>119154</v>
       </c>
-      <c r="L64" s="323">
+      <c r="L64" s="318">
         <f t="shared" si="32"/>
         <v>-46023</v>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8303,115 +8319,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>0</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>9614287</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>9350607</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>8509373</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>7908726</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>7269197</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>6596029</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>6239073</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>5994090</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>5731485</v>
       </c>
-      <c r="L79" s="323">
+      <c r="L79" s="318">
         <f t="shared" si="41"/>
         <v>4981503</v>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8420,47 +8436,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>893611</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>807719</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>757298</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>694298</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>624803</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>549652</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>472584</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>422752</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>354410</v>
       </c>
-      <c r="L80" s="323">
+      <c r="L80" s="318">
         <f t="shared" si="42"/>
         <v>317377</v>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9548,11 +9564,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-7052.6474952516664</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-7000.4599952516664</v>
       </c>
@@ -9580,8 +9596,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>6736706</v>
       </c>
@@ -9885,54 +9901,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>AVERAGE(G4:J4)</f>
         <v>68018</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>61890</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>62009</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>74823</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>73350</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>57536</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>76564</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>61222</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>50549</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>39074</v>
       </c>
-      <c r="P4" s="323">
+      <c r="P4" s="339">
         <f>Data!L36</f>
         <v>21559</v>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9942,52 +9958,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>0</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>0</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P5" s="323">
+      <c r="P5" s="339">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9997,52 +10013,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>68018</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>61890</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>62009</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>74823</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>73350</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>57536</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>76564</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>61222</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>50549</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>39074</v>
       </c>
-      <c r="P6" s="319">
+      <c r="P6" s="335">
         <f t="shared" si="2"/>
         <v>21559</v>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10052,52 +10068,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-61984.75</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-62611</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-63194</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-65314</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-56820</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-49077</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-47190</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-42561</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>-38680</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>-36735</v>
       </c>
-      <c r="P7" s="318">
+      <c r="P7" s="334">
         <f t="shared" si="3"/>
         <v>-33323</v>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10107,54 +10123,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>6033.25</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>-721</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>-1185</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>9509</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>16530</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>8459</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>29374</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>18661</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>11869</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>2339</v>
       </c>
-      <c r="P8" s="319">
+      <c r="P8" s="335">
         <f t="shared" si="4"/>
         <v>-11764</v>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10164,52 +10180,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="318">
+      <c r="P9" s="334">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10219,52 +10235,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>0</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>0</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>0</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>0</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>0</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>0</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>0</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>0</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>0</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>0</v>
       </c>
-      <c r="P10" s="318">
+      <c r="P10" s="334">
         <f>Data!L62</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10274,54 +10290,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>0</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324">
+      <c r="P11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10331,52 +10347,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>148107</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>148107</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>146503</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>145273</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>145679</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>143515</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>102988</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>95657</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>88451</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>112319</v>
       </c>
-      <c r="P12" s="318">
+      <c r="P12" s="334">
         <f t="shared" si="6"/>
         <v>119834</v>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10386,52 +10402,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>154140.25</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>147386</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>145318</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>154782</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>162209</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>151974</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>132362</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>114318</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>100320</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>114658</v>
       </c>
-      <c r="P13" s="319">
+      <c r="P13" s="335">
         <f t="shared" si="7"/>
         <v>108070</v>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10441,52 +10457,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-38535.0625</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-9629</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-6675</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-13807</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-11494</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-8956</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-7801</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>-6832</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>-7018</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>-9598</v>
       </c>
-      <c r="P14" s="318">
+      <c r="P14" s="334">
         <f>Data!L46</f>
         <v>-12594</v>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10496,54 +10512,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>-902.60509486250271</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>-286</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>-538</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>-1037</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>-1136</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>-1055</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>-834</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>-625</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>-535</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>-477</v>
       </c>
-      <c r="P15" s="323">
+      <c r="P15" s="339">
         <f>Data!L48</f>
         <v>-443</v>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10553,54 +10569,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>114702.58240513749</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>137471</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>138105</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>139938</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>149579</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>141963</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>123727</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>106861</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>92767</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>104583</v>
       </c>
-      <c r="P16" s="319">
+      <c r="P16" s="335">
         <f t="shared" si="8"/>
         <v>95033</v>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10610,7 +10626,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10619,24 +10635,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10644,71 +10660,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>114702.58240513749</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>137471</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>138105</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>139938</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>149579</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>141963</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>123727</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>106861</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>92767</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>104583</v>
       </c>
-      <c r="P19" s="324">
+      <c r="P19" s="340">
         <f t="shared" si="9"/>
         <v>95033</v>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10781,54 +10797,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>0</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>0</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>0</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>0</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>0</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>0</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>0</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>0</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>0</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>0</v>
       </c>
-      <c r="P23" s="323">
+      <c r="P23" s="339">
         <f>Data!L37</f>
         <v>0</v>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10838,54 +10854,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>0</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>0</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>0</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>0</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>0</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>0</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>0</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>0</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>0</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>0</v>
       </c>
-      <c r="P24" s="323">
+      <c r="P24" s="339">
         <f>Data!L40</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10895,54 +10911,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>0</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="P25" s="319">
+      <c r="P25" s="335">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11148,54 +11164,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>AVERAGE(G33:J33)</f>
         <v>-61984.75</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-62611</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-63194</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-65314</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-56820</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-49077</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>-47190</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>-42561</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>-38680</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>-36735</v>
       </c>
-      <c r="P33" s="318">
+      <c r="P33" s="334">
         <f>Data!L41</f>
         <v>-33323</v>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11205,7 +11221,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>AVERAGE(G34:J34)</f>
         <v>0</v>
       </c>
@@ -11214,47 +11230,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>0</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>0</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>0</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>0</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>0</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>0</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>0</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>0</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>0</v>
       </c>
-      <c r="P34" s="323">
+      <c r="P34" s="339">
         <f>Data!L42</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11264,54 +11280,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-61984.75</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-62611</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-63194</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-65314</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-56820</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-49077</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-47190</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-42561</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>-38680</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>-36735</v>
       </c>
-      <c r="P35" s="319">
+      <c r="P35" s="335">
         <f t="shared" si="14"/>
         <v>-33323</v>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11605,52 +11621,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-195728</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-195728</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-202576</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-183473</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-169479</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>-159963</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>-166689</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>-174921</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>-164193</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>-123960</v>
       </c>
-      <c r="P47" s="318">
+      <c r="P47" s="334">
         <f>Data!L51</f>
         <v>-136138</v>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11660,52 +11676,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>343835</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>343835</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>349079</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>328746</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>315158</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>303478</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>269677</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>270578</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>252644</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>236279</v>
       </c>
-      <c r="P48" s="327">
+      <c r="P48" s="343">
         <f t="shared" si="19"/>
         <v>255972</v>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11715,54 +11731,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>343835</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>343835</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>349079</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>328746</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>315158</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>303478</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>269677</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>270578</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>252644</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>236279</v>
       </c>
-      <c r="P49" s="329">
+      <c r="P49" s="348">
         <f>Data!L52</f>
         <v>255972</v>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11772,52 +11788,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>148107</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>148107</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>146503</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>145273</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>145679</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>143515</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>102988</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>95657</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>88451</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>112319</v>
       </c>
-      <c r="P50" s="319">
+      <c r="P50" s="335">
         <f t="shared" si="20"/>
         <v>119834</v>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -11964,52 +11980,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318">
+      <c r="P58" s="334">
         <f>Data!L56</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -12019,52 +12035,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>0</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>0</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318">
+      <c r="P59" s="334">
         <f>Data!L55</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -12074,52 +12090,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318">
+      <c r="P60" s="334">
         <f>Data!L57</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12129,52 +12145,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319">
+      <c r="P61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12184,53 +12200,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>-60266</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>-60989</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>-48561</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>-66899</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>-75337</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>-57859</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>-46241</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>-35567</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>-50733</v>
       </c>
-      <c r="P62" s="318">
+      <c r="P62" s="334">
         <f>Data!L58</f>
         <v>-44826</v>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12240,52 +12256,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-60266</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>-60989</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>-48561</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>-66899</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>-75337</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>-57859</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>-46241</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>-35567</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>-50733</v>
       </c>
-      <c r="P63" s="319">
+      <c r="P63" s="335">
         <f t="shared" si="23"/>
         <v>-44826</v>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13660,54 +13676,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>10507898</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>10507898</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>10158326</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>9266671</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>8603024</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>7894000</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>7145681</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>6711657</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>6416842</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>6085895</v>
       </c>
-      <c r="P101" s="323">
+      <c r="P101" s="339">
         <f t="shared" si="42"/>
         <v>5298880</v>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13717,54 +13733,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>0</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>0</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>0</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>0</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>0</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>0</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333">
+      <c r="P102" s="352">
         <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13774,54 +13790,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>0</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>0</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>0</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>0</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>0</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>0</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333">
+      <c r="P103" s="352">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13831,54 +13847,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>9614287</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>9614287</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>9350607</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>8509373</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>7908726</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>7269197</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>6596029</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>6239073</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>5994090</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>5731485</v>
       </c>
-      <c r="P104" s="323">
+      <c r="P104" s="339">
         <f>Data!L79</f>
         <v>4981503</v>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13888,54 +13904,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>893611</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>893611</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>807719</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>757298</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>694298</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>624803</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>549652</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>472584</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>422752</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>354410</v>
       </c>
-      <c r="P105" s="323">
+      <c r="P105" s="339">
         <f>Data!L80</f>
         <v>317377</v>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -15433,7 +15449,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15472,7 +15488,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>114702.58240513749</v>
       </c>
@@ -15504,7 +15520,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>1911709.7067522916</v>
       </c>
@@ -15512,17 +15528,17 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>9516669</v>
       </c>
@@ -15530,15 +15546,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>0</v>
       </c>
@@ -15546,15 +15562,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>2145886.1</v>
       </c>
@@ -15562,15 +15578,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>-5459073.1932477076</v>
       </c>
@@ -15637,7 +15653,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15647,7 +15663,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
@@ -15661,10 +15677,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15682,7 +15698,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15704,7 +15720,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15726,7 +15742,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15746,9 +15762,19 @@
         <f t="shared" si="1"/>
         <v>105384.01017104799</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15768,9 +15794,19 @@
         <f t="shared" si="1"/>
         <v>102449.19786744905</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15790,9 +15826,19 @@
         <f t="shared" si="1"/>
         <v>99596.116399897961</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15814,7 +15860,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15836,7 +15882,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15858,7 +15904,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15880,7 +15926,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15902,7 +15948,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15924,7 +15970,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15946,11 +15992,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>169468.65630259874</v>
       </c>
@@ -15966,13 +16012,23 @@
         <f t="shared" si="1"/>
         <v>79453.51912165276</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>174634.11713140711</v>
       </c>
@@ -15988,13 +16044,23 @@
         <f t="shared" si="1"/>
         <v>77240.838420814121</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>179957.02291880603</v>
       </c>
@@ -16010,9 +16076,19 @@
         <f t="shared" si="1"/>
         <v>75089.778098002629</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16034,7 +16110,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16056,7 +16132,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16078,7 +16154,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16100,7 +16176,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16122,7 +16198,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16144,7 +16220,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16166,7 +16242,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16188,7 +16264,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16210,7 +16286,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16232,7 +16308,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16254,11 +16330,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>258015.19507484647</v>
       </c>
@@ -16274,13 +16350,23 @@
         <f t="shared" si="1"/>
         <v>53504.082504124774</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>265879.58376166486</v>
       </c>
@@ -16296,13 +16382,23 @@
         <f t="shared" si="1"/>
         <v>52014.061016320193</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>273983.68162297359</v>
       </c>
@@ -16318,13 +16414,23 @@
         <f t="shared" si="1"/>
         <v>50565.534755238688</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>282334.79507388303</v>
       </c>
@@ -16340,9 +16446,19 @@
         <f t="shared" si="1"/>
         <v>49157.348130940874</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16364,7 +16480,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16375,11 +16491,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16389,7 +16505,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>2631063.579932001</v>
@@ -16416,7 +16532,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16438,7 +16554,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16459,14 +16575,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>1911709.7067522905</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>2095973.8538441975</v>
       </c>
       <c r="D58" s="123">
@@ -16478,16 +16594,26 @@
       <c r="F58" s="123">
         <v>2566089.782987583</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>1911709.7067522905</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>2177729.7057453385</v>
       </c>
       <c r="D59" s="123">
@@ -16499,16 +16625,26 @@
       <c r="F59" s="123">
         <v>2925896.5784820877</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>1911709.7067522905</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>2261174.8479017401</v>
       </c>
       <c r="D60" s="123">
@@ -16520,16 +16656,26 @@
       <c r="F60" s="123">
         <v>3339715.8483383819</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>1911709.70675229</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>2341971.4002733147</v>
       </c>
       <c r="D61" s="123">
@@ -16541,26 +16687,56 @@
       <c r="F61" s="123">
         <v>3793896.3810982425</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16932,6 +17108,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17034,7 +17280,7 @@
       <c r="B6" s="149" t="s">
         <v>446</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>367012.83238366671</v>
       </c>
@@ -17042,8 +17288,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18500,7 +18746,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>-721</v>
       </c>
@@ -18508,11 +18754,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 兴业银行(601166.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18525,7 +18771,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>137471</v>
       </c>
@@ -18533,8 +18779,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18547,7 +18793,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>114702.58240513749</v>
       </c>
@@ -18555,8 +18801,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18566,8 +18812,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18580,8 +18826,8 @@
       <c r="B11" s="159" t="s">
         <v>452</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18599,8 +18845,8 @@
         <v>-5.5054441259114184E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18617,8 +18863,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.3520092995664894</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18635,8 +18881,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.7745066708446342E-2</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18662,21 +18908,21 @@
       <c r="C18" s="150">
         <v>30</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18690,8 +18936,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18705,8 +18951,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18726,8 +18972,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18737,8 +18983,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18752,8 +18998,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18763,8 +19009,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18784,8 +19030,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18795,8 +19041,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18810,8 +19056,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18821,8 +19067,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18842,8 +19088,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18853,8 +19099,8 @@
         <v>0.04</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18868,8 +19114,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18880,8 +19126,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18943,8 +19189,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18954,8 +19200,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -18969,8 +19215,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -18980,8 +19226,8 @@
         <v>0.01</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19001,8 +19247,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19012,8 +19258,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19027,8 +19273,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19038,8 +19284,8 @@
         <v>0.01</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19223,7 +19469,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19232,7 +19478,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.829322250329541</v>
+        <v>1.8293222503295408</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0733131-E52E-417C-8CFE-86F2FDD44A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C66090-795F-49C2-ABB5-D604FAF50099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3898,29 +3898,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4338,7 +4338,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>22.9</v>
+        <v>22.81</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>475731.7280143</v>
+        <v>473862.04000026995</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4396,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.8956167773784021E-2</v>
+        <v>0.10046122894835863</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4529,7 +4529,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4604,22 +4604,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4631,13 +4631,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4657,13 +4657,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4692,13 +4692,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4714,13 +4714,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4784,13 +4784,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4806,7 +4806,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4828,22 +4828,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.24110769925711084</v>
+        <v>0.24205902292800696</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.6288209606986902E-2</v>
+        <v>4.6470846120122755E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>453</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5037,22 +5037,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5089,13 +5089,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5108,13 +5108,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5236,13 +5236,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5281,13 +5281,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5430,13 +5430,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5449,22 +5449,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5797,13 +5797,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5840,13 +5840,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5893,17 +5893,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5920,6 +5909,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13448,12 +13448,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.6288209606986902E-2</v>
+        <v>4.6470846120122755E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.6288209606986902E-2</v>
+        <v>4.6470846120122755E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14647,50 +14647,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.24110769925711084</v>
+        <v>0.24205902292800696</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.28896748294212526</v>
+        <v>0.29010764398836775</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29030016681134352</v>
+        <v>0.29144558614553995</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.29415317869190682</v>
+        <v>0.2953138006157241</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.31441880200915212</v>
+        <v>0.31565938474395366</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.29840977937829016</v>
+        <v>0.29958719630700764</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.26007725092550671</v>
+        <v>0.26110342157799665</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.2246244967642517</v>
+        <v>0.2255107836870392</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.19499855598702368</v>
+        <v>0.19576794967570549</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.21983608374519925</v>
+        <v>0.22070347732420267</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.1997617447057124</v>
+        <v>0.20054993221222331</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14704,43 +14704,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16288802162396598</v>
+        <v>0.16353071877197814</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16323065170390696</v>
+        <v>0.16387470074614072</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19425654115132329</v>
+        <v>0.19502300711816323</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17618332994069419</v>
+        <v>0.17687848556080216</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14226715607659782</v>
+        <v>0.14282849075642659</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14020927357192162</v>
+        <v>0.14076248859259122</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1287385229815049</v>
+        <v>0.12924647857415442</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12136041512510712</v>
+        <v>0.12183925937592956</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11419671382180124</v>
+        <v>0.11464729270141379</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10646756778534122</v>
+        <v>0.10688765025358678</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18690,7 +18690,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.9</v>
+        <v>-22.81</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.9</v>
+        <v>22.81</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19469,7 +19469,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19528,7 +19528,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.9</v>
+        <v>22.81</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.8956167773784021E-2</v>
+        <v>0.10046122894835863</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C40224-D8DA-474B-877E-DAF02C2E6C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC6D14C-5C19-814E-8D39-D51F39C4D4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2513,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3894,30 +3905,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3932,7 +3943,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4221,16 +4232,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4247,7 +4258,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4261,7 +4272,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4270,7 +4281,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4278,7 +4289,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4287,7 +4298,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4297,7 +4308,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4307,17 +4318,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4329,7 +4340,7 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
@@ -4339,7 +4350,7 @@
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4349,7 +4360,7 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
@@ -4363,7 +4374,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4377,7 +4388,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4387,27 +4398,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4422,7 +4433,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4437,7 +4448,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4445,7 +4456,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4453,7 +4464,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4469,7 +4480,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4486,11 +4497,11 @@
         <v>0.10366547931610515</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4509,7 +4520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4525,10 +4536,10 @@
         <v>424</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4547,7 +4558,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4566,7 +4577,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4585,11 +4596,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4599,25 +4610,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4626,16 +4637,16 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4648,20 +4659,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4674,7 +4685,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4687,16 +4698,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4709,16 +4720,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4733,7 +4744,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4748,7 +4759,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4761,12 +4772,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4779,16 +4790,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4801,8 +4812,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4810,7 +4821,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4823,25 +4834,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4854,7 +4865,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4867,7 +4878,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
@@ -4877,7 +4888,7 @@
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
@@ -4893,7 +4904,7 @@
         <v>0.19198146616473824</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>454</v>
       </c>
@@ -4904,7 +4915,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>455</v>
       </c>
@@ -4917,7 +4928,7 @@
         <v>0.16493306371564362</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4931,7 +4942,7 @@
         <v>0.7018481216398329</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4945,7 +4956,7 @@
         <v>1.9984681998245511E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4959,7 +4970,7 @@
         <v>11.758917470801054</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4969,34 +4980,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5005,7 +5016,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5014,7 +5025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5023,34 +5034,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5058,7 +5069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5071,7 +5082,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5081,38 +5092,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5125,7 +5136,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5138,7 +5149,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5147,7 +5158,7 @@
         <v>nm</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5156,12 +5167,12 @@
         <v>nm</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5174,7 +5185,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5187,7 +5198,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5200,12 +5211,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5218,7 +5229,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5231,16 +5242,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>453</v>
       </c>
@@ -5253,7 +5264,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5266,7 +5277,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5276,16 +5287,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5302,7 +5313,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5324,7 +5335,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5346,7 +5357,7 @@
         <v>0.19600000000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5368,7 +5379,7 @@
         <v>0.58799999999999997</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5390,7 +5401,7 @@
         <v>0.19600000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5412,7 +5423,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5425,16 +5436,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5444,30 +5455,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5476,16 +5487,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5498,7 +5509,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5511,26 +5522,26 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8293222503295408</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
+        <v>1.829322250329541</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5540,7 +5551,7 @@
         <v>11.250367775156876</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5553,7 +5564,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5566,7 +5577,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5575,12 +5586,12 @@
         <v>0.51355190135855366</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5589,7 +5600,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5599,7 +5610,7 @@
         <v>2.279132885208865</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5609,7 +5620,7 @@
         <v>16.07713967014136</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5622,7 +5633,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5635,7 +5646,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5644,12 +5655,12 @@
         <v>0.3173099771252258</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5658,7 +5669,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5668,7 +5679,7 @@
         <v>2.8333926664293383</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5678,7 +5689,7 @@
         <v>22.575810229609498</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5691,7 +5702,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5704,7 +5715,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5713,12 +5724,12 @@
         <v>5.5003718537040891E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5727,7 +5738,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5737,7 +5748,7 @@
         <v>2.6975834619563113</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5747,7 +5758,7 @@
         <v>20.934968382149542</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5760,7 +5771,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5773,7 +5784,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5782,7 +5793,7 @@
         <v>0.1210155297728992</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5792,21 +5803,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5815,80 +5826,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5927,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5946,15 +5957,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6003,7 +6014,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6019,7 +6030,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6027,7 +6038,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6063,7 +6074,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6099,7 +6110,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6135,7 +6146,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6171,7 +6182,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6207,7 +6218,7 @@
       </c>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6223,7 +6234,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6239,7 +6250,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6255,7 +6266,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6291,7 +6302,7 @@
       </c>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6327,7 +6338,7 @@
       </c>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6363,7 +6374,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6399,7 +6410,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6435,13 +6446,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6457,7 +6468,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6473,7 +6484,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6489,7 +6500,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6525,7 +6536,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6561,7 +6572,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6597,7 +6608,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6617,7 +6628,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6625,7 +6636,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6644,7 +6655,7 @@
       <c r="L28" s="351"/>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6663,7 +6674,7 @@
       <c r="L29" s="351"/>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6700,7 +6711,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6737,7 +6748,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6774,7 +6785,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6790,12 +6801,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6844,7 +6855,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6893,7 +6904,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6942,7 +6953,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6991,7 +7002,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7040,7 +7051,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7089,7 +7100,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7138,7 +7149,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7187,7 +7198,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7236,7 +7247,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7285,7 +7296,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7334,7 +7345,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7383,7 +7394,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7432,12 +7443,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7486,7 +7497,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7535,12 +7546,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7589,7 +7600,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7638,7 +7649,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7687,7 +7698,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7736,13 +7747,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7791,7 +7802,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7840,7 +7851,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7889,7 +7900,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7938,7 +7949,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7987,12 +7998,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8042,7 +8053,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8091,7 +8102,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8141,7 +8152,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8190,7 +8201,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8240,7 +8251,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8256,13 +8267,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8311,7 +8322,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8345,7 +8356,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8379,7 +8390,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8428,7 +8439,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8509,18 +8520,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8536,7 +8547,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8547,7 +8558,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8567,7 +8578,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8589,7 +8600,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8610,7 +8621,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8631,7 +8642,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8653,7 +8664,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8674,7 +8685,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8695,7 +8706,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8707,7 +8718,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8719,7 +8730,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8743,12 +8754,12 @@
         <v>859334.7</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8768,7 +8779,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>458</v>
       </c>
@@ -8789,7 +8800,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8809,7 +8820,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8830,7 +8841,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8850,7 +8861,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8871,7 +8882,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8891,7 +8902,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8911,7 +8922,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8923,7 +8934,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8936,7 +8947,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8960,7 +8971,7 @@
         <v>6770949.1000000006</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -8977,7 +8988,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8997,7 +9008,7 @@
         <v>-1919409.4999999991</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9012,7 +9023,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9031,7 +9042,7 @@
         <v>-1931112.4999999991</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9048,7 +9059,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9065,7 +9076,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9085,7 +9096,7 @@
         <v>7694877.5000000009</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9096,7 +9107,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9109,7 +9120,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9128,7 +9139,7 @@
         <v>64593.7</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9144,7 +9155,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9160,7 +9171,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9176,7 +9187,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9195,7 +9206,7 @@
         <v>4004.5</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9215,7 +9226,7 @@
         <v>7630283.8000000007</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9235,7 +9246,7 @@
         <v>5484397.7000000011</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9254,7 +9265,7 @@
         <v>2145886.1</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9265,7 +9276,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9279,7 +9290,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9293,7 +9304,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9308,10 +9319,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9324,7 +9335,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9338,7 +9349,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9349,10 +9360,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9364,7 +9375,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9378,7 +9389,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9392,10 +9403,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9407,7 +9418,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9418,7 +9429,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9429,10 +9440,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9444,7 +9455,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9460,7 +9471,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9471,7 +9482,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9485,7 +9496,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9501,7 +9512,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9511,7 +9522,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9521,7 +9532,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9531,7 +9542,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9541,10 +9552,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9556,7 +9567,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9572,7 +9583,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9588,7 +9599,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9601,7 +9612,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9614,10 +9625,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9629,7 +9640,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9643,7 +9654,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9657,7 +9668,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9671,7 +9682,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9685,7 +9696,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9696,7 +9707,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9704,7 +9715,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9721,7 +9732,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9738,7 +9749,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9755,7 +9766,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9786,19 +9797,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9855,7 +9866,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9878,7 +9889,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9892,7 +9903,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9949,7 +9960,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10004,7 +10015,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10059,7 +10070,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10114,7 +10125,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10171,7 +10182,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10226,7 +10237,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10281,7 +10292,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10338,7 +10349,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10393,7 +10404,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10448,7 +10459,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10503,7 +10514,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10560,7 +10571,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10617,7 +10628,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10643,7 +10654,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10668,7 +10679,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10725,7 +10736,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10744,7 +10755,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10767,7 +10778,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10788,7 +10799,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10845,7 +10856,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10902,7 +10913,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10959,18 +10970,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11029,7 +11040,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11089,7 +11100,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11144,18 +11155,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11212,7 +11223,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11271,7 +11282,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11328,18 +11339,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11397,7 +11408,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11455,7 +11466,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11510,18 +11521,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11579,10 +11590,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11605,14 +11616,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11667,7 +11678,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11722,7 +11733,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11779,7 +11790,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11834,11 +11845,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11848,7 +11859,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11875,7 +11886,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11902,7 +11913,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11957,11 +11968,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -11971,7 +11982,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12026,7 +12037,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12081,7 +12092,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12136,7 +12147,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12191,7 +12202,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12247,7 +12258,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12302,11 +12313,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12316,7 +12327,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12341,7 +12352,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12366,7 +12377,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12391,7 +12402,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12418,10 +12429,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12444,7 +12455,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12465,7 +12476,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12522,7 +12533,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12579,7 +12590,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12636,7 +12647,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12693,7 +12704,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12750,7 +12761,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12809,7 +12820,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12866,7 +12877,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12923,7 +12934,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -12980,7 +12991,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13037,7 +13048,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13095,7 +13106,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13152,7 +13163,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13178,7 +13189,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13202,7 +13213,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13259,18 +13270,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13326,7 +13337,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13382,7 +13393,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13437,7 +13448,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
@@ -13492,11 +13503,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13517,7 +13528,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13574,7 +13585,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13631,10 +13642,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13657,7 +13668,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13667,7 +13678,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13724,7 +13735,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13781,7 +13792,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13838,7 +13849,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13895,7 +13906,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13952,11 +13963,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -13979,7 +13990,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14036,7 +14047,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14093,7 +14104,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14120,18 +14131,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14183,7 +14194,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14235,11 +14246,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14293,7 +14304,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14348,7 +14359,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14402,7 +14413,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14458,7 +14469,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14515,7 +14526,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14534,7 +14545,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14557,7 +14568,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14578,7 +14589,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14636,7 +14647,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
@@ -14693,7 +14704,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
@@ -14743,688 +14754,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15446,16 +15457,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15467,7 +15478,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15480,7 +15491,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15501,7 +15512,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15512,7 +15523,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15530,7 +15541,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15546,7 +15557,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15562,7 +15573,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15578,7 +15589,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15592,7 +15603,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15606,7 +15617,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15620,10 +15631,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15633,13 +15644,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15649,7 +15660,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15659,7 +15670,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15673,10 +15684,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15694,7 +15705,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15716,7 +15727,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15738,7 +15749,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15770,7 +15781,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15802,7 +15813,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15834,7 +15845,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15856,7 +15867,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15878,7 +15889,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15900,7 +15911,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15922,7 +15933,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15944,7 +15955,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15966,7 +15977,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15988,7 +15999,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16020,7 +16031,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16052,7 +16063,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16084,7 +16095,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16106,7 +16117,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16128,7 +16139,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16150,7 +16161,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16172,7 +16183,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16194,7 +16205,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16216,7 +16227,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16238,7 +16249,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16260,7 +16271,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16282,7 +16293,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16304,7 +16315,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16326,7 +16337,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16358,7 +16369,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16390,7 +16401,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16422,7 +16433,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16454,7 +16465,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16476,7 +16487,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16487,11 +16498,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16501,7 +16512,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>2631063.579932001</v>
@@ -16528,7 +16539,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16550,7 +16561,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16571,7 +16582,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16602,7 +16613,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16633,7 +16644,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16664,7 +16675,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16695,7 +16706,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16712,7 +16723,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16732,7 +16743,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16755,7 +16766,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16781,7 +16792,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16808,7 +16819,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16835,7 +16846,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16862,7 +16873,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16889,7 +16900,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16915,7 +16926,7 @@
         <v>-194.04094796947462</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16941,7 +16952,7 @@
         <v>-172.1783443470226</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15">
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16958,7 +16969,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16980,7 +16991,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17003,7 +17014,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17026,7 +17037,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17049,7 +17060,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17071,14 +17082,14 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17086,26 +17097,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17119,7 +17130,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17133,7 +17144,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17147,7 +17158,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17161,7 +17172,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17206,16 +17217,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>447</v>
       </c>
@@ -17227,7 +17238,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>446</v>
       </c>
@@ -17240,7 +17251,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>444</v>
       </c>
@@ -17261,7 +17272,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17272,7 +17283,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>445</v>
       </c>
@@ -17288,7 +17299,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>448</v>
       </c>
@@ -17302,10 +17313,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17315,13 +17326,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17331,7 +17342,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17341,7 +17352,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17355,10 +17366,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17376,7 +17387,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17398,7 +17409,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17420,7 +17431,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17442,7 +17453,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17464,7 +17475,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17486,7 +17497,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17508,7 +17519,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17530,7 +17541,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17552,7 +17563,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17574,7 +17585,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17596,7 +17607,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17618,7 +17629,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17640,7 +17651,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17662,7 +17673,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17684,7 +17695,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17706,7 +17717,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17728,7 +17739,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17750,7 +17761,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17772,7 +17783,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17794,7 +17805,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17816,7 +17827,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17838,7 +17849,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17860,7 +17871,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17882,7 +17893,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17904,7 +17915,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17926,7 +17937,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17948,7 +17959,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -17970,7 +17981,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -17992,7 +18003,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18014,7 +18025,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18036,7 +18047,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18058,7 +18069,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18069,11 +18080,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" ht="13.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18083,7 +18094,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" ht="13.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>558542.27767656068</v>
@@ -18110,7 +18121,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" ht="13.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18132,7 +18143,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" ht="13.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18153,7 +18164,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" ht="13.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18174,7 +18185,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18195,7 +18206,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18216,7 +18227,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18237,14 +18248,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18254,7 +18265,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18277,7 +18288,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18303,7 +18314,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18330,7 +18341,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" ht="13.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18357,7 +18368,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18384,7 +18395,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18411,7 +18422,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18437,7 +18448,7 @@
         <v>33.658435935253991</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18463,7 +18474,7 @@
         <v>37.705948764800347</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18480,7 +18491,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18502,7 +18513,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18525,7 +18536,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18548,7 +18559,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18571,7 +18582,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18593,14 +18604,14 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18608,23 +18619,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18654,17 +18665,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
-    <col min="5" max="6" width="42.73046875" customWidth="1"/>
-    <col min="8" max="9" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="42.6640625" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18677,7 +18688,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18689,7 +18700,7 @@
         <v>-22.62</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18709,7 +18720,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18718,7 +18729,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18738,7 +18749,7 @@
         <v>27.94815119642859</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18763,7 +18774,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18785,7 +18796,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18807,7 +18818,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18818,7 +18829,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B11" s="159" t="s">
         <v>451</v>
       </c>
@@ -18832,7 +18843,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18851,7 +18862,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18869,7 +18880,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18880,7 +18891,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18889,7 +18900,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18897,7 +18908,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18909,18 +18920,18 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
@@ -18935,7 +18946,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18950,7 +18961,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18959,7 +18970,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -18971,7 +18982,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -18982,7 +18993,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -18997,7 +19008,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19008,7 +19019,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19017,7 +19028,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19029,7 +19040,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19040,7 +19051,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19055,7 +19066,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19066,7 +19077,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19075,7 +19086,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19087,7 +19098,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19098,7 +19109,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19113,7 +19124,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19125,7 +19136,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19138,7 +19149,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9">
+    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19147,12 +19158,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19162,12 +19173,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19176,7 +19187,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19188,7 +19199,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19199,7 +19210,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19214,7 +19225,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19225,7 +19236,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19234,7 +19245,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19246,7 +19257,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19257,7 +19268,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19272,7 +19283,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19283,7 +19294,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19303,7 +19314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9">
+    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19312,7 +19323,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19320,7 +19331,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19333,7 +19344,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19345,7 +19356,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19361,7 +19372,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19369,7 +19380,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19379,7 +19390,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19391,7 +19402,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19401,7 +19412,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19417,7 +19428,7 @@
         <v>-13.19550584997735</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9">
+    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19426,12 +19437,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19441,7 +19452,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19454,33 +19465,33 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19490,7 +19501,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19510,15 +19521,15 @@
         <v>0.51355190135855366</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
@@ -19531,7 +19542,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
@@ -19540,15 +19551,15 @@
         <v>0.10366547931610515</v>
       </c>
     </row>
-    <row r="88" spans="2:8">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19557,7 +19568,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19569,7 +19580,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19579,7 +19590,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19599,14 +19610,14 @@
         <v>0.3173099771252258</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="13.15">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19617,7 +19628,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19629,7 +19640,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19641,7 +19652,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" ht="13.15">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19660,15 +19671,15 @@
         <v>5.5003718537040891E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="13.15">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19677,7 +19688,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19687,7 +19698,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19697,7 +19708,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" ht="13.15">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19716,16 +19727,16 @@
         <v>0.1210155297728992</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="14.65">
+    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="13.9">
+    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19733,7 +19744,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="13.9">
+    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19741,7 +19752,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="13.9">
+    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC6D14C-5C19-814E-8D39-D51F39C4D4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F8667C-985F-4C82-AC94-0415D86080FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2513,7 +2502,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3905,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3943,7 +3932,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4232,7 +4221,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4241,7 +4230,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4258,7 +4247,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4272,7 +4261,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4281,7 +4270,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4289,7 +4278,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4298,7 +4287,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4308,7 +4297,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4318,17 +4307,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4340,17 +4329,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>22.62</v>
+        <v>22.54</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4360,13 +4349,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>469914.92085954006</v>
+        <v>468252.97595817997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4374,7 +4363,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4388,7 +4377,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4398,27 +4387,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="356" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4433,7 +4422,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4448,7 +4437,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4456,7 +4445,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4464,7 +4453,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4480,7 +4469,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4494,14 +4483,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10366547931610515</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.1050256973263648</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4520,7 +4509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4539,7 +4528,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4558,7 +4547,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4577,7 +4566,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4596,11 +4585,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4610,25 +4599,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="356" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="358" t="s">
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4637,16 +4626,16 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="357" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4659,20 +4648,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="357" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4685,7 +4674,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4698,16 +4687,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="357" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4720,16 +4709,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="357" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4744,7 +4733,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4759,7 +4748,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4772,12 +4761,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4790,16 +4779,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="357" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4812,8 +4801,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="357" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4821,7 +4810,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4834,25 +4823,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="356" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="356" t="s">
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4865,7 +4854,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4878,23 +4867,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.24409223311175232</v>
+        <v>0.24495857644134153</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.6861184792219276E-2</v>
+        <v>4.7027506654835849E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>452</v>
@@ -4904,7 +4893,7 @@
         <v>0.19198146616473824</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
         <v>454</v>
       </c>
@@ -4915,7 +4904,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
         <v>455</v>
       </c>
@@ -4928,7 +4917,7 @@
         <v>0.16493306371564362</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4942,7 +4931,7 @@
         <v>0.7018481216398329</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4956,7 +4945,7 @@
         <v>1.9984681998245511E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4970,7 +4959,7 @@
         <v>11.758917470801054</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4980,34 +4969,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B81" s="358" t="s">
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5016,7 +5005,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5025,7 +5014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5034,34 +5023,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="356" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="356" t="s">
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5069,7 +5058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5082,7 +5071,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5092,38 +5081,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="356" t="s">
+    <row r="97" spans="2:6">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="356" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5136,7 +5125,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5149,7 +5138,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5158,7 +5147,7 @@
         <v>nm</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5167,12 +5156,12 @@
         <v>nm</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5185,7 +5174,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5198,7 +5187,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5211,12 +5200,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5229,7 +5218,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5242,16 +5231,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B116" s="356" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
         <v>453</v>
       </c>
@@ -5264,7 +5253,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5277,7 +5266,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5287,16 +5276,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B123" s="357" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
-    </row>
-    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5313,7 +5302,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5335,7 +5324,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5357,7 +5346,7 @@
         <v>0.19600000000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5379,7 +5368,7 @@
         <v>0.58799999999999997</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5401,7 +5390,7 @@
         <v>0.19600000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5423,7 +5412,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5436,16 +5425,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="361" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
-    </row>
-    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5455,30 +5444,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B138" s="359" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B139" s="356" t="s">
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5487,7 +5476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5496,7 +5485,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5509,7 +5498,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5522,7 +5511,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5531,7 +5520,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:4">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5541,7 +5530,7 @@
         <v>1.829322250329541</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:4">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5551,7 +5540,7 @@
         <v>11.250367775156876</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5564,7 +5553,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5577,7 +5566,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5586,12 +5575,12 @@
         <v>0.51355190135855366</v>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5600,7 +5589,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:4">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5610,7 +5599,7 @@
         <v>2.279132885208865</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5620,7 +5609,7 @@
         <v>16.07713967014136</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5633,7 +5622,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5646,7 +5635,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5655,12 +5644,12 @@
         <v>0.3173099771252258</v>
       </c>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5669,7 +5658,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:4">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5679,7 +5668,7 @@
         <v>2.8333926664293383</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:4">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5689,7 +5678,7 @@
         <v>22.575810229609498</v>
       </c>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5702,7 +5691,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5715,7 +5704,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5724,12 +5713,12 @@
         <v>5.5003718537040891E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5738,7 +5727,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:4">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5748,7 +5737,7 @@
         <v>2.6975834619563113</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:4">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5758,7 +5747,7 @@
         <v>20.934968382149542</v>
       </c>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5771,7 +5760,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5784,7 +5773,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5793,7 +5782,7 @@
         <v>0.1210155297728992</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5803,21 +5792,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B179" s="363" t="s">
+    <row r="179" spans="1:6">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
+    </row>
+    <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5826,91 +5815,80 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B188" s="357" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
+    </row>
+    <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B191" s="362" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B192" s="362" t="s">
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
+    </row>
+    <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5927,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5957,15 +5946,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6014,7 +6003,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6030,7 +6019,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6038,7 +6027,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6074,7 +6063,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6110,7 +6099,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6146,7 +6135,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6182,7 +6171,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6218,7 +6207,7 @@
       </c>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6234,7 +6223,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6250,7 +6239,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6266,7 +6255,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6302,7 +6291,7 @@
       </c>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6338,7 +6327,7 @@
       </c>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6374,7 +6363,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6410,7 +6399,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6446,13 +6435,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6468,7 +6457,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6484,7 +6473,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6500,7 +6489,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6536,7 +6525,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6572,7 +6561,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6608,7 +6597,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6628,7 +6617,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6636,7 +6625,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6655,7 +6644,7 @@
       <c r="L28" s="351"/>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6674,7 +6663,7 @@
       <c r="L29" s="351"/>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6711,7 +6700,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6748,7 +6737,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6785,7 +6774,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6801,12 +6790,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6855,7 +6844,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6904,7 +6893,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6953,7 +6942,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7002,7 +6991,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7051,7 +7040,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7100,7 +7089,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7149,7 +7138,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7198,7 +7187,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7247,7 +7236,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7296,7 +7285,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7345,7 +7334,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7394,7 +7383,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7443,12 +7432,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7497,7 +7486,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7546,12 +7535,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7600,7 +7589,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7649,7 +7638,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7698,7 +7687,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7747,13 +7736,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7802,7 +7791,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7851,7 +7840,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7900,7 +7889,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7949,7 +7938,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7998,12 +7987,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8053,7 +8042,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8102,7 +8091,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8152,7 +8141,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8201,7 +8190,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8251,7 +8240,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8267,13 +8256,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8322,7 +8311,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8356,7 +8345,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8390,7 +8379,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8439,7 +8428,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8520,7 +8509,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8531,7 +8520,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8547,7 +8536,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8558,7 +8547,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8578,7 +8567,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8600,7 +8589,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8621,7 +8610,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8642,7 +8631,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8664,7 +8653,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8685,7 +8674,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8706,7 +8695,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8718,7 +8707,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8730,7 +8719,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8754,12 +8743,12 @@
         <v>859334.7</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8779,7 +8768,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>458</v>
       </c>
@@ -8800,7 +8789,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8820,7 +8809,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8841,7 +8830,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8861,7 +8850,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8882,7 +8871,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8902,7 +8891,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8922,7 +8911,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8934,7 +8923,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8947,7 +8936,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8971,7 +8960,7 @@
         <v>6770949.1000000006</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -8988,7 +8977,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9008,7 +8997,7 @@
         <v>-1919409.4999999991</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9023,7 +9012,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9042,7 +9031,7 @@
         <v>-1931112.4999999991</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9059,7 +9048,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9076,7 +9065,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9096,7 +9085,7 @@
         <v>7694877.5000000009</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9107,7 +9096,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9120,7 +9109,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9139,7 +9128,7 @@
         <v>64593.7</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9155,7 +9144,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9171,7 +9160,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9187,7 +9176,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9206,7 +9195,7 @@
         <v>4004.5</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9226,7 +9215,7 @@
         <v>7630283.8000000007</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9246,7 +9235,7 @@
         <v>5484397.7000000011</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9265,7 +9254,7 @@
         <v>2145886.1</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9276,7 +9265,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9290,7 +9279,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9304,7 +9293,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9319,10 +9308,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9335,7 +9324,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9349,7 +9338,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9360,10 +9349,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9375,7 +9364,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9389,7 +9378,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9403,10 +9392,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9418,7 +9407,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9429,7 +9418,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9440,10 +9429,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9455,7 +9444,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9471,7 +9460,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9482,7 +9471,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9496,7 +9485,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9512,7 +9501,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9522,7 +9511,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9532,7 +9521,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9542,7 +9531,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9552,10 +9541,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9567,7 +9556,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9583,7 +9572,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9599,7 +9588,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9612,7 +9601,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9625,10 +9614,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9640,7 +9629,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9654,7 +9643,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9668,7 +9657,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9682,7 +9671,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9696,7 +9685,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9707,7 +9696,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9715,7 +9704,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9732,7 +9721,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9749,7 +9738,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9766,7 +9755,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9797,19 +9786,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9866,7 +9855,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9889,7 +9878,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9903,7 +9892,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9960,7 +9949,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10015,7 +10004,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10070,7 +10059,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10125,7 +10114,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10182,7 +10171,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10237,7 +10226,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10292,7 +10281,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10349,7 +10338,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10404,7 +10393,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10459,7 +10448,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10514,7 +10503,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10571,7 +10560,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10628,7 +10617,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10654,7 +10643,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10679,7 +10668,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10736,7 +10725,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10755,7 +10744,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10778,7 +10767,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10799,7 +10788,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10856,7 +10845,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10913,7 +10902,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10970,18 +10959,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11040,7 +11029,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11100,7 +11089,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11155,18 +11144,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11223,7 +11212,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11282,7 +11271,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11339,18 +11328,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11408,7 +11397,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11466,7 +11455,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11521,18 +11510,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11590,10 +11579,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11616,14 +11605,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11678,7 +11667,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11733,7 +11722,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11790,7 +11779,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11845,11 +11834,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11859,7 +11848,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11886,7 +11875,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11913,7 +11902,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11968,11 +11957,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -11982,7 +11971,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12037,7 +12026,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12092,7 +12081,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12147,7 +12136,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12202,7 +12191,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12258,7 +12247,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12313,11 +12302,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12327,7 +12316,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12352,7 +12341,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12377,7 +12366,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12402,7 +12391,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12429,10 +12418,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12455,7 +12444,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12476,7 +12465,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12533,7 +12522,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12590,7 +12579,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12647,7 +12636,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12704,7 +12693,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12761,7 +12750,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12820,7 +12809,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12877,7 +12866,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12934,7 +12923,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -12991,7 +12980,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13048,7 +13037,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13106,7 +13095,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13163,7 +13152,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13189,7 +13178,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13213,7 +13202,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13270,18 +13259,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13337,7 +13326,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13393,7 +13382,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13448,19 +13437,19 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.6861184792219276E-2</v>
+        <v>4.7027506654835849E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.6861184792219276E-2</v>
+        <v>4.7027506654835849E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13503,11 +13492,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13528,7 +13517,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13585,7 +13574,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13642,10 +13631,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13668,7 +13657,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13678,7 +13667,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13735,7 +13724,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13792,7 +13781,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13849,7 +13838,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13906,7 +13895,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13963,11 +13952,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -13990,7 +13979,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14047,7 +14036,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14104,7 +14093,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14131,18 +14120,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14194,7 +14183,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14246,11 +14235,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14304,7 +14293,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14359,7 +14348,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14413,7 +14402,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14469,7 +14458,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14526,7 +14515,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14545,7 +14534,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14568,7 +14557,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14589,7 +14578,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14647,795 +14636,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.24409223311175232</v>
+        <v>0.24495857644134153</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.29254444559569703</v>
+        <v>0.29358275773623194</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29389362599380042</v>
+        <v>0.29493672670717686</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.29779433209746531</v>
+        <v>0.29885127737553974</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.31831081193676319</v>
+        <v>0.31944057524443581</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.30210362280118674</v>
+        <v>0.30317586281112885</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.26329659797498245</v>
+        <v>0.26423110231562125</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.22740499451376497</v>
+        <v>0.22821211073209244</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.19741233121586393</v>
+        <v>0.19811299610039229</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.22255730847767738</v>
+        <v>0.22334721906677299</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.202234480714448</v>
+        <v>0.20295226059276014</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16490431897386476</v>
+        <v>0.16548960493295567</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16525119027495441</v>
+        <v>0.16583770736554879</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19666113140430161</v>
+        <v>0.1973591300960649</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1783642022830193</v>
+        <v>0.17899726067621546</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14402819956472546</v>
+        <v>0.14453939104499069</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14194484371339544</v>
+        <v>0.14244864085168613</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13033210328366321</v>
+        <v>0.13079468395192823</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12286266606387944</v>
+        <v>0.12329873586357379</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1156102894128757</v>
+        <v>0.11602061874530827</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10778546871283438</v>
+        <v>0.10816802583337684</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15457,16 +15446,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15478,7 +15467,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15491,7 +15480,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15512,7 +15501,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15523,7 +15512,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15541,7 +15530,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15557,7 +15546,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15573,7 +15562,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15589,7 +15578,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15603,7 +15592,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15617,7 +15606,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15631,10 +15620,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15644,13 +15633,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15660,7 +15649,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15670,7 +15659,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15684,10 +15673,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15705,7 +15694,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15727,7 +15716,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15749,7 +15738,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15781,7 +15770,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15813,7 +15802,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15845,7 +15834,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15867,7 +15856,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15889,7 +15878,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15911,7 +15900,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15933,7 +15922,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15955,7 +15944,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15977,7 +15966,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15999,7 +15988,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16031,7 +16020,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16063,7 +16052,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16095,7 +16084,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16117,7 +16106,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16139,7 +16128,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16161,7 +16150,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16183,7 +16172,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16205,7 +16194,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16227,7 +16216,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16249,7 +16238,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16271,7 +16260,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16293,7 +16282,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16315,7 +16304,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16337,7 +16326,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16369,7 +16358,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16401,7 +16390,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16433,7 +16422,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16465,7 +16454,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16487,7 +16476,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16498,11 +16487,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16512,7 +16501,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>2631063.579932001</v>
@@ -16539,7 +16528,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16561,7 +16550,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16582,7 +16571,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16613,7 +16602,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16644,7 +16633,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16675,7 +16664,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16706,7 +16695,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16723,7 +16712,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16743,7 +16732,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16766,7 +16755,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16792,7 +16781,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16819,7 +16808,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16846,7 +16835,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16873,7 +16862,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16900,7 +16889,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16926,7 +16915,7 @@
         <v>-194.04094796947462</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16952,7 +16941,7 @@
         <v>-172.1783443470226</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16969,7 +16958,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16991,7 +16980,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17014,7 +17003,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17037,7 +17026,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17060,7 +17049,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17082,14 +17071,14 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17097,26 +17086,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:17">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17130,7 +17119,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:17">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17144,7 +17133,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:17">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17158,7 +17147,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="104" spans="3:17">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17172,7 +17161,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:17">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17217,16 +17206,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>447</v>
       </c>
@@ -17238,7 +17227,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>446</v>
       </c>
@@ -17251,7 +17240,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>444</v>
       </c>
@@ -17272,7 +17261,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17283,7 +17272,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>445</v>
       </c>
@@ -17299,7 +17288,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
         <v>448</v>
       </c>
@@ -17313,10 +17302,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17326,13 +17315,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17342,7 +17331,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17352,7 +17341,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17366,10 +17355,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17387,7 +17376,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17409,7 +17398,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17431,7 +17420,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17453,7 +17442,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17475,7 +17464,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17497,7 +17486,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17519,7 +17508,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17541,7 +17530,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17563,7 +17552,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17585,7 +17574,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17607,7 +17596,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17629,7 +17618,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17651,7 +17640,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17673,7 +17662,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17695,7 +17684,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17717,7 +17706,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17739,7 +17728,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17761,7 +17750,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17783,7 +17772,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17805,7 +17794,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17827,7 +17816,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17849,7 +17838,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17871,7 +17860,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17893,7 +17882,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17915,7 +17904,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17937,7 +17926,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17959,7 +17948,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -17981,7 +17970,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18003,7 +17992,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18025,7 +18014,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18047,7 +18036,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18069,7 +18058,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18080,11 +18069,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18094,7 +18083,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>558542.27767656068</v>
@@ -18121,7 +18110,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18143,7 +18132,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18164,7 +18153,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18185,7 +18174,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18206,7 +18195,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18227,7 +18216,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18248,14 +18237,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18265,7 +18254,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18288,7 +18277,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18314,7 +18303,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18341,7 +18330,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18368,7 +18357,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18395,7 +18384,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18422,7 +18411,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18448,7 +18437,7 @@
         <v>33.658435935253991</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18474,7 +18463,7 @@
         <v>37.705948764800347</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18491,7 +18480,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18513,7 +18502,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18536,7 +18525,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18559,7 +18548,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18582,7 +18571,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18604,14 +18593,14 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18619,23 +18608,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18665,7 +18654,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18675,7 +18664,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18688,7 +18677,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18697,10 +18686,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.62</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>-22.54</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18720,7 +18709,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18729,7 +18718,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18749,7 +18738,7 @@
         <v>27.94815119642859</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18774,7 +18763,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18796,7 +18785,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18818,7 +18807,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18829,7 +18818,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
         <v>451</v>
       </c>
@@ -18843,7 +18832,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18862,7 +18851,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18880,7 +18869,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18891,7 +18880,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18900,7 +18889,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18908,7 +18897,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18920,24 +18909,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.62</v>
+        <v>22.54</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18946,7 +18935,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18961,7 +18950,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18970,7 +18959,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -18982,7 +18971,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -18993,7 +18982,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19008,7 +18997,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19019,7 +19008,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19028,7 +19017,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19040,7 +19029,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19051,7 +19040,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19066,7 +19055,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19077,7 +19066,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19086,7 +19075,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19098,7 +19087,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19109,7 +19098,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19124,7 +19113,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19136,7 +19125,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19149,7 +19138,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19158,12 +19147,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19173,12 +19162,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19187,7 +19176,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19199,7 +19188,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19210,7 +19199,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19225,7 +19214,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19236,7 +19225,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19245,7 +19234,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19257,7 +19246,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19268,7 +19257,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19283,7 +19272,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19294,7 +19283,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19314,7 +19303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19323,7 +19312,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19331,7 +19320,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19344,7 +19333,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19356,7 +19345,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19372,7 +19361,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19380,7 +19369,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19390,7 +19379,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19402,7 +19391,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19412,7 +19401,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19428,7 +19417,7 @@
         <v>-13.19550584997735</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19437,12 +19426,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19452,7 +19441,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19465,12 +19454,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19479,7 +19468,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19491,7 +19480,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19501,7 +19490,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19521,45 +19510,45 @@
         <v>0.51355190135855366</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.62</v>
+        <v>22.54</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10366547931610515</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.1050256973263648</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19568,7 +19557,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19580,7 +19569,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19590,7 +19579,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19610,14 +19599,14 @@
         <v>0.3173099771252258</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19628,7 +19617,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19640,7 +19629,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19652,7 +19641,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19671,15 +19660,15 @@
         <v>5.5003718537040891E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19688,7 +19677,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19698,7 +19687,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19708,7 +19697,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19727,16 +19716,16 @@
         <v>0.1210155297728992</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19744,7 +19733,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19752,7 +19741,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F8667C-985F-4C82-AC94-0415D86080FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83EE384-9E3E-439C-A7B1-183BA7769DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>22.54</v>
+        <v>22.65</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>468252.97595817997</v>
+        <v>470538.15019755001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1050256973263648</v>
+        <v>0.10315709677575202</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.24495857644134153</v>
+        <v>0.24376893214074341</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.7027506654835849E-2</v>
+        <v>4.6799116997792503E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>452</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13444,12 +13444,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.7027506654835849E-2</v>
+        <v>4.6799116997792503E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.7027506654835849E-2</v>
+        <v>4.6799116997792503E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14643,50 +14643,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.24495857644134153</v>
+        <v>0.24376893214074341</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.29358275773623194</v>
+        <v>0.29215696950881537</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29493672670717686</v>
+        <v>0.29350436291301402</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.29885127737553974</v>
+        <v>0.29739990251852833</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.31944057524443581</v>
+        <v>0.31788920821234368</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.30317586281112885</v>
+        <v>0.30170348555244347</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.26423110231562125</v>
+        <v>0.26294786075912158</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.22821211073209244</v>
+        <v>0.22710379584553483</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.19811299610039229</v>
+        <v>0.19715085792948531</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.22334721906677299</v>
+        <v>0.22226253058565398</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.20295226059276014</v>
+        <v>0.20196662047509112</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14700,43 +14700,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16548960493295567</v>
+        <v>0.16468590265734309</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16583770736554879</v>
+        <v>0.16503231452624589</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1973591300960649</v>
+        <v>0.19640065308456084</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17899726067621546</v>
+        <v>0.17812795830648551</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14453939104499069</v>
+        <v>0.14383743373748742</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14244864085168613</v>
+        <v>0.14175683729788102</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13079468395192823</v>
+        <v>0.13015947798130076</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12329873586357379</v>
+        <v>0.12269993405584782</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11602061874530827</v>
+        <v>0.11545716320173283</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10816802583337684</v>
+        <v>0.10764270650261873</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.54</v>
+        <v>-22.65</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18926,7 +18926,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.54</v>
+        <v>22.65</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.54</v>
+        <v>22.65</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1050256973263648</v>
+        <v>0.10315709677575202</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83EE384-9E3E-439C-A7B1-183BA7769DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFD3B8E-0352-4181-B23B-F5661BB0F86E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>22.65</v>
+        <v>22.64</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>470538.15019755001</v>
+        <v>470330.40708487999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10315709677575202</v>
+        <v>0.103326455001991</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.24376893214074341</v>
+        <v>0.24387660393055821</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.6799116997792503E-2</v>
+        <v>4.6819787985865724E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>452</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13444,12 +13444,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.6799116997792503E-2</v>
+        <v>4.6819787985865724E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.6799116997792503E-2</v>
+        <v>4.6819787985865724E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14643,50 +14643,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.24376893214074341</v>
+        <v>0.24387660393055821</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.29215696950881537</v>
+        <v>0.29228601410665495</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29350436291301402</v>
+        <v>0.29363400264928297</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.29739990251852833</v>
+        <v>0.29753126289949938</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.31788920821234368</v>
+        <v>0.31802961863999923</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.30170348555244347</v>
+        <v>0.30183674680931288</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.26294786075912158</v>
+        <v>0.26306400380716</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.22710379584553483</v>
+        <v>0.22720410670942418</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.19715085792948531</v>
+        <v>0.197237938697122</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.22226253058565398</v>
+        <v>0.22236070308149569</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.20196662047509112</v>
+        <v>0.20205582834632568</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14700,43 +14700,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16468590265734309</v>
+        <v>0.16475864378042496</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16503231452624589</v>
+        <v>0.16510520865810377</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19640065308456084</v>
+        <v>0.19648740248963353</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17812795830648551</v>
+        <v>0.17820663673329931</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14383743373748742</v>
+        <v>0.14390096617288384</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14175683729788102</v>
+        <v>0.14181945074191718</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13015947798130076</v>
+        <v>0.13021696891680487</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12269993405584782</v>
+        <v>0.12275413013979475</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11545716320173283</v>
+        <v>0.1155081601819456</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10764270650261873</v>
+        <v>0.10769025186768172</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.65</v>
+        <v>-22.64</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18926,7 +18926,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.65</v>
+        <v>22.64</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.65</v>
+        <v>22.64</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10315709677575202</v>
+        <v>0.103326455001991</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFD3B8E-0352-4181-B23B-F5661BB0F86E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5397698B-5FE8-4F32-BFA0-9E5777F74F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5397698B-5FE8-4F32-BFA0-9E5777F74F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBB46BC-E928-4C06-B832-E60C33B9F58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>22.64</v>
+        <v>23.71</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>470330.40708487999</v>
+        <v>492558.92014057003</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.103326455001991</v>
+        <v>8.5765652100956657E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.24387660393055821</v>
+        <v>0.23287078502690164</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.6819787985865724E-2</v>
+        <v>4.4706874736398144E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>452</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13444,12 +13444,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.6819787985865724E-2</v>
+        <v>4.4706874736398144E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.6819787985865724E-2</v>
+        <v>4.4706874736398144E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14643,50 +14643,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.24387660393055821</v>
+        <v>0.23287078502690164</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.29228601410665495</v>
+        <v>0.27909554446961904</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.29363400264928297</v>
+        <v>0.28038270012567551</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.29753126289949938</v>
+        <v>0.28410408233001544</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.31802961863999923</v>
+        <v>0.30367737520074156</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.30183674680931288</v>
+        <v>0.28821526561631566</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.26306400380716</v>
+        <v>0.25119228368595964</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.22720410670942418</v>
+        <v>0.21695069489250796</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.197237938697122</v>
+        <v>0.18833685921985838</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.22236070308149569</v>
+        <v>0.21232586747216628</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.20205582834632568</v>
+        <v>0.19293732407257755</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14700,43 +14700,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16475864378042496</v>
+        <v>0.1573233106363906</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16510520865810377</v>
+        <v>0.15765423551326316</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19648740248963353</v>
+        <v>0.1876201936889626</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17820663673329931</v>
+        <v>0.1701644139874271</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14390096617288384</v>
+        <v>0.13740691160498059</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14181945074191718</v>
+        <v>0.13541933212977669</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13021696891680487</v>
+        <v>0.12434045450343577</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12275413013979475</v>
+        <v>0.11721440347384872</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1155081601819456</v>
+        <v>0.11029543426905307</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10769025186768172</v>
+        <v>0.10283033750671927</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-22.64</v>
+        <v>-23.71</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18926,7 +18926,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>22.64</v>
+        <v>23.71</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>22.64</v>
+        <v>23.71</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.103326455001991</v>
+        <v>8.5765652100956657E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBB46BC-E928-4C06-B832-E60C33B9F58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE859FE3-8296-4098-B08A-3C946AED9D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.71</v>
+        <v>23.61</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>492558.92014057003</v>
+        <v>490481.48901387001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.5765652100956657E-2</v>
+        <v>8.736046746812165E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.23287078502690164</v>
+        <v>0.23385710770808293</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.4706874736398144E-2</v>
+        <v>4.4896230410842869E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>452</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13444,12 +13444,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.4706874736398144E-2</v>
+        <v>4.4896230410842869E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.4706874736398144E-2</v>
+        <v>4.4896230410842869E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14643,50 +14643,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.23287078502690164</v>
+        <v>0.23385710770808293</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.27909554446961904</v>
+        <v>0.28027765181595377</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.28038270012567551</v>
+        <v>0.28157025921134121</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.28410408233001544</v>
+        <v>0.28530740330557669</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.30367737520074156</v>
+        <v>0.30496359872975787</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.28821526561631566</v>
+        <v>0.28943599948169607</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.25119228368595964</v>
+        <v>0.25225620695443046</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.21695069489250796</v>
+        <v>0.21786958813644064</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.18833685921985838</v>
+        <v>0.18913455875064983</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.21232586747216628</v>
+        <v>0.21322517228992219</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.19293732407257755</v>
+        <v>0.19375450884205056</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14700,43 +14700,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1573233106363906</v>
+        <v>0.15798965248576116</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15765423551326316</v>
+        <v>0.1583219789927772</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1876201936889626</v>
+        <v>0.18841485778760284</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1701644139874271</v>
+        <v>0.17088514424573895</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13740691160498059</v>
+        <v>0.13798889767700509</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13541933212977669</v>
+        <v>0.13599289982198243</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12434045450343577</v>
+        <v>0.12486709768218815</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11721440347384872</v>
+        <v>0.11771086431024791</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11029543426905307</v>
+        <v>0.11076258985680849</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10283033750671927</v>
+        <v>0.1032658747261463</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.71</v>
+        <v>-23.61</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18926,7 +18926,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.71</v>
+        <v>23.61</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.71</v>
+        <v>23.61</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.5765652100956657E-2</v>
+        <v>8.736046746812165E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE859FE3-8296-4098-B08A-3C946AED9D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830E167D-48C3-47EF-A071-11A4B8C9AC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.61</v>
+        <v>23.52</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>490481.48901387001</v>
+        <v>488611.80099983996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.736046746812165E-2</v>
+        <v>8.8803734132347323E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.23385710770808293</v>
+        <v>0.23475196908961898</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.4896230410842869E-2</v>
+        <v>4.5068027210884355E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>452</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13444,12 +13444,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.4896230410842869E-2</v>
+        <v>4.5068027210884355E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.4896230410842869E-2</v>
+        <v>4.5068027210884355E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14643,50 +14643,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.23385710770808293</v>
+        <v>0.23475196908961898</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.28027765181595377</v>
+        <v>0.28135014283055559</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.28157025921134121</v>
+        <v>0.28264769642771115</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.28530740330557669</v>
+        <v>0.28639914081822559</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.30496359872975787</v>
+        <v>0.30613055127591765</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.28943599948169607</v>
+        <v>0.2905435351939985</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.25225620695443046</v>
+        <v>0.25322147305247039</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.21786958813644064</v>
+        <v>0.21870327278492194</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.18913455875064983</v>
+        <v>0.18985828792954262</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.21322517228992219</v>
+        <v>0.21404108493899077</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.19375450884205056</v>
+        <v>0.19449591640139513</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14700,43 +14700,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15798965248576116</v>
+        <v>0.15859420472741587</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1583219789927772</v>
+        <v>0.15892780289198424</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18841485778760284</v>
+        <v>0.18913583300872888</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17088514424573895</v>
+        <v>0.17153904148137317</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13798889767700509</v>
+        <v>0.13851691641811609</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13599289982198243</v>
+        <v>0.13651328081619921</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12486709768218815</v>
+        <v>0.12534490545393123</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11771086431024791</v>
+        <v>0.11816128853592488</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11076258985680849</v>
+        <v>0.1111864262975871</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1032658747261463</v>
+        <v>0.10366102475698614</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.61</v>
+        <v>-23.52</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18926,7 +18926,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.61</v>
+        <v>23.52</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.61</v>
+        <v>23.52</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.736046746812165E-2</v>
+        <v>8.8803734132347323E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830E167D-48C3-47EF-A071-11A4B8C9AC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9863D5D7-CC72-4736-A265-110424BFAEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.52</v>
+        <v>23.56</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>488611.80099983996</v>
+        <v>489442.77345051995</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.8803734132347323E-2</v>
+        <v>8.8161349768844932E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.23475196908961898</v>
+        <v>0.23435340887045156</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.5068027210884355E-2</v>
+        <v>4.4991511035653652E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>452</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13444,12 +13444,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.5068027210884355E-2</v>
+        <v>4.4991511035653652E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.5068027210884355E-2</v>
+        <v>4.4991511035653652E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14643,50 +14643,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.23475196908961898</v>
+        <v>0.23435340887045156</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.28135014283055559</v>
+        <v>0.28087246856428982</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.28264769642771115</v>
+        <v>0.28216781918420064</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.28639914081822559</v>
+        <v>0.28591289439917938</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.30613055127591765</v>
+        <v>0.30561080500889576</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.2905435351939985</v>
+        <v>0.29005025245173366</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.25322147305247039</v>
+        <v>0.25279155544117587</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.21870327278492194</v>
+        <v>0.21833195992790169</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.18985828792954262</v>
+        <v>0.18953594788212405</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.21404108493899077</v>
+        <v>0.21367768751125055</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.19449591640139513</v>
+        <v>0.19416570262142674</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14700,43 +14700,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15859420472741587</v>
+        <v>0.15832494461752211</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15892780289198424</v>
+        <v>0.1586579764015055</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18913583300872888</v>
+        <v>0.18881471954012324</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17153904148137317</v>
+        <v>0.17124780371994469</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13851691641811609</v>
+        <v>0.13828174338514815</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13651328081619921</v>
+        <v>0.13628150954146884</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12534490545393123</v>
+        <v>0.12513209576725223</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11816128853592488</v>
+        <v>0.11796067514282484</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1111864262975871</v>
+        <v>0.11099765477585945</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10366102475698614</v>
+        <v>0.10348502980833252</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.52</v>
+        <v>-23.56</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18926,7 +18926,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.52</v>
+        <v>23.56</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.52</v>
+        <v>23.56</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.8803734132347323E-2</v>
+        <v>8.8161349768844932E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9863D5D7-CC72-4736-A265-110424BFAEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59EE462-CC50-4ACC-BAB2-7DB52F4809FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.56</v>
+        <v>23.8</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>489442.77345051995</v>
+        <v>494428.60815460002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.8161349768844932E-2</v>
+        <v>8.4338176800193398E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.23435340887045156</v>
+        <v>0.23199018121797638</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.4991511035653652E-2</v>
+        <v>4.4537815126050422E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>452</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13444,12 +13444,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.4991511035653652E-2</v>
+        <v>4.4537815126050422E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.4991511035653652E-2</v>
+        <v>4.4537815126050422E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14643,50 +14643,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.23435340887045156</v>
+        <v>0.23199018121797638</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.28087246856428982</v>
+        <v>0.2780401411501961</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.28216781918420064</v>
+        <v>0.27932242941091456</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.28591289439917938</v>
+        <v>0.28302973916154056</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.30561080500889576</v>
+        <v>0.30252901537855392</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.29005025245173366</v>
+        <v>0.28712537595642201</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.25279155544117587</v>
+        <v>0.25024239689891187</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.21833195992790169</v>
+        <v>0.21613029310509932</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.18953594788212405</v>
+        <v>0.18762466101272446</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.21367768751125055</v>
+        <v>0.21152295452794381</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>0.19416570262142674</v>
+        <v>0.19220772914961401</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14700,43 +14700,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15832494461752211</v>
+        <v>0.15672839055415214</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1586579764015055</v>
+        <v>0.15705806403443148</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18881471954012324</v>
+        <v>0.18691070556156733</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17124780371994469</v>
+        <v>0.16952093511100405</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13828174338514815</v>
+        <v>0.13688730563672646</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13628150954146884</v>
+        <v>0.13490724221836156</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12513209576725223</v>
+        <v>0.12387025950741437</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11796067514282484</v>
+        <v>0.11677115572961987</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11099765477585945</v>
+        <v>0.10987835069408605</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10348502980833252</v>
+        <v>0.10244148328925688</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.56</v>
+        <v>-23.8</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18926,7 +18926,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.56</v>
+        <v>23.8</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.56</v>
+        <v>23.8</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.8161349768844932E-2</v>
+        <v>8.4338176800193398E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59EE462-CC50-4ACC-BAB2-7DB52F4809FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50BD947-08B7-4878-8A76-8C4D7CAB7DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -465,10 +466,6 @@
   <si>
     <t>PV of FCFE</t>
     <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HGP</t>
@@ -1497,14 +1494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dividend/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2457,6 +2446,18 @@
     <t>LT AR and Prepayments</t>
   </si>
   <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
     <t>CN</t>
   </si>
   <si>
@@ -2470,9 +2471,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
@@ -3149,7 +3147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3894,6 +3892,10 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4223,10 +4225,10 @@
   <dimension ref="A1:J197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4238,18 +4240,18 @@
         <v>45794</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4263,7 +4265,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4272,10 +4274,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4289,7 +4291,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4299,7 +4301,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4312,20 +4314,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4341,17 +4343,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4365,7 +4367,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4391,35 +4393,35 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
-        <v>359</v>
-      </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="360" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4427,7 +4429,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4439,26 +4441,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4479,7 +4481,7 @@
         <v>26.888151196428591</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4492,7 +4494,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4503,7 +4505,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4511,7 +4513,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4522,15 +4524,15 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4541,7 +4543,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F30" s="312">
         <v>0.187</v>
@@ -4549,7 +4551,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4560,7 +4562,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F31" s="312">
         <v>0.06</v>
@@ -4568,7 +4570,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4579,7 +4581,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4591,7 +4593,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4599,45 +4601,45 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
-        <v>360</v>
-      </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
-        <v>339</v>
-      </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="360" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="363" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+    <row r="40" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B40" s="361" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4652,18 +4654,18 @@
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="361" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4676,7 +4678,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4688,17 +4690,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="B47" s="361" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4710,17 +4712,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="B50" s="361" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4735,7 +4737,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4750,7 +4752,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4763,12 +4765,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4780,17 +4782,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="B58" s="361" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4802,17 +4804,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
-        <v>338</v>
-      </c>
-      <c r="C61" s="360"/>
-      <c r="D61" s="360"/>
-      <c r="E61" s="360"/>
-      <c r="F61" s="360"/>
+      <c r="B61" s="361" t="s">
+        <v>335</v>
+      </c>
+      <c r="C61" s="362"/>
+      <c r="D61" s="362"/>
+      <c r="E61" s="362"/>
+      <c r="F61" s="362"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4823,27 +4825,27 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
-        <v>343</v>
-      </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
-        <v>361</v>
-      </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+    <row r="64" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B64" s="360" t="s">
+        <v>340</v>
+      </c>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B65" s="360" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4856,7 +4858,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4869,24 +4871,24 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C69" s="92">
-        <f>Normalized_FCF!C125</f>
+        <f>Normalized_FCF!C126</f>
         <v>0.23199018121797638</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>308</v>
+        <v>458</v>
       </c>
       <c r="C70" s="92">
-        <f>Normalized_FCF!C93</f>
+        <f>Normalized_FCF!C94</f>
         <v>4.4537815126050422E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4895,73 +4897,73 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
+        <v>451</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>453</v>
+      </c>
+      <c r="D72" s="323" t="s">
         <v>454</v>
-      </c>
-      <c r="C72" s="323" t="s">
-        <v>456</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C73" s="92">
-        <f>Normalized_FCF!C120</f>
+        <f>Normalized_FCF!C121</f>
         <v>0.17249144202566888</v>
       </c>
       <c r="D73" s="92">
-        <f>Normalized_FCF!G120</f>
+        <f>Normalized_FCF!G121</f>
         <v>0.16493306371564362</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B117</f>
+        <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
       <c r="C74" s="322">
-        <f>Normalized_FCF!C117</f>
+        <f>Normalized_FCF!C118</f>
         <v>0.71319953730480046</v>
       </c>
       <c r="D74" s="322">
-        <f>Normalized_FCF!G117</f>
+        <f>Normalized_FCF!G118</f>
         <v>0.7018481216398329</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
+        <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
       </c>
       <c r="C75" s="324">
-        <f>Normalized_FCF!C118</f>
+        <f>Normalized_FCF!C119</f>
         <v>2.0567862383133143E-2</v>
       </c>
       <c r="D75" s="324">
-        <f>Normalized_FCF!G118</f>
+        <f>Normalized_FCF!G119</f>
         <v>1.9984681998245511E-2</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
+        <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
       </c>
       <c r="C76" s="324">
-        <f>Normalized_FCF!C119</f>
+        <f>Normalized_FCF!C120</f>
         <v>11.758917470801054</v>
       </c>
       <c r="D76" s="324">
-        <f>Normalized_FCF!G119</f>
+        <f>Normalized_FCF!G120</f>
         <v>11.758917470801054</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4972,33 +4974,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1">
+    <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
-        <v>362</v>
-      </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="B80" s="360" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
-        <v>252</v>
-      </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="B81" s="363" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5007,7 +5009,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5016,7 +5018,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5028,31 +5030,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
-        <v>363</v>
-      </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
-        <v>364</v>
-      </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+    <row r="89" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B89" s="360" t="s">
+        <v>360</v>
+      </c>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B90" s="360" t="s">
+        <v>361</v>
+      </c>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5060,7 +5062,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5073,7 +5075,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5085,36 +5087,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
-        <v>365</v>
-      </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="B97" s="360" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
-        <v>344</v>
-      </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B101" s="360" t="s">
+        <v>341</v>
+      </c>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5127,7 +5129,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5140,7 +5142,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C104" s="325" t="str">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5149,7 +5151,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C105" s="326" t="str">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5158,12 +5160,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5176,7 +5178,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5189,7 +5191,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5202,12 +5204,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5220,7 +5222,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5231,18 +5233,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
-        <v>366</v>
-      </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+    <row r="116" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B116" s="360" t="s">
+        <v>363</v>
+      </c>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5255,7 +5257,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5268,7 +5270,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5276,30 +5278,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
-        <v>367</v>
-      </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+    <row r="123" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B123" s="361" t="s">
+        <v>364</v>
+      </c>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5414,7 +5416,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5425,18 +5427,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
-        <v>370</v>
-      </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+    <row r="134" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B134" s="364" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5445,31 +5447,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
-        <v>368</v>
-      </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
-        <v>369</v>
-      </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="B138" s="365" t="s">
+        <v>365</v>
+      </c>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="360" t="s">
+        <v>366</v>
+      </c>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5478,16 +5480,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
@@ -5500,7 +5502,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5513,11 +5515,11 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5527,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.829322250329541</v>
+        <v>1.8293222503295408</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5542,7 +5544,7 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
@@ -5555,7 +5557,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5568,7 +5570,7 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
@@ -5577,12 +5579,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5611,7 +5613,7 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
@@ -5624,7 +5626,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5637,7 +5639,7 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
@@ -5646,12 +5648,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5680,7 +5682,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5693,7 +5695,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5706,7 +5708,7 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
@@ -5715,12 +5717,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5749,7 +5751,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5762,7 +5764,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5775,7 +5777,7 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
@@ -5784,7 +5786,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5793,98 +5795,98 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
-        <v>376</v>
-      </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="B179" s="359" t="s">
+        <v>373</v>
+      </c>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="360" t="s">
-        <v>380</v>
-      </c>
-      <c r="C182" s="360"/>
-      <c r="D182" s="360"/>
-      <c r="E182" s="360"/>
-      <c r="F182" s="360"/>
+      <c r="B182" s="362" t="s">
+        <v>377</v>
+      </c>
+      <c r="C182" s="362"/>
+      <c r="D182" s="362"/>
+      <c r="E182" s="362"/>
+      <c r="F182" s="362"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
-        <v>381</v>
-      </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="B188" s="361" t="s">
+        <v>378</v>
+      </c>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
-        <v>383</v>
-      </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+    </row>
+    <row r="191" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B191" s="358" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B192" s="358" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5922,7 +5924,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -5946,12 +5948,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
@@ -6209,7 +6211,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6225,7 +6227,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6241,7 +6243,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6491,7 +6493,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C22" s="351">
         <v>-237258</v>
@@ -6527,7 +6529,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C23" s="351">
         <v>23438</v>
@@ -6563,7 +6565,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C24" s="351">
         <v>194894</v>
@@ -6622,7 +6624,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6739,7 +6741,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -7140,7 +7142,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7189,7 +7191,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7537,12 +7539,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7591,7 +7593,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7640,7 +7642,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7689,7 +7691,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7891,7 +7893,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8143,7 +8145,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8509,15 +8511,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8538,7 +8540,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8549,19 +8551,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="183" t="s">
         <v>35</v>
@@ -8622,7 +8624,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8643,7 +8645,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G7" s="19">
         <f>6731</f>
@@ -8655,7 +8657,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8665,7 +8667,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8686,7 +8688,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8750,19 +8752,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="183" t="s">
         <v>35</v>
@@ -8770,7 +8772,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8800,7 +8802,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8820,7 +8822,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G17" s="19">
         <f>923189+1896064+630916+4011+114913</f>
@@ -8832,7 +8834,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8841,7 +8843,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8862,7 +8864,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="19">
         <v>3917</v>
@@ -8882,7 +8884,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8902,7 +8904,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -8962,16 +8964,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26" s="186" t="s">
         <v>35</v>
@@ -9005,7 +9007,7 @@
         <v>9304</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G28" s="12">
         <v>11703</v>
@@ -9050,7 +9052,7 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
@@ -9100,10 +9102,10 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H34" s="198" t="s">
         <v>35</v>
@@ -9111,10 +9113,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="199" t="s">
         <v>31</v>
@@ -9136,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9152,7 +9154,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9168,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9197,14 +9199,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>0</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9224,7 +9226,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9243,7 +9245,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9267,13 +9269,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -9281,7 +9283,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9313,7 +9315,7 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" s="235" t="s">
         <v>57</v>
@@ -9340,7 +9342,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9354,7 +9356,7 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" s="235" t="s">
         <v>57</v>
@@ -9366,7 +9368,7 @@
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9380,7 +9382,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9397,7 +9399,7 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" s="235" t="s">
         <v>57</v>
@@ -9434,10 +9436,10 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" s="197" t="s">
         <v>95</v>
@@ -9446,7 +9448,7 @@
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9457,12 +9459,12 @@
         <v>1.3270091664890215E-2</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9473,13 +9475,13 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>59</v>
@@ -9487,7 +9489,7 @@
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9498,12 +9500,12 @@
         <v>0</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9513,7 +9515,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9523,7 +9525,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9533,7 +9535,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9546,7 +9548,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>95</v>
@@ -9558,7 +9560,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9569,12 +9571,12 @@
         <v>-7000.4599952516664</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9585,12 +9587,12 @@
         <v>962.32333369084779</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9598,12 +9600,12 @@
         <v>6736706</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9611,7 +9613,7 @@
         <v>962.32333369084779</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9619,10 +9621,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>35</v>
@@ -9631,7 +9633,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9645,7 +9647,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9659,7 +9661,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9673,7 +9675,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9687,7 +9689,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9698,15 +9700,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D85" s="241" t="s">
         <v>289</v>
-      </c>
-      <c r="D85" s="241" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9723,7 +9725,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9740,7 +9742,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9757,7 +9759,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9785,17 +9787,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:Q809"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
@@ -10117,7 +10119,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10284,7 +10286,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10396,7 +10398,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10506,7 +10508,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10563,7 +10565,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10628,7 +10630,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10653,7 +10655,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10747,7 +10749,7 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
@@ -10966,7 +10968,7 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="268"/>
     </row>
@@ -10981,7 +10983,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11041,7 +11043,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11158,14 +11160,14 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C33" s="340">
         <f>AVERAGE(G33:J33)</f>
         <v>-61984.75</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11223,7 +11225,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11335,7 +11337,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11517,21 +11519,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11585,7 +11587,7 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
@@ -11670,7 +11672,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11725,7 +11727,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11841,11 +11843,11 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
@@ -11858,7 +11860,7 @@
         <v>5.1039038960584003E-2</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11885,7 +11887,7 @@
         <v>2.0566860106198924E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11964,17 +11966,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12029,7 +12031,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12084,7 +12086,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12139,7 +12141,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12194,13 +12196,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12250,7 +12252,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12309,17 +12311,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12344,7 +12346,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12369,7 +12371,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12394,7 +12396,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12424,12 +12426,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>464</v>
+        <v>59</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12447,7 +12449,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12639,7 +12641,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12812,7 +12814,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12926,7 +12928,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13098,7 +13100,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13205,7 +13207,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13266,7 +13268,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13385,7 +13387,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13440,606 +13442,570 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C93" s="23">
-        <f>C90/Market_Price</f>
+        <v>457</v>
+      </c>
+      <c r="C93" s="356">
+        <v>0</v>
+      </c>
+      <c r="E93" s="268"/>
+      <c r="G93" s="357"/>
+      <c r="H93" s="357"/>
+      <c r="I93" s="357"/>
+      <c r="J93" s="357"/>
+      <c r="K93" s="357"/>
+      <c r="L93" s="357"/>
+      <c r="M93" s="357"/>
+      <c r="N93" s="357"/>
+      <c r="O93" s="357"/>
+      <c r="P93" s="357"/>
+      <c r="Q93" s="357"/>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A94" s="10"/>
+      <c r="B94" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C94" s="23">
+        <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
         <v>4.4537815126050422E-2</v>
       </c>
-      <c r="E93" s="268"/>
-      <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
+      <c r="E94" s="268"/>
+      <c r="G94" s="23">
+        <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
         <v>4.4537815126050422E-2</v>
       </c>
-      <c r="H93" s="23">
+      <c r="H94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="I93" s="23">
+      <c r="I94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="J93" s="23">
+      <c r="J94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="K93" s="23">
+      <c r="K94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="L93" s="23">
+      <c r="L94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="M93" s="23">
+      <c r="M94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N93" s="23">
+      <c r="N94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="O93" s="23">
+      <c r="O94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="P93" s="23">
+      <c r="P94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="Q93" s="23" t="str">
+      <c r="Q94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A94" s="10"/>
-      <c r="E94" s="268"/>
-    </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
-      <c r="B95" s="157" t="s">
-        <v>84</v>
-      </c>
-      <c r="C95" s="62"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="265"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
+      <c r="E95" s="268"/>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
-      <c r="B96" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C96" s="77">
-        <f>C4/G4-1</f>
-        <v>9.9014380352237863E-2</v>
-      </c>
+      <c r="B96" s="157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="62"/>
       <c r="D96" s="27"/>
       <c r="E96" s="265"/>
       <c r="F96" s="27"/>
-      <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>-1.9190762631230429E-3</v>
-      </c>
-      <c r="H96" s="6">
-        <f t="shared" si="40"/>
-        <v>-0.17125750103577775</v>
-      </c>
-      <c r="I96" s="6">
-        <f t="shared" si="40"/>
-        <v>2.0081799591002092E-2</v>
-      </c>
-      <c r="J96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.27485400444938812</v>
-      </c>
-      <c r="K96" s="6">
-        <f t="shared" si="40"/>
-        <v>-0.24852411054803825</v>
-      </c>
-      <c r="L96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.25059619091176377</v>
-      </c>
-      <c r="M96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.21114166452353156</v>
-      </c>
-      <c r="N96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.29367354250908528</v>
-      </c>
-      <c r="O96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.81242172642515897</v>
-      </c>
-      <c r="P96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="Q96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
     </row>
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
-      <c r="B97" s="70" t="s">
-        <v>164</v>
+      <c r="B97" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="C97" s="77">
-        <f>C13/G13-1</f>
-        <v>4.5826944214511611E-2</v>
+        <f>C4/G4-1</f>
+        <v>9.9014380352237863E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <f t="shared" ref="G97:Q97" si="40">IF(H4="","",G4/H4-1)</f>
+        <v>-1.9190762631230429E-3</v>
+      </c>
+      <c r="H97" s="6">
+        <f t="shared" si="40"/>
+        <v>-0.17125750103577775</v>
+      </c>
+      <c r="I97" s="6">
+        <f t="shared" si="40"/>
+        <v>2.0081799591002092E-2</v>
+      </c>
+      <c r="J97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.27485400444938812</v>
+      </c>
+      <c r="K97" s="6">
+        <f t="shared" si="40"/>
+        <v>-0.24852411054803825</v>
+      </c>
+      <c r="L97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.25059619091176377</v>
+      </c>
+      <c r="M97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.21114166452353156</v>
+      </c>
+      <c r="N97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.29367354250908528</v>
+      </c>
+      <c r="O97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.81242172642515897</v>
+      </c>
+      <c r="P97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="Q97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A98" s="10"/>
+      <c r="B98" s="70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C98" s="77">
+        <f>C13/G13-1</f>
+        <v>4.5826944214511611E-2</v>
+      </c>
+      <c r="D98" s="27"/>
+      <c r="E98" s="265"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="6">
+        <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
         <v>1.423085921909184E-2</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H98" s="6">
         <f t="shared" si="41"/>
         <v>-6.1144060678890333E-2</v>
       </c>
-      <c r="I97" s="6">
+      <c r="I98" s="6">
         <f t="shared" si="41"/>
         <v>-4.5786608634539427E-2</v>
       </c>
-      <c r="J97" s="6">
+      <c r="J98" s="6">
         <f t="shared" si="41"/>
         <v>6.7347046205271877E-2</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K98" s="6">
         <f t="shared" si="41"/>
         <v>0.14816941418231822</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L98" s="6">
         <f t="shared" si="41"/>
         <v>0.15784041008415128</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M98" s="6">
         <f t="shared" si="41"/>
         <v>0.13953349282296656</v>
       </c>
-      <c r="N97" s="6">
+      <c r="N98" s="6">
         <f t="shared" si="41"/>
         <v>-0.12505014913917911</v>
       </c>
-      <c r="O97" s="6">
+      <c r="O98" s="6">
         <f t="shared" si="41"/>
         <v>6.0960488572221694E-2</v>
       </c>
-      <c r="P97" s="6" t="str">
+      <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="Q97" s="6" t="str">
+      <c r="Q98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A98" s="10"/>
-    </row>
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="C99" s="54"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="66" t="s">
+      <c r="A99" s="10"/>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A100" s="3"/>
+      <c r="B100" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="54"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="F99" s="56"/>
-      <c r="G99" s="37"/>
-      <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
-      <c r="J99" s="37"/>
-      <c r="K99" s="37"/>
-      <c r="L99" s="37"/>
-      <c r="M99" s="37"/>
-      <c r="N99" s="37"/>
-      <c r="O99" s="37"/>
-      <c r="P99" s="37"/>
-      <c r="Q99" s="37"/>
-    </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A100" s="10"/>
-      <c r="B100" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" s="268"/>
-      <c r="G100" s="97" t="s">
-        <v>219</v>
-      </c>
+      <c r="F100" s="56"/>
+      <c r="G100" s="37"/>
+      <c r="H100" s="37"/>
+      <c r="I100" s="37"/>
+      <c r="J100" s="37"/>
+      <c r="K100" s="37"/>
+      <c r="L100" s="37"/>
+      <c r="M100" s="37"/>
+      <c r="N100" s="37"/>
+      <c r="O100" s="37"/>
+      <c r="P100" s="37"/>
+      <c r="Q100" s="37"/>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
-      <c r="B101" s="26" t="s">
+      <c r="B101" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="268"/>
+      <c r="G101" s="97" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A102" s="10"/>
+      <c r="B102" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="344">
+      <c r="C102" s="344">
         <f>BS!G32</f>
         <v>10507898</v>
       </c>
-      <c r="D101" s="26"/>
-      <c r="E101" s="269"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="333">
-        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
+      <c r="D102" s="26"/>
+      <c r="E102" s="269"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="333">
+        <f t="shared" ref="G102:Q102" si="42">IF(G$4="","",G106+G105)</f>
         <v>10507898</v>
       </c>
-      <c r="H101" s="333">
+      <c r="H102" s="333">
         <f t="shared" si="42"/>
         <v>10158326</v>
       </c>
-      <c r="I101" s="333">
+      <c r="I102" s="333">
         <f t="shared" si="42"/>
         <v>9266671</v>
       </c>
-      <c r="J101" s="333">
+      <c r="J102" s="333">
         <f t="shared" si="42"/>
         <v>8603024</v>
       </c>
-      <c r="K101" s="333">
+      <c r="K102" s="333">
         <f t="shared" si="42"/>
         <v>7894000</v>
       </c>
-      <c r="L101" s="333">
+      <c r="L102" s="333">
         <f t="shared" si="42"/>
         <v>7145681</v>
       </c>
-      <c r="M101" s="333">
+      <c r="M102" s="333">
         <f t="shared" si="42"/>
         <v>6711657</v>
       </c>
-      <c r="N101" s="333">
+      <c r="N102" s="333">
         <f t="shared" si="42"/>
         <v>6416842</v>
       </c>
-      <c r="O101" s="333">
+      <c r="O102" s="333">
         <f t="shared" si="42"/>
         <v>6085895</v>
       </c>
-      <c r="P101" s="333">
+      <c r="P102" s="333">
         <f t="shared" si="42"/>
         <v>5298880</v>
       </c>
-      <c r="Q101" s="333" t="str">
+      <c r="Q102" s="333" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A102" s="10"/>
-      <c r="B102" s="93" t="s">
-        <v>210</v>
-      </c>
-      <c r="C102" s="345">
-        <f>BS!C4</f>
-        <v>0</v>
-      </c>
-      <c r="D102" s="89"/>
-      <c r="E102" s="270"/>
-      <c r="F102" s="89"/>
-      <c r="G102" s="346">
-        <f>IF(G$4="","",Data!D77)</f>
-        <v>0</v>
-      </c>
-      <c r="H102" s="346">
-        <f>IF(H$4="","",Data!E77)</f>
-        <v>0</v>
-      </c>
-      <c r="I102" s="346">
-        <f>IF(I$4="","",Data!F77)</f>
-        <v>0</v>
-      </c>
-      <c r="J102" s="346">
-        <f>IF(J$4="","",Data!G77)</f>
-        <v>0</v>
-      </c>
-      <c r="K102" s="346">
-        <f>IF(K$4="","",Data!H77)</f>
-        <v>0</v>
-      </c>
-      <c r="L102" s="346">
-        <f>IF(L$4="","",Data!I77)</f>
-        <v>0</v>
-      </c>
-      <c r="M102" s="346">
-        <f>IF(M$4="","",Data!J77)</f>
-        <v>0</v>
-      </c>
-      <c r="N102" s="346">
-        <f>IF(N$4="","",Data!K77)</f>
-        <v>0</v>
-      </c>
-      <c r="O102" s="346">
-        <f>IF(O$4="","",Data!L77)</f>
-        <v>0</v>
-      </c>
-      <c r="P102" s="346">
-        <f>IF(P$4="","",Data!M77)</f>
-        <v>0</v>
-      </c>
-      <c r="Q102" s="346" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C103" s="345">
-        <f>BS!C6+BS!C7</f>
+        <f>BS!C4</f>
         <v>0</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
       <c r="G103" s="346">
-        <f>IF(G$4="","",Data!D78)</f>
+        <f>IF(G$4="","",Data!D77)</f>
         <v>0</v>
       </c>
       <c r="H103" s="346">
-        <f>IF(H$4="","",Data!E78)</f>
+        <f>IF(H$4="","",Data!E77)</f>
         <v>0</v>
       </c>
       <c r="I103" s="346">
-        <f>IF(I$4="","",Data!F78)</f>
+        <f>IF(I$4="","",Data!F77)</f>
         <v>0</v>
       </c>
       <c r="J103" s="346">
-        <f>IF(J$4="","",Data!G78)</f>
+        <f>IF(J$4="","",Data!G77)</f>
         <v>0</v>
       </c>
       <c r="K103" s="346">
-        <f>IF(K$4="","",Data!H78)</f>
+        <f>IF(K$4="","",Data!H77)</f>
         <v>0</v>
       </c>
       <c r="L103" s="346">
-        <f>IF(L$4="","",Data!I78)</f>
+        <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
       <c r="M103" s="346">
-        <f>IF(M$4="","",Data!J78)</f>
+        <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
       <c r="N103" s="346">
-        <f>IF(N$4="","",Data!K78)</f>
+        <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
       <c r="O103" s="346">
-        <f>IF(O$4="","",Data!L78)</f>
+        <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
       <c r="P103" s="346">
-        <f>IF(P$4="","",Data!M78)</f>
+        <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
       <c r="Q103" s="346" t="str">
-        <f>IF(Q$4="","",Data!N78)</f>
+        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
-      <c r="B104" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C104" s="344">
-        <f>BS!G30</f>
-        <v>9614287</v>
-      </c>
-      <c r="D104" s="26"/>
-      <c r="E104" s="269"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="333">
-        <f>Data!C79</f>
-        <v>9614287</v>
-      </c>
-      <c r="H104" s="333">
-        <f>Data!D79</f>
-        <v>9350607</v>
-      </c>
-      <c r="I104" s="333">
-        <f>Data!E79</f>
-        <v>8509373</v>
-      </c>
-      <c r="J104" s="333">
-        <f>Data!F79</f>
-        <v>7908726</v>
-      </c>
-      <c r="K104" s="333">
-        <f>Data!G79</f>
-        <v>7269197</v>
-      </c>
-      <c r="L104" s="333">
-        <f>Data!H79</f>
-        <v>6596029</v>
-      </c>
-      <c r="M104" s="333">
-        <f>Data!I79</f>
-        <v>6239073</v>
-      </c>
-      <c r="N104" s="333">
-        <f>Data!J79</f>
-        <v>5994090</v>
-      </c>
-      <c r="O104" s="333">
-        <f>Data!K79</f>
-        <v>5731485</v>
-      </c>
-      <c r="P104" s="333">
-        <f>Data!L79</f>
-        <v>4981503</v>
-      </c>
-      <c r="Q104" s="333" t="str">
-        <f>Data!M79</f>
+      <c r="B104" s="93" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="345">
+        <f>BS!C6+BS!C7</f>
+        <v>0</v>
+      </c>
+      <c r="D104" s="89"/>
+      <c r="E104" s="270"/>
+      <c r="F104" s="89"/>
+      <c r="G104" s="346">
+        <f>IF(G$4="","",Data!D78)</f>
+        <v>0</v>
+      </c>
+      <c r="H104" s="346">
+        <f>IF(H$4="","",Data!E78)</f>
+        <v>0</v>
+      </c>
+      <c r="I104" s="346">
+        <f>IF(I$4="","",Data!F78)</f>
+        <v>0</v>
+      </c>
+      <c r="J104" s="346">
+        <f>IF(J$4="","",Data!G78)</f>
+        <v>0</v>
+      </c>
+      <c r="K104" s="346">
+        <f>IF(K$4="","",Data!H78)</f>
+        <v>0</v>
+      </c>
+      <c r="L104" s="346">
+        <f>IF(L$4="","",Data!I78)</f>
+        <v>0</v>
+      </c>
+      <c r="M104" s="346">
+        <f>IF(M$4="","",Data!J78)</f>
+        <v>0</v>
+      </c>
+      <c r="N104" s="346">
+        <f>IF(N$4="","",Data!K78)</f>
+        <v>0</v>
+      </c>
+      <c r="O104" s="346">
+        <f>IF(O$4="","",Data!L78)</f>
+        <v>0</v>
+      </c>
+      <c r="P104" s="346">
+        <f>IF(P$4="","",Data!M78)</f>
+        <v>0</v>
+      </c>
+      <c r="Q104" s="346" t="str">
+        <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C105" s="344">
-        <f>BS!G27</f>
-        <v>893611</v>
+        <f>BS!G30</f>
+        <v>9614287</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
       <c r="G105" s="333">
+        <f>Data!C79</f>
+        <v>9614287</v>
+      </c>
+      <c r="H105" s="333">
+        <f>Data!D79</f>
+        <v>9350607</v>
+      </c>
+      <c r="I105" s="333">
+        <f>Data!E79</f>
+        <v>8509373</v>
+      </c>
+      <c r="J105" s="333">
+        <f>Data!F79</f>
+        <v>7908726</v>
+      </c>
+      <c r="K105" s="333">
+        <f>Data!G79</f>
+        <v>7269197</v>
+      </c>
+      <c r="L105" s="333">
+        <f>Data!H79</f>
+        <v>6596029</v>
+      </c>
+      <c r="M105" s="333">
+        <f>Data!I79</f>
+        <v>6239073</v>
+      </c>
+      <c r="N105" s="333">
+        <f>Data!J79</f>
+        <v>5994090</v>
+      </c>
+      <c r="O105" s="333">
+        <f>Data!K79</f>
+        <v>5731485</v>
+      </c>
+      <c r="P105" s="333">
+        <f>Data!L79</f>
+        <v>4981503</v>
+      </c>
+      <c r="Q105" s="333" t="str">
+        <f>Data!M79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A106" s="10"/>
+      <c r="B106" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="344">
+        <f>BS!G27</f>
+        <v>893611</v>
+      </c>
+      <c r="D106" s="26"/>
+      <c r="E106" s="269"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="333">
         <f>Data!C80</f>
         <v>893611</v>
       </c>
-      <c r="H105" s="333">
+      <c r="H106" s="333">
         <f>Data!D80</f>
         <v>807719</v>
       </c>
-      <c r="I105" s="333">
+      <c r="I106" s="333">
         <f>Data!E80</f>
         <v>757298</v>
       </c>
-      <c r="J105" s="333">
+      <c r="J106" s="333">
         <f>Data!F80</f>
         <v>694298</v>
       </c>
-      <c r="K105" s="333">
+      <c r="K106" s="333">
         <f>Data!G80</f>
         <v>624803</v>
       </c>
-      <c r="L105" s="333">
+      <c r="L106" s="333">
         <f>Data!H80</f>
         <v>549652</v>
       </c>
-      <c r="M105" s="333">
+      <c r="M106" s="333">
         <f>Data!I80</f>
         <v>472584</v>
       </c>
-      <c r="N105" s="333">
+      <c r="N106" s="333">
         <f>Data!J80</f>
         <v>422752</v>
       </c>
-      <c r="O105" s="333">
+      <c r="O106" s="333">
         <f>Data!K80</f>
         <v>354410</v>
       </c>
-      <c r="P105" s="333">
+      <c r="P106" s="333">
         <f>Data!L80</f>
         <v>317377</v>
       </c>
-      <c r="Q105" s="333" t="str">
+      <c r="Q106" s="333" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A106" s="10"/>
-      <c r="E106" s="268"/>
-    </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
-      <c r="B107" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="269"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="97" t="s">
-        <v>219</v>
-      </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
-      <c r="L107" s="12"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="12"/>
-      <c r="O107" s="12"/>
-      <c r="P107" s="12"/>
-      <c r="Q107" s="12"/>
+      <c r="E107" s="268"/>
     </row>
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
-      <c r="B108" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="94">
-        <f>C102/C$4</f>
-        <v>0</v>
-      </c>
+      <c r="B108" s="91" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
-      <c r="G108" s="94">
-        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>0</v>
-      </c>
-      <c r="H108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="I108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="J108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="K108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="L108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="N108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="O108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Q108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
+      <c r="G108" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="12"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+      <c r="N108" s="12"/>
+      <c r="O108" s="12"/>
+      <c r="P108" s="12"/>
+      <c r="Q108" s="12"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -14049,701 +14015,757 @@
       <c r="E109" s="269"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
-        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
+        <f t="shared" ref="G109:Q109" si="43">IF(G$4="","",G103/G$4)</f>
         <v>0</v>
       </c>
       <c r="H109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="I109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="J109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="K109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="L109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="O109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Q109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="C110" s="94">
-        <f>BS!$G$38/C$4</f>
+        <f>C104/C$4</f>
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
       <c r="E110" s="269"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
-        <f>BS!$G$38/G$4</f>
-        <v>0</v>
-      </c>
-      <c r="H110" s="204"/>
-      <c r="I110" s="204"/>
-      <c r="J110" s="204"/>
-      <c r="K110" s="204"/>
-      <c r="L110" s="204"/>
-      <c r="M110" s="204"/>
-      <c r="N110" s="204"/>
-      <c r="O110" s="204"/>
-      <c r="P110" s="204"/>
-      <c r="Q110" s="204"/>
+        <f t="shared" ref="G110:Q110" si="44">IF(G$4="","",G104/G$4)</f>
+        <v>0</v>
+      </c>
+      <c r="H110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="I110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="J110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="K110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="L110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="N110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="O110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="P110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="268"/>
+      <c r="B111" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="94">
+        <f>BS!$G$38/C$4</f>
+        <v>0</v>
+      </c>
+      <c r="D111" s="26"/>
+      <c r="E111" s="269"/>
+      <c r="F111" s="26"/>
+      <c r="G111" s="94">
+        <f>BS!$G$38/G$4</f>
+        <v>0</v>
+      </c>
+      <c r="H111" s="204"/>
+      <c r="I111" s="204"/>
+      <c r="J111" s="204"/>
+      <c r="K111" s="204"/>
+      <c r="L111" s="204"/>
+      <c r="M111" s="204"/>
+      <c r="N111" s="204"/>
+      <c r="O111" s="204"/>
+      <c r="P111" s="204"/>
+      <c r="Q111" s="204"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
-      <c r="B112" s="64" t="s">
-        <v>51</v>
-      </c>
       <c r="E112" s="268"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
-      <c r="B113" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C113" s="169"/>
+      <c r="B113" s="64" t="s">
+        <v>51</v>
+      </c>
       <c r="E113" s="268"/>
-      <c r="G113" s="295">
-        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>-3.0617491063478339</v>
-      </c>
-      <c r="H113" s="295">
-        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
-        <v>5.5839621912586601</v>
-      </c>
-      <c r="I113" s="295">
-        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v>-3.7287315774666174</v>
-      </c>
-      <c r="J113" s="295">
-        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v>-4.6503173618402212</v>
-      </c>
-      <c r="K113" s="295">
-        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v>-0.50572538821825919</v>
-      </c>
-      <c r="L113" s="295">
-        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
-        <v>-8.8154628047135013</v>
-      </c>
-      <c r="M113" s="295">
-        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
-        <v>-5.8143358641521754</v>
-      </c>
-      <c r="N113" s="295">
-        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
-        <v>-2.817043387892959</v>
-      </c>
-      <c r="O113" s="295">
-        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
-        <v>3.7369447972463048</v>
-      </c>
-      <c r="P113" s="295">
-        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
-        <v>16.163731490621917</v>
-      </c>
-      <c r="Q113" s="295" t="str">
-        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
       <c r="G114" s="295">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>-3.0617491063478339</v>
+      </c>
+      <c r="H114" s="295">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>5.5839621912586601</v>
+      </c>
+      <c r="I114" s="295">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>-3.7287315774666174</v>
+      </c>
+      <c r="J114" s="295">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>-4.6503173618402212</v>
+      </c>
+      <c r="K114" s="295">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v>-0.50572538821825919</v>
+      </c>
+      <c r="L114" s="295">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v>-8.8154628047135013</v>
+      </c>
+      <c r="M114" s="295">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v>-5.8143358641521754</v>
+      </c>
+      <c r="N114" s="295">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v>-2.817043387892959</v>
+      </c>
+      <c r="O114" s="295">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v>3.7369447972463048</v>
+      </c>
+      <c r="P114" s="295">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v>16.163731490621917</v>
+      </c>
+      <c r="Q114" s="295" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A115" s="10"/>
+      <c r="B115" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C115" s="169"/>
+      <c r="E115" s="268"/>
+      <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>-1.7258767303649496</v>
       </c>
-      <c r="H114" s="295">
+      <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>3.1397632236341915</v>
       </c>
-      <c r="I114" s="295">
+      <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>-2.4624262173248153</v>
       </c>
-      <c r="J114" s="295">
+      <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>-2.6057869085901095</v>
       </c>
-      <c r="K114" s="295">
+      <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>-0.24110507667490824</v>
       </c>
-      <c r="L114" s="295">
+      <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>-4.752471166358192</v>
       </c>
-      <c r="M114" s="295">
+      <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>-3.3323569871141014</v>
       </c>
-      <c r="N114" s="295">
+      <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>-1.7532312136859012</v>
       </c>
-      <c r="O114" s="295">
+      <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.941204593480776</v>
       </c>
-      <c r="P114" s="295">
+      <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>8.6148285332463459</v>
       </c>
-      <c r="Q114" s="295" t="str">
+      <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A115" s="10"/>
-      <c r="E115" s="268"/>
-    </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
-      <c r="B116" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="55"/>
-      <c r="D116" s="55"/>
-      <c r="E116" s="271"/>
-      <c r="F116" s="55"/>
-      <c r="G116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="E116" s="268"/>
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
-      <c r="B117" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C117" s="23">
+      <c r="B117" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="271"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G119*(1/#REF!)=G121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H119*(1/#REF!)=H121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I119*(1/#REF!)=I121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J119*(1/#REF!)=J121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K119*(1/#REF!)=K121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L119*(1/#REF!)=L121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M119*(1/#REF!)=M121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N119*(1/#REF!)=N121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O119*(1/#REF!)=O121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P119*(1/#REF!)=P121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q119*(1/#REF!)=Q121,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A118" s="10"/>
+      <c r="B118" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
         <v>0.71319953730480046</v>
       </c>
-      <c r="E117" s="268"/>
-      <c r="G117" s="23">
-        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
+      <c r="E118" s="268"/>
+      <c r="G118" s="23">
+        <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
         <v>0.7018481216398329</v>
       </c>
-      <c r="H117" s="23">
+      <c r="H118" s="23">
         <f t="shared" si="45"/>
         <v>0.69692871393492939</v>
       </c>
-      <c r="I117" s="23">
+      <c r="I118" s="23">
         <f t="shared" si="45"/>
         <v>0.70324767374236696</v>
       </c>
-      <c r="J117" s="23">
+      <c r="J118" s="23">
         <f t="shared" si="45"/>
         <v>0.74058229732135927</v>
       </c>
-      <c r="K117" s="23">
+      <c r="K118" s="23">
         <f t="shared" si="45"/>
         <v>0.75589775728546493</v>
       </c>
-      <c r="L117" s="23">
+      <c r="L118" s="23">
         <f t="shared" si="45"/>
         <v>0.73717920156834793</v>
       </c>
-      <c r="M117" s="23">
+      <c r="M118" s="23">
         <f t="shared" si="45"/>
         <v>0.7287017382823705</v>
       </c>
-      <c r="N117" s="23">
+      <c r="N118" s="23">
         <f t="shared" si="45"/>
         <v>0.72172661870503596</v>
       </c>
-      <c r="O117" s="23">
+      <c r="O118" s="23">
         <f t="shared" si="45"/>
         <v>0.75735337829358029</v>
       </c>
-      <c r="P117" s="23">
+      <c r="P118" s="23">
         <f t="shared" si="45"/>
         <v>0.76432355208532243</v>
       </c>
-      <c r="Q117" s="23" t="str">
+      <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B118" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B119" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C118" s="42">
-        <f>IF(valuation_method="DDM",(C4+C12)/C101,C4/C101)</f>
+      <c r="C119" s="42">
+        <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
         <v>2.0567862383133143E-2</v>
       </c>
-      <c r="E118" s="268"/>
-      <c r="G118" s="42">
-        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
+      <c r="E119" s="268"/>
+      <c r="G119" s="42">
+        <f t="shared" ref="G119:Q119" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G102,G4/G102))</f>
         <v>1.9984681998245511E-2</v>
       </c>
-      <c r="H118" s="42">
+      <c r="H119" s="42">
         <f t="shared" si="46"/>
         <v>2.0526216622699447E-2</v>
       </c>
-      <c r="I118" s="42">
+      <c r="I119" s="42">
         <f t="shared" si="46"/>
         <v>2.3751355799725704E-2</v>
       </c>
-      <c r="J118" s="42">
+      <c r="J119" s="42">
         <f t="shared" si="46"/>
         <v>2.5459536088705551E-2</v>
       </c>
-      <c r="K118" s="42">
+      <c r="K119" s="42">
         <f t="shared" si="46"/>
         <v>2.546883709146187E-2</v>
       </c>
-      <c r="L118" s="42">
+      <c r="L119" s="42">
         <f t="shared" si="46"/>
         <v>2.5127346154971093E-2</v>
       </c>
-      <c r="M118" s="42">
+      <c r="M119" s="42">
         <f t="shared" si="46"/>
         <v>2.3374108659009244E-2</v>
       </c>
-      <c r="N118" s="42">
+      <c r="N119" s="42">
         <f t="shared" si="46"/>
         <v>2.1661745762167745E-2</v>
       </c>
-      <c r="O118" s="42">
+      <c r="O119" s="42">
         <f t="shared" si="46"/>
         <v>2.4876045347479704E-2</v>
       </c>
-      <c r="P118" s="42">
+      <c r="P119" s="42">
         <f t="shared" si="46"/>
         <v>2.6683563319041006E-2</v>
       </c>
-      <c r="Q118" s="42" t="str">
+      <c r="Q119" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B119" s="7" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B120" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C119" s="15">
-        <f>C101/C105</f>
+      <c r="C120" s="15">
+        <f>C102/C106</f>
         <v>11.758917470801054</v>
       </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="272"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D120" s="11"/>
+      <c r="E120" s="272"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="15">
+        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G102/G106)</f>
         <v>11.758917470801054</v>
       </c>
-      <c r="H119" s="15">
+      <c r="H120" s="15">
         <f t="shared" si="47"/>
         <v>12.576559422274331</v>
       </c>
-      <c r="I119" s="15">
+      <c r="I120" s="15">
         <f t="shared" si="47"/>
         <v>12.236492107466281</v>
       </c>
-      <c r="J119" s="15">
+      <c r="J120" s="15">
         <f t="shared" si="47"/>
         <v>12.39096756724058</v>
       </c>
-      <c r="K119" s="15">
+      <c r="K120" s="15">
         <f t="shared" si="47"/>
         <v>12.634382357319026</v>
       </c>
-      <c r="L119" s="15">
+      <c r="L120" s="15">
         <f t="shared" si="47"/>
         <v>13.000372963256751</v>
       </c>
-      <c r="M119" s="15">
+      <c r="M120" s="15">
         <f t="shared" si="47"/>
         <v>14.202040272205576</v>
       </c>
-      <c r="N119" s="15">
+      <c r="N120" s="15">
         <f t="shared" si="47"/>
         <v>15.178738361971085</v>
       </c>
-      <c r="O119" s="15">
+      <c r="O120" s="15">
         <f t="shared" si="47"/>
         <v>17.171905420275952</v>
       </c>
-      <c r="P119" s="15">
+      <c r="P120" s="15">
         <f t="shared" si="47"/>
         <v>16.695853826836853</v>
       </c>
-      <c r="Q119" s="15" t="str">
+      <c r="Q120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A120" s="10"/>
-      <c r="B120" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="C120" s="102">
-        <f>C13/C105</f>
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A121" s="10"/>
+      <c r="B121" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C121" s="102">
+        <f>C13/C106</f>
         <v>0.17249144202566888</v>
       </c>
-      <c r="D120" s="103"/>
-      <c r="E120" s="271"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="102">
-        <f>IF(G$4="","",G13/G105)</f>
+      <c r="D121" s="103"/>
+      <c r="E121" s="271"/>
+      <c r="F121" s="103"/>
+      <c r="G121" s="102">
+        <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
         <v>0.16493306371564362</v>
       </c>
-      <c r="H120" s="102">
-        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
+      <c r="H121" s="102">
+        <f t="shared" si="48"/>
         <v>0.17991157816022652</v>
       </c>
-      <c r="I120" s="102">
+      <c r="I121" s="102">
         <f t="shared" si="48"/>
         <v>0.20438717651439725</v>
       </c>
-      <c r="J120" s="102">
+      <c r="J121" s="102">
         <f t="shared" si="48"/>
         <v>0.23363022794246852</v>
       </c>
-      <c r="K120" s="102">
+      <c r="K121" s="102">
         <f t="shared" si="48"/>
         <v>0.24323506769333694</v>
       </c>
-      <c r="L120" s="102">
+      <c r="L121" s="102">
         <f t="shared" si="48"/>
         <v>0.2408105492202339</v>
       </c>
-      <c r="M120" s="102">
+      <c r="M121" s="102">
         <f t="shared" si="48"/>
         <v>0.24189985272459499</v>
       </c>
-      <c r="N120" s="102">
+      <c r="N121" s="102">
         <f t="shared" si="48"/>
         <v>0.2373022481265612</v>
       </c>
-      <c r="O120" s="102">
+      <c r="O121" s="102">
         <f t="shared" si="48"/>
         <v>0.32351795942552414</v>
       </c>
-      <c r="P120" s="102">
+      <c r="P121" s="102">
         <f t="shared" si="48"/>
         <v>0.34050986681454548</v>
       </c>
-      <c r="Q120" s="102" t="str">
+      <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="62"/>
-      <c r="D121" s="27"/>
-      <c r="E121" s="67"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
-      <c r="O121" s="12"/>
-      <c r="P121" s="12"/>
-      <c r="Q121" s="12"/>
-    </row>
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
-      <c r="B122" s="54" t="s">
-        <v>223</v>
-      </c>
-      <c r="C122" s="54"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="F122" s="56"/>
-      <c r="G122" s="37"/>
-      <c r="H122" s="37"/>
-      <c r="I122" s="37"/>
-      <c r="J122" s="37"/>
-      <c r="K122" s="37"/>
-      <c r="L122" s="37"/>
-      <c r="M122" s="37"/>
-      <c r="N122" s="37"/>
-      <c r="O122" s="37"/>
-      <c r="P122" s="37"/>
-      <c r="Q122" s="37"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="62"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="67"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="12"/>
     </row>
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
-      <c r="B123" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="C123" s="179"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="265"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="12"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12"/>
-      <c r="M123" s="12"/>
-      <c r="N123" s="12"/>
-      <c r="O123" s="12"/>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="12"/>
+      <c r="B123" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C123" s="54"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="56"/>
+      <c r="G123" s="37"/>
+      <c r="H123" s="37"/>
+      <c r="I123" s="37"/>
+      <c r="J123" s="37"/>
+      <c r="K123" s="37"/>
+      <c r="L123" s="37"/>
+      <c r="M123" s="37"/>
+      <c r="N123" s="37"/>
+      <c r="O123" s="37"/>
+      <c r="P123" s="37"/>
+      <c r="Q123" s="37"/>
     </row>
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
-      <c r="B124" s="27" t="str">
-        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
-        <v>FCFE per share (CNY)</v>
-      </c>
-      <c r="C124" s="177">
-        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.5213663129878379</v>
-      </c>
+      <c r="B124" s="178" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="179"/>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
-      <c r="G124" s="177">
-        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.6173553593746677</v>
-      </c>
-      <c r="H124" s="177">
-        <f t="shared" si="49"/>
-        <v>6.6478738199797665</v>
-      </c>
-      <c r="I124" s="177">
-        <f t="shared" si="49"/>
-        <v>6.7361077920446659</v>
-      </c>
-      <c r="J124" s="177">
-        <f t="shared" si="49"/>
-        <v>7.2001905660095833</v>
-      </c>
-      <c r="K124" s="177">
-        <f t="shared" si="49"/>
-        <v>6.8335839477628442</v>
-      </c>
-      <c r="L124" s="177">
-        <f t="shared" si="49"/>
-        <v>5.9557690461941029</v>
-      </c>
-      <c r="M124" s="177">
-        <f t="shared" si="49"/>
-        <v>5.1439009759013636</v>
-      </c>
-      <c r="N124" s="177">
-        <f t="shared" si="49"/>
-        <v>4.4654669321028422</v>
-      </c>
-      <c r="O124" s="177">
-        <f t="shared" si="49"/>
-        <v>5.0342463177650627</v>
-      </c>
-      <c r="P124" s="177">
-        <f t="shared" si="49"/>
-        <v>4.5745439537608137</v>
-      </c>
-      <c r="Q124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="12"/>
+      <c r="M124" s="12"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="12"/>
+      <c r="Q124" s="12"/>
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
-      <c r="B125" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C125" s="77">
-        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.23199018121797638</v>
+      <c r="B125" s="27" t="str">
+        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
+        <v>FCFE per share (CNY)</v>
+      </c>
+      <c r="C125" s="177">
+        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>5.5213663129878379</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
-      <c r="G125" s="77">
-        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+      <c r="G125" s="177">
+        <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>6.6173553593746677</v>
+      </c>
+      <c r="H125" s="177">
+        <f t="shared" si="49"/>
+        <v>6.6478738199797665</v>
+      </c>
+      <c r="I125" s="177">
+        <f t="shared" si="49"/>
+        <v>6.7361077920446659</v>
+      </c>
+      <c r="J125" s="177">
+        <f t="shared" si="49"/>
+        <v>7.2001905660095833</v>
+      </c>
+      <c r="K125" s="177">
+        <f t="shared" si="49"/>
+        <v>6.8335839477628442</v>
+      </c>
+      <c r="L125" s="177">
+        <f t="shared" si="49"/>
+        <v>5.9557690461941029</v>
+      </c>
+      <c r="M125" s="177">
+        <f t="shared" si="49"/>
+        <v>5.1439009759013636</v>
+      </c>
+      <c r="N125" s="177">
+        <f t="shared" si="49"/>
+        <v>4.4654669321028422</v>
+      </c>
+      <c r="O125" s="177">
+        <f t="shared" si="49"/>
+        <v>5.0342463177650627</v>
+      </c>
+      <c r="P125" s="177">
+        <f t="shared" si="49"/>
+        <v>4.5745439537608137</v>
+      </c>
+      <c r="Q125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A126" s="10"/>
+      <c r="B126" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" s="77">
+        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
+        <v>0.23199018121797638</v>
+      </c>
+      <c r="D126" s="27"/>
+      <c r="E126" s="265"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="77">
+        <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
         <v>0.2780401411501961</v>
       </c>
-      <c r="H125" s="77">
-        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+      <c r="H126" s="77">
+        <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
         <v>0.27932242941091456</v>
       </c>
-      <c r="I125" s="77">
-        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+      <c r="I126" s="77">
+        <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
         <v>0.28302973916154056</v>
       </c>
-      <c r="J125" s="77">
-        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+      <c r="J126" s="77">
+        <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
         <v>0.30252901537855392</v>
       </c>
-      <c r="K125" s="77">
-        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+      <c r="K126" s="77">
+        <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
         <v>0.28712537595642201</v>
       </c>
-      <c r="L125" s="77">
-        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+      <c r="L126" s="77">
+        <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
         <v>0.25024239689891187</v>
       </c>
-      <c r="M125" s="77">
-        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+      <c r="M126" s="77">
+        <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
         <v>0.21613029310509932</v>
       </c>
-      <c r="N125" s="77">
-        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+      <c r="N126" s="77">
+        <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
         <v>0.18762466101272446</v>
       </c>
-      <c r="O125" s="77">
-        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+      <c r="O126" s="77">
+        <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
         <v>0.21152295452794381</v>
       </c>
-      <c r="P125" s="77">
-        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+      <c r="P126" s="77">
+        <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
         <v>0.19220772914961401</v>
       </c>
-      <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+      <c r="Q126" s="77" t="str">
+        <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B126" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C126" s="169"/>
-      <c r="G126" s="23">
+    <row r="127" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B127" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C127" s="169"/>
+      <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.15672839055415214</v>
       </c>
-      <c r="H126" s="23">
+      <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.15705806403443148</v>
       </c>
-      <c r="I126" s="23">
+      <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.18691070556156733</v>
       </c>
-      <c r="J126" s="23">
+      <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.16952093511100405</v>
       </c>
-      <c r="K126" s="23">
+      <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.13688730563672646</v>
       </c>
-      <c r="L126" s="23">
+      <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.13490724221836156</v>
       </c>
-      <c r="M126" s="23">
+      <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.12387025950741437</v>
       </c>
-      <c r="N126" s="23">
+      <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.11677115572961987</v>
       </c>
-      <c r="O126" s="23">
+      <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.10987835069408605</v>
       </c>
-      <c r="P126" s="23">
+      <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.10244148328925688</v>
       </c>
-      <c r="Q126" s="23" t="str">
+      <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
@@ -15425,6 +15447,7 @@
     <row r="806" ht="15.75" customHeight="1"/>
     <row r="807" ht="15.75" customHeight="1"/>
     <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15446,13 +15469,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15469,20 +15492,20 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15493,7 +15516,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15503,7 +15526,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15512,9 +15535,9 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15524,15 +15547,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15542,13 +15565,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="364"/>
-      <c r="F7" s="364"/>
+      <c r="E7" s="366"/>
+      <c r="F7" s="366"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15558,13 +15581,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="364"/>
-      <c r="F8" s="364"/>
+      <c r="E8" s="366"/>
+      <c r="F8" s="366"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15574,13 +15597,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="364"/>
-      <c r="F9" s="364"/>
+      <c r="E9" s="366"/>
+      <c r="F9" s="366"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15594,7 +15617,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15625,7 +15648,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15635,13 +15658,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15649,9 +15672,9 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15659,7 +15682,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15684,7 +15707,7 @@
         <v>108</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="128" t="s">
         <v>109</v>
@@ -16456,7 +16479,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16493,7 +16516,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16714,7 +16737,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -16943,19 +16966,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D73" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E73" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17080,7 +17103,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C80" s="155" t="s">
         <v>105</v>
@@ -17206,18 +17229,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -17229,23 +17252,23 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C4" s="114">
-        <f>Normalized_FCF!C91</f>
+        <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
         <v>22020.769943020001</v>
       </c>
       <c r="D4" t="str">
@@ -17253,7 +17276,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17263,7 +17286,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17272,9 +17295,9 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -17284,13 +17307,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366"/>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -17307,7 +17330,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17317,13 +17340,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1">
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17331,9 +17354,9 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1">
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17341,7 +17364,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1">
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17363,16 +17386,16 @@
         <v>107</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="128" t="s">
         <v>109</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -18038,7 +18061,7 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
@@ -18075,7 +18098,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18246,7 +18269,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18465,19 +18488,19 @@
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D68" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E68" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F68" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18602,7 +18625,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C75" s="155" t="s">
         <v>105</v>
@@ -18654,32 +18677,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="6" width="42.6640625" customWidth="1"/>
-    <col min="8" max="9" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
+    <col min="5" max="6" width="42.73046875" customWidth="1"/>
+    <col min="8" max="9" width="15.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18691,14 +18714,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18727,7 +18750,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18740,7 +18763,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18750,11 +18773,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366" t="str">
+      <c r="E7" s="368" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 兴业银行(601166.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="366"/>
+      <c r="F7" s="368"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18775,8 +18798,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="368"/>
+      <c r="F8" s="368"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18797,8 +18820,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18808,8 +18831,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="366"/>
-      <c r="F10" s="366"/>
+      <c r="E10" s="368"/>
+      <c r="F10" s="368"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18820,10 +18843,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>451</v>
-      </c>
-      <c r="E11" s="366"/>
-      <c r="F11" s="366"/>
+        <v>448</v>
+      </c>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18834,15 +18857,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-5.5054441259114184E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="366"/>
-      <c r="F12" s="366"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18853,14 +18876,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.3520092995664894</v>
       </c>
-      <c r="E13" s="366"/>
-      <c r="F13" s="366"/>
+      <c r="E13" s="368"/>
+      <c r="F13" s="368"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18877,12 +18900,12 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.7745066708446342E-2</v>
       </c>
-      <c r="E14" s="366"/>
-      <c r="F14" s="366"/>
+      <c r="E14" s="368"/>
+      <c r="F14" s="368"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -18891,38 +18914,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="150">
         <v>30</v>
       </c>
-      <c r="E18" s="366" t="s">
-        <v>330</v>
-      </c>
-      <c r="F18" s="367"/>
+      <c r="E18" s="368" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" s="369"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
+      <c r="E19" s="369"/>
+      <c r="F19" s="369"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>303</v>
-      </c>
-      <c r="E20" s="367"/>
-      <c r="F20" s="367"/>
+        <v>302</v>
+      </c>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -18932,12 +18955,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="367"/>
-      <c r="F21" s="367"/>
+      <c r="E21" s="369"/>
+      <c r="F21" s="369"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -18947,44 +18970,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
+      <c r="E22" s="369"/>
+      <c r="F22" s="369"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>30</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="365"/>
-      <c r="F25" s="365"/>
+      <c r="E25" s="367"/>
+      <c r="F25" s="367"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="164">
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="365"/>
-      <c r="F26" s="365"/>
+      <c r="E26" s="367"/>
+      <c r="F26" s="367"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -18994,55 +19017,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="365"/>
-      <c r="F27" s="365"/>
+      <c r="E27" s="367"/>
+      <c r="F27" s="367"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="365"/>
-      <c r="F28" s="365"/>
+      <c r="E28" s="367"/>
+      <c r="F28" s="367"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>30</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="365"/>
-      <c r="F31" s="365"/>
+      <c r="E31" s="367"/>
+      <c r="F31" s="367"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32" s="164">
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="365"/>
-      <c r="F32" s="365"/>
+      <c r="E32" s="367"/>
+      <c r="F32" s="367"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19052,55 +19075,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="365"/>
-      <c r="F33" s="365"/>
+      <c r="E33" s="367"/>
+      <c r="F33" s="367"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="365"/>
-      <c r="F34" s="365"/>
+      <c r="E34" s="367"/>
+      <c r="F34" s="367"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>30</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="365"/>
-      <c r="F37" s="365"/>
+      <c r="E37" s="367"/>
+      <c r="F37" s="367"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="164">
         <v>0.04</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="365"/>
-      <c r="F38" s="365"/>
+      <c r="E38" s="367"/>
+      <c r="F38" s="367"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19110,24 +19133,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="365"/>
-      <c r="F39" s="365"/>
+      <c r="E39" s="367"/>
+      <c r="F39" s="367"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="365"/>
-      <c r="F40" s="365"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19140,7 +19163,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19149,12 +19172,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C46" s="150">
         <v>30</v>
@@ -19169,39 +19192,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>30</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="365"/>
-      <c r="F49" s="365"/>
+      <c r="E49" s="367"/>
+      <c r="F49" s="367"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="365"/>
-      <c r="F50" s="365"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19211,55 +19234,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="365"/>
-      <c r="F51" s="365"/>
+      <c r="E51" s="367"/>
+      <c r="F51" s="367"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" s="165">
         <v>0.01</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="365"/>
-      <c r="F52" s="365"/>
+      <c r="E52" s="367"/>
+      <c r="F52" s="367"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>30</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="365"/>
-      <c r="F55" s="365"/>
+      <c r="E55" s="367"/>
+      <c r="F55" s="367"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C56" s="164">
         <v>0.06</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="365"/>
-      <c r="F56" s="365"/>
+      <c r="E56" s="367"/>
+      <c r="F56" s="367"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19269,23 +19292,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="365"/>
-      <c r="F57" s="365"/>
+      <c r="E57" s="367"/>
+      <c r="F57" s="367"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" s="165">
         <v>0.01</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="365"/>
-      <c r="F58" s="365"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19296,7 +19319,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19305,7 +19328,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19314,15 +19337,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E63" s="252" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19330,19 +19353,19 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C65" s="151">
         <v>3.0480331534493699E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -19358,20 +19381,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19381,19 +19404,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19403,14 +19426,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19419,7 +19442,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19428,12 +19451,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19443,10 +19466,10 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>111</v>
+        <v>459</v>
       </c>
       <c r="C77" s="173">
-        <f>Normalized_FCF!C90</f>
+        <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
         <v>1.06</v>
       </c>
       <c r="D77" t="str">
@@ -19456,25 +19479,25 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.829322250329541</v>
+        <v>1.8293222503295408</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19482,7 +19505,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19503,7 +19526,7 @@
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
@@ -19515,12 +19538,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19533,7 +19556,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -19545,12 +19568,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19559,7 +19582,7 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
@@ -19571,7 +19594,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19592,7 +19615,7 @@
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
@@ -19601,14 +19624,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19619,7 +19642,7 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
@@ -19631,7 +19654,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19643,17 +19666,17 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
         <v>25.409202896038835</v>
       </c>
       <c r="D99" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
@@ -19665,12 +19688,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19679,7 +19702,7 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
@@ -19689,7 +19712,7 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19699,17 +19722,17 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
         <v>23.632551844105855</v>
       </c>
       <c r="D105" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
@@ -19721,32 +19744,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
+        <v>322</v>
+      </c>
+      <c r="F110" s="284" t="s">
         <v>325</v>
-      </c>
-      <c r="F110" s="284" t="s">
-        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50BD947-08B7-4878-8A76-8C4D7CAB7DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7622E091-076E-4A8E-BD90-B514BDE2DE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.8</v>
+        <v>23.98</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>494428.60815460002</v>
+        <v>498167.98418266006</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.4338176800193398E-2</v>
+        <v>8.1505286463246396E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4527,7 +4527,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.23199018121797638</v>
+        <v>0.23024880371091902</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4537815126050422E-2</v>
+        <v>4.4203502919099254E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,6 +5891,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5907,17 +5918,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,12 +13467,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4537815126050422E-2</v>
+        <v>4.4203502919099254E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4537815126050422E-2</v>
+        <v>4.4203502919099254E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.23199018121797638</v>
+        <v>0.23024880371091902</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.2780401411501961</v>
+        <v>0.27595310089135394</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.27932242941091456</v>
+        <v>0.27722576396913123</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.28302973916154056</v>
+        <v>0.28090524570661657</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.30252901537855392</v>
+        <v>0.30025815537988254</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.28712537595642201</v>
+        <v>0.28497013960645723</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.25024239689891187</v>
+        <v>0.24836401360275659</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.21613029310509932</v>
+        <v>0.21450796396586169</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.18762466101272446</v>
+        <v>0.18621630242297091</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.21152295452794381</v>
+        <v>0.20993520924791753</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.19220772914961401</v>
+        <v>0.19076496888076788</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15672839055415214</v>
+        <v>0.15555194725558052</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15705806403443148</v>
+        <v>0.15587914612258003</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18691070556156733</v>
+        <v>0.18550770610364065</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16952093511100405</v>
+        <v>0.16824846770816915</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13688730563672646</v>
+        <v>0.13585979458524144</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13490724221836156</v>
+        <v>0.13389459402823206</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12387025950741437</v>
+        <v>0.12294045772629116</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11677115572961987</v>
+        <v>0.11589464163323407</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10987835069408605</v>
+        <v>0.1090535757514282</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10244148328925688</v>
+        <v>0.10167253137132251</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.8</v>
+        <v>-23.98</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.8</v>
+        <v>23.98</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19497,7 +19497,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.8</v>
+        <v>23.98</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.4338176800193398E-2</v>
+        <v>8.1505286463246396E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7622E091-076E-4A8E-BD90-B514BDE2DE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D4A7AE-5A7E-4C1C-B2F3-341C4C1557E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.98</v>
+        <v>24</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>498167.98418266006</v>
+        <v>498583.47040799999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.1505286463246396E-2</v>
+        <v>8.1192319066667018E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.23024880371091902</v>
+        <v>0.2300569297078266</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4203502919099254E-2</v>
+        <v>4.4166666666666667E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,17 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5918,6 +5907,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,12 +13467,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4203502919099254E-2</v>
+        <v>4.4166666666666667E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4203502919099254E-2</v>
+        <v>4.4166666666666667E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.23024880371091902</v>
+        <v>0.2300569297078266</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.27595310089135394</v>
+        <v>0.27572313997394449</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.27722576396913123</v>
+        <v>0.27699474249915695</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.28090524570661657</v>
+        <v>0.2806711580018611</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.30025815537988254</v>
+        <v>0.30000794025039929</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.28497013960645723</v>
+        <v>0.28473266449011853</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.24836401360275659</v>
+        <v>0.24815704359142096</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.21450796396586169</v>
+        <v>0.21432920732922348</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.18621630242297091</v>
+        <v>0.18606112217095175</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.20993520924791753</v>
+        <v>0.20976026324021094</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.19076496888076788</v>
+        <v>0.19060599807336723</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15555194725558052</v>
+        <v>0.15542232063286754</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15587914612258003</v>
+        <v>0.15574924683414457</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18550770610364065</v>
+        <v>0.18535311634855428</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16824846770816915</v>
+        <v>0.16810826065174569</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13585979458524144</v>
+        <v>0.13574657808975374</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13389459402823206</v>
+        <v>0.1337830151998752</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12294045772629116</v>
+        <v>0.12283800734485259</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11589464163323407</v>
+        <v>0.11579806276520638</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1090535757514282</v>
+        <v>0.10896269777163535</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10167253137132251</v>
+        <v>0.10158780426184642</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.98</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.98</v>
+        <v>24</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.98</v>
+        <v>24</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.1505286463246396E-2</v>
+        <v>8.1192319066667018E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D4A7AE-5A7E-4C1C-B2F3-341C4C1557E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184754E2-EED7-4148-83B2-90636B76B1B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>24</v>
+        <v>23.94</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>498583.47040799999</v>
+        <v>497337.01173198002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.1192319066667018E-2</v>
+        <v>8.2132295157241408E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.2300569297078266</v>
+        <v>0.23063351349155548</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4166666666666667E-2</v>
+        <v>4.4277360066833749E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,6 +5891,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5907,17 +5918,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,12 +13467,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4166666666666667E-2</v>
+        <v>4.4277360066833749E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4166666666666667E-2</v>
+        <v>4.4277360066833749E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.2300569297078266</v>
+        <v>0.23063351349155548</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.27572313997394449</v>
+        <v>0.27641417541247565</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.27699474249915695</v>
+        <v>0.27768896491143552</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.2806711580018611</v>
+        <v>0.28137459448808128</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.30000794025039929</v>
+        <v>0.30075983985002436</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.28473266449011853</v>
+        <v>0.28544628019059498</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.24815704359142096</v>
+        <v>0.24877899106909368</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.21432920732922348</v>
+        <v>0.21486637326237942</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.18606112217095175</v>
+        <v>0.18652744077288397</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.20976026324021094</v>
+        <v>0.21028597818567513</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.19060599807336723</v>
+        <v>0.19108370734172153</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15542232063286754</v>
+        <v>0.15581185025851382</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15574924683414457</v>
+        <v>0.15613959582370379</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18535311634855428</v>
+        <v>0.18581766049980378</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16810826065174569</v>
+        <v>0.16852958461327888</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13574657808975374</v>
+        <v>0.13608679507744736</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1337830151998752</v>
+        <v>0.13411831097731849</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12283800734485259</v>
+        <v>0.12314587202491487</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11579806276520638</v>
+        <v>0.11608828347389109</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10896269777163535</v>
+        <v>0.10923578723973468</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10158780426184642</v>
+        <v>0.10184241028756533</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-24</v>
+        <v>-23.94</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>24</v>
+        <v>23.94</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>24</v>
+        <v>23.94</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.1192319066667018E-2</v>
+        <v>8.2132295157241408E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184754E2-EED7-4148-83B2-90636B76B1B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AF1F21-CDC9-4D7E-9587-FB0D739F7AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.94</v>
+        <v>23.16</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>497337.01173198002</v>
+        <v>481133.04894372006</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.2132295157241408E-2</v>
+        <v>9.4653369060194503E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.23063351349155548</v>
+        <v>0.23840096342779957</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4277360066833749E-2</v>
+        <v>4.5768566493955096E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,17 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5918,6 +5907,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,12 +13467,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4277360066833749E-2</v>
+        <v>4.5768566493955096E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4277360066833749E-2</v>
+        <v>4.5768566493955096E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.23063351349155548</v>
+        <v>0.23840096342779957</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.27641417541247565</v>
+        <v>0.28572346111289582</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.27768896491143552</v>
+        <v>0.28704118393695022</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.28137459448808128</v>
+        <v>0.29085094093457109</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.30075983985002436</v>
+        <v>0.31088905725429977</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.28544628019059498</v>
+        <v>0.29505975594830935</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.24877899106909368</v>
+        <v>0.2571575581258248</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.21486637326237942</v>
+        <v>0.22210280552251138</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.18652744077288397</v>
+        <v>0.19280945302689301</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.21028597818567513</v>
+        <v>0.21736814843545177</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.19108370734172153</v>
+        <v>0.19751916898794533</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15581185025851382</v>
+        <v>0.16105939961955185</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15613959582370379</v>
+        <v>0.16139818324781818</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18581766049980378</v>
+        <v>0.1920757682368438</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16852958461327888</v>
+        <v>0.1742054514525862</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13608679507744736</v>
+        <v>0.14067002910855311</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13411831097731849</v>
+        <v>0.13863524891178777</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12314587202491487</v>
+        <v>0.12729327185995087</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11608828347389109</v>
+        <v>0.11999799250280453</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10923578723973468</v>
+        <v>0.11291471271672056</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10184241028756533</v>
+        <v>0.10527233602263877</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.94</v>
+        <v>-23.16</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.94</v>
+        <v>23.16</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.94</v>
+        <v>23.16</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.2132295157241408E-2</v>
+        <v>9.4653369060194503E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AF1F21-CDC9-4D7E-9587-FB0D739F7AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCE59B1-26CD-4462-AE12-B0ADE4E31D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.16</v>
+        <v>23.75</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>481133.04894372006</v>
+        <v>493389.89259125001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.4653369060194503E-2</v>
+        <v>8.5130303817171127E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.23840096342779957</v>
+        <v>0.23247858159948792</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.5768566493955096E-2</v>
+        <v>4.4631578947368425E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,6 +5891,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5907,17 +5918,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,12 +13467,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.5768566493955096E-2</v>
+        <v>4.4631578947368425E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.5768566493955096E-2</v>
+        <v>4.4631578947368425E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.23840096342779957</v>
+        <v>0.23247858159948792</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.28572346111289582</v>
+        <v>0.27862548881577548</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.28704118393695022</v>
+        <v>0.27991047663072699</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.29085094093457109</v>
+        <v>0.28362559124398595</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.31088905725429977</v>
+        <v>0.30316591856882458</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.29505975594830935</v>
+        <v>0.28772985043211974</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.2571575581258248</v>
+        <v>0.25076922299764642</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.22210280552251138</v>
+        <v>0.21658530424847847</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.19280945302689301</v>
+        <v>0.18801966029906703</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.21736814843545177</v>
+        <v>0.21196826601116053</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.19751916898794533</v>
+        <v>0.1926123770004553</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16105939961955185</v>
+        <v>0.15705834506058194</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16139818324781818</v>
+        <v>0.15738871259029344</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1920757682368438</v>
+        <v>0.18730420178380222</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1742054514525862</v>
+        <v>0.16987782129018511</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14067002910855311</v>
+        <v>0.13717548943806696</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13863524891178777</v>
+        <v>0.13519125746513705</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12729327185995087</v>
+        <v>0.1241310390011142</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11999799250280453</v>
+        <v>0.11701698974168223</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11291471271672056</v>
+        <v>0.11010967353765257</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10527233602263877</v>
+        <v>0.10265714956986585</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.16</v>
+        <v>-23.75</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.16</v>
+        <v>23.75</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.16</v>
+        <v>23.75</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.4653369060194503E-2</v>
+        <v>8.5130303817171127E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCE59B1-26CD-4462-AE12-B0ADE4E31D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F8E4C9-64D8-47DA-B04E-D320FC62BA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.75</v>
+        <v>23.85</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>493389.89259125001</v>
+        <v>495467.32371795003</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.5130303817171127E-2</v>
+        <v>8.3548326143585427E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.23247858159948792</v>
+        <v>0.23150382863680663</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4631578947368425E-2</v>
+        <v>4.4444444444444446E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,17 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5918,6 +5907,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,12 +13467,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4631578947368425E-2</v>
+        <v>4.4444444444444446E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4631578947368425E-2</v>
+        <v>4.4444444444444446E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.23247858159948792</v>
+        <v>0.23150382863680663</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.27862548881577548</v>
+        <v>0.27745724777252273</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.27991047663072699</v>
+        <v>0.27873684779789376</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.28362559124398595</v>
+        <v>0.28243638541067778</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.30316591856882458</v>
+        <v>0.30189478264191122</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.28772985043211974</v>
+        <v>0.2865234359648991</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.25076922299764642</v>
+        <v>0.24971777971463743</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.21658530424847847</v>
+        <v>0.21567718976525632</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.18801966029906703</v>
+        <v>0.18723131790787598</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.21196826601116053</v>
+        <v>0.21107951017882862</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.1926123770004553</v>
+        <v>0.19180477793546388</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15705834506058194</v>
+        <v>0.15639981950477236</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15738871259029344</v>
+        <v>0.15672880184568005</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18730420178380222</v>
+        <v>0.18651885921867098</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16987782129018511</v>
+        <v>0.16916554530993277</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13717548943806696</v>
+        <v>0.13660033015321132</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13519125746513705</v>
+        <v>0.13462441781119519</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1241310390011142</v>
+        <v>0.12361057342878248</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11701698974168223</v>
+        <v>0.1165263524681322</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11010967353765257</v>
+        <v>0.10964799775762048</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10265714956986585</v>
+        <v>0.10222672126978255</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.75</v>
+        <v>-23.85</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.75</v>
+        <v>23.85</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.75</v>
+        <v>23.85</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.5130303817171127E-2</v>
+        <v>8.3548326143585427E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F8E4C9-64D8-47DA-B04E-D320FC62BA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CD6F97-79B7-41A6-A9A4-A32B2CFC3658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.85</v>
+        <v>24.06</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>495467.32371795003</v>
+        <v>499829.92908401997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.3548326143585427E-2</v>
+        <v>8.025555615701041E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.23150382863680663</v>
+        <v>0.22948322165369239</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4444444444444446E-2</v>
+        <v>4.4056525353283464E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,6 +5891,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5907,17 +5918,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,12 +13467,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4444444444444446E-2</v>
+        <v>4.4056525353283464E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4444444444444446E-2</v>
+        <v>4.4056525353283464E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.23150382863680663</v>
+        <v>0.22948322165369239</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.27745724777252273</v>
+        <v>0.27503555109620398</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.27873684779789376</v>
+        <v>0.27630398254279998</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.28243638541067778</v>
+        <v>0.27997122992704349</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.30189478264191122</v>
+        <v>0.29925979077346565</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.2865234359648991</v>
+        <v>0.28402260797019302</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.24971777971463743</v>
+        <v>0.24753819809618052</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.21567718976525632</v>
+        <v>0.21379472052790374</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.18723131790787598</v>
+        <v>0.18559712934758282</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.21107951017882862</v>
+        <v>0.2092371703144249</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.19180477793546388</v>
+        <v>0.19013067139488005</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15639981950477236</v>
+        <v>0.15503473379837163</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15672880184568005</v>
+        <v>0.15536084472233871</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18651885921867098</v>
+        <v>0.18489088912573995</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16916554530993277</v>
+        <v>0.16768903805660421</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13660033015321132</v>
+        <v>0.13540805794489152</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13462441781119519</v>
+        <v>0.1334493917205738</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12361057342878248</v>
+        <v>0.12253167814947891</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1165263524681322</v>
+        <v>0.11550928954135301</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10964799775762048</v>
+        <v>0.10869097034577092</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10222672126978255</v>
+        <v>0.10133446809161738</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.85</v>
+        <v>-24.06</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.85</v>
+        <v>24.06</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.85</v>
+        <v>24.06</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.3548326143585427E-2</v>
+        <v>8.025555615701041E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CD6F97-79B7-41A6-A9A4-A32B2CFC3658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A04AD0-84B7-48B8-85A0-CF5C9D8D8A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>24.06</v>
+        <v>23.81</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>499829.92908401997</v>
+        <v>494636.35126726999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.025555615701041E-2</v>
+        <v>8.4180024924960684E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.22948322165369239</v>
+        <v>0.23189274729054341</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4056525353283464E-2</v>
+        <v>4.4519109617807646E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,17 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5918,6 +5907,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,12 +13467,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4056525353283464E-2</v>
+        <v>4.4519109617807646E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4056525353283464E-2</v>
+        <v>4.4519109617807646E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.22948322165369239</v>
+        <v>0.23189274729054341</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.27503555109620398</v>
+        <v>0.27792336662640355</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.27630398254279998</v>
+        <v>0.27920511633682349</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.27997122992704349</v>
+        <v>0.282910869048495</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.29925979077346565</v>
+        <v>0.30240195573328787</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.28402260797019302</v>
+        <v>0.28700478571032528</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.24753819809618052</v>
+        <v>0.25013729719420846</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.21379472052790374</v>
+        <v>0.21603952019745334</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.18559712934758282</v>
+        <v>0.18754586023111475</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.2092371703144249</v>
+        <v>0.21143411666379938</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.19013067139488005</v>
+        <v>0.19212700351788384</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15503473379837163</v>
+        <v>0.15666256594661157</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15536084472233871</v>
+        <v>0.15699210096679839</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18489088912573995</v>
+        <v>0.18683220463525005</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16768903805660421</v>
+        <v>0.16944973774220484</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13540805794489152</v>
+        <v>0.13682981411818942</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1334493917205738</v>
+        <v>0.13485058230982802</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12253167814947891</v>
+        <v>0.12381823503891065</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11550928954135301</v>
+        <v>0.11672211282507154</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10869097034577092</v>
+        <v>0.10983220270975425</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10133446809161738</v>
+        <v>0.10239845872676666</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-24.06</v>
+        <v>-23.81</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>24.06</v>
+        <v>23.81</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>24.06</v>
+        <v>23.81</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.025555615701041E-2</v>
+        <v>8.4180024924960684E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A04AD0-84B7-48B8-85A0-CF5C9D8D8A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82343F16-A1A2-4433-B8E4-3BFFB3EC7BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>23.81</v>
+        <v>24.07</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>494636.35126726999</v>
+        <v>500037.67219668999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.4180024924960684E-2</v>
+        <v>8.009974005597531E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.23189274729054341</v>
+        <v>0.2293878817194781</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4519109617807646E-2</v>
+        <v>4.4038221852928959E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,6 +5891,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5907,17 +5918,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,12 +13467,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4519109617807646E-2</v>
+        <v>4.4038221852928959E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4519109617807646E-2</v>
+        <v>4.4038221852928959E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.23189274729054341</v>
+        <v>0.2293878817194781</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.27792336662640355</v>
+        <v>0.27492128622246231</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.27920511633682349</v>
+        <v>0.2761891906929691</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.282910869048495</v>
+        <v>0.27985491450123245</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.30240195573328787</v>
+        <v>0.29913546182009071</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.28700478571032528</v>
+        <v>0.28390460937942852</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.25013729719420846</v>
+        <v>0.24743535713311604</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.21603952019745334</v>
+        <v>0.21370589845871887</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.18754586023111475</v>
+        <v>0.18552002210647453</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.21143411666379938</v>
+        <v>0.20915024170191371</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.19212700351788384</v>
+        <v>0.19005168067140896</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15666256594661157</v>
+        <v>0.15497032385495724</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15699210096679839</v>
+        <v>0.15529629929453551</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18683220463525005</v>
+        <v>0.18481407529560875</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16944973774220484</v>
+        <v>0.16761937082018682</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13682981411818942</v>
+        <v>0.13535180200058539</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13485058230982802</v>
+        <v>0.13339394951379333</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12381823503891065</v>
+        <v>0.12248077176055099</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11672211282507154</v>
+        <v>0.11546130063834453</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10983220270975425</v>
+        <v>0.10864581414703982</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10239845872676666</v>
+        <v>0.10129236818796486</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-23.81</v>
+        <v>-24.07</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>23.81</v>
+        <v>24.07</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>23.81</v>
+        <v>24.07</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.4180024924960684E-2</v>
+        <v>8.009974005597531E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82343F16-A1A2-4433-B8E4-3BFFB3EC7BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1CC404-81D1-4672-8143-8E1EC208E30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>24.07</v>
+        <v>24.83</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>500037.67219668999</v>
+        <v>515826.14875960996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.009974005597531E-2</v>
+        <v>6.8510810559615054E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>13.079690025486418</v>
+        <v>12.726109311153213</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4527,7 +4527,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>18.356272555350223</v>
+        <v>15.835853412571439</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4546,7 +4546,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.2293878817194781</v>
+        <v>0.22236674639499954</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.4038221852928959E-2</v>
+        <v>4.269029399919453E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.829322250329541</v>
+        <v>1.7976324747243817</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>11.250367775156876</v>
+        <v>10.928476836428832</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>13.079690025486418</v>
+        <v>12.726109311153213</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.51355190135855366</v>
+        <v>0.52670195811590226</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>2.279132885208865</v>
+        <v>2.0691199999999998</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>16.07713967014136</v>
+        <v>13.766733412571439</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>18.356272555350223</v>
+        <v>15.835853412571439</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.3173099771252258</v>
+        <v>0.41104714500880857</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,17 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5918,6 +5907,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,12 +13467,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.4038221852928959E-2</v>
+        <v>4.269029399919453E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.4038221852928959E-2</v>
+        <v>4.269029399919453E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.2293878817194781</v>
+        <v>0.22236674639499954</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.27492128622246231</v>
+        <v>0.26650645829136804</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.2761891906929691</v>
+        <v>0.26773555457026849</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.27985491450123245</v>
+        <v>0.27128907740816216</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.29913546182009071</v>
+        <v>0.2899794831256377</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.28390460937942852</v>
+        <v>0.2752148186775209</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.24743535713311604</v>
+        <v>0.23986182223898925</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.21370589845871887</v>
+        <v>0.20716475939997439</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.18552002210647453</v>
+        <v>0.17984160016523731</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.20915024170191371</v>
+        <v>0.20274854280165377</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.19005168067140896</v>
+        <v>0.18423455311159137</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15497032385495724</v>
+        <v>0.15022697121179304</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15529629929453551</v>
+        <v>0.15054296915100562</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18481407529560875</v>
+        <v>0.17915726106988736</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16761937082018682</v>
+        <v>0.16248885443583957</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13535180200058539</v>
+        <v>0.13120893572912162</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13339394951379333</v>
+        <v>0.12931100945618226</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12248077176055099</v>
+        <v>0.11873186372438431</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11546130063834453</v>
+        <v>0.11192724552416243</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10864581414703982</v>
+        <v>0.10532036836565641</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10129236818796486</v>
+        <v>9.8191997675566411E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-24.07</v>
+        <v>-24.83</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>24.07</v>
+        <v>24.83</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19497,7 +19497,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.829322250329541</v>
+        <v>1.7976324747243817</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>11.250367775156876</v>
+        <v>10.928476836428832</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19519,7 +19519,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>13.079690025486418</v>
+        <v>12.726109311153213</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19530,7 +19530,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.51355190135855366</v>
+        <v>0.52670195811590226</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>24.07</v>
+        <v>24.83</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.009974005597531E-2</v>
+        <v>6.8510810559615054E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19586,7 +19586,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.279132885208865</v>
+        <v>2.0691199999999998</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>16.07713967014136</v>
+        <v>13.766733412571439</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>18.356272555350223</v>
+        <v>15.835853412571439</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.3173099771252258</v>
+        <v>0.41104714500880857</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1CC404-81D1-4672-8143-8E1EC208E30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D75C78-7225-48A1-8C12-3A7A6988CAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>24.83</v>
+        <v>25.12</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>515826.14875960996</v>
+        <v>521850.69902704004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.8510810559615054E-2</v>
+        <v>6.4215973755760603E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.22236674639499954</v>
+        <v>0.21979961437053494</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.269029399919453E-2</v>
+        <v>4.2197452229299361E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,6 +5891,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5907,17 +5918,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,12 +13467,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.269029399919453E-2</v>
+        <v>4.2197452229299361E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.269029399919453E-2</v>
+        <v>4.2197452229299361E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.22236674639499954</v>
+        <v>0.21979961437053494</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.26650645829136804</v>
+        <v>0.2634297515674629</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.26773555457026849</v>
+        <v>0.26464465843868495</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.27128907740816216</v>
+        <v>0.26815715732661888</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.2899794831256377</v>
+        <v>0.2866317900481522</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.2752148186775209</v>
+        <v>0.2720375775383298</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.23986182223898925</v>
+        <v>0.23709271680709007</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.20716475939997439</v>
+        <v>0.20477312802155109</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.17984160016523731</v>
+        <v>0.17776540334804308</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.20274854280165377</v>
+        <v>0.20040789481548815</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.18423455311159137</v>
+        <v>0.18210764147136996</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15022697121179304</v>
+        <v>0.14849266302503267</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15054296915100562</v>
+        <v>0.14880501289886422</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17915726106988736</v>
+        <v>0.17708896466422383</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16248885443583957</v>
+        <v>0.16061298788383346</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13120893572912162</v>
+        <v>0.12969418288829976</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12931100945618226</v>
+        <v>0.12781816738841581</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11873186372438431</v>
+        <v>0.11736115351419037</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11192724552416243</v>
+        <v>0.11063509181389143</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10532036836565641</v>
+        <v>0.10410448831684906</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8191997675566411E-2</v>
+        <v>9.7058411715139889E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-24.83</v>
+        <v>-25.12</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>24.83</v>
+        <v>25.12</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>24.83</v>
+        <v>25.12</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.8510810559615054E-2</v>
+        <v>6.4215973755760603E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D75C78-7225-48A1-8C12-3A7A6988CAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A7D2B4-210C-41EF-B54D-57181319A2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>25.12</v>
+        <v>25.14</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>521850.69902704004</v>
+        <v>522266.18525238003</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.4215973755760603E-2</v>
+        <v>6.392228128073163E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.21979961437053494</v>
+        <v>0.21962475389768649</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.2197452229299361E-2</v>
+        <v>4.2163882259347654E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,17 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5918,6 +5907,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13467,12 +13467,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.2197452229299361E-2</v>
+        <v>4.2163882259347654E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.2197452229299361E-2</v>
+        <v>4.2163882259347654E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14666,50 +14666,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.21979961437053494</v>
+        <v>0.21962475389768649</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.2634297515674629</v>
+        <v>0.26322018135937419</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.26464465843868495</v>
+        <v>0.26443412171757225</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.26815715732661888</v>
+        <v>0.26794382625475999</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.2866317900481522</v>
+        <v>0.28640376157556019</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.2720375775383298</v>
+        <v>0.27182115941777424</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.23709271680709007</v>
+        <v>0.23690409889395794</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.20477312802155109</v>
+        <v>0.20461022179400809</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.17776540334804308</v>
+        <v>0.17762398297942888</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.20040789481548815</v>
+        <v>0.20024846132717036</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.18210764147136996</v>
+        <v>0.1819627666571525</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14723,43 +14723,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14849266302503267</v>
+        <v>0.14837453043710505</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14880501289886422</v>
+        <v>0.14868663182257236</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17708896466422383</v>
+        <v>0.1769480824329874</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16061298788383346</v>
+        <v>0.16048521303269278</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12969418288829976</v>
+        <v>0.12959100533628043</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12781816738841581</v>
+        <v>0.12771648229105032</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11736115351419037</v>
+        <v>0.11726778744138672</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11063509181389143</v>
+        <v>0.11054707662549534</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10410448831684906</v>
+        <v>0.10402166851707431</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7058411715139889E-2</v>
+        <v>9.6981197386010895E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-25.12</v>
+        <v>-25.14</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>25.12</v>
+        <v>25.14</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>25.12</v>
+        <v>25.14</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>6.4215973755760603E-2</v>
+        <v>6.392228128073163E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A7D2B4-210C-41EF-B54D-57181319A2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CDCD01-9076-4351-9AE4-EE1D38256C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="467">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2456,6 +2457,9 @@
   </si>
   <si>
     <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
   </si>
   <si>
     <t>CN</t>
@@ -4240,13 +4244,13 @@
         <v>45794</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E1" s="292" t="s">
         <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4327,7 +4331,7 @@
         <v>438</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4444,7 +4448,7 @@
         <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -4452,7 +4456,7 @@
         <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -6624,7 +6628,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12763,7 +12767,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -19786,4 +19790,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>460</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CDCD01-9076-4351-9AE4-EE1D38256C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB2205D-6244-4908-ABEE-911A767CDACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,20 +20,33 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
+    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
+    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
+    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
+    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +55,7 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
@@ -2504,7 +2517,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2944,6 +2957,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3147,11 +3166,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="373">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3936,9 +3956,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{2A296993-17E8-4481-A7B5-82C5E0098357}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4023,6 +4049,89 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="C6">
+            <v>20774311267</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>25.14</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>DDM</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="C86">
+            <v>0.06</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>1000000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="93">
+          <cell r="C93">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19793,22 +19902,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E34599D9-BD65-4240-BB2F-590DEC389933}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="372"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="370" t="s">
         <v>460</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="371"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/601166.SS_Valuation.xlsx
+++ b/financial_models/opportunities/601166.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB2205D-6244-4908-ABEE-911A767CDACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A824383-9DAC-4251-AEFD-3820879EDA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3920,47 +3920,47 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4449,7 +4449,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>25.14</v>
+        <v>24.94</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>522266.18525238003</v>
+        <v>518111.32299898006</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4507,13 +4507,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="361" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="361"/>
+      <c r="D18" s="361"/>
+      <c r="E18" s="361"/>
+      <c r="F18" s="361"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>26.888151196428591</v>
+        <v>20.647898129891665</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>6.392228128073163E-2</v>
+        <v>-1.5778435496761389E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>12.726109311153213</v>
+        <v>8.355749929850889</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4640,7 +4640,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>15.835853412571439</v>
+        <v>11.323303654934758</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4659,7 +4659,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>25.409202896038835</v>
+        <v>19.377301122078141</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4678,7 +4678,7 @@
         <v>433</v>
       </c>
       <c r="F31" s="312">
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>23.632551844105855</v>
+        <v>18.773924722806626</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4715,13 +4715,13 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="361" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="361"/>
+      <c r="D36" s="361"/>
+      <c r="E36" s="361"/>
+      <c r="F36" s="361"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
       <c r="B37" s="363" t="s">
@@ -4742,13 +4742,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="362" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="362"/>
+      <c r="D40" s="362"/>
+      <c r="E40" s="362"/>
+      <c r="F40" s="362"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4768,13 +4768,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="362" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="362"/>
+      <c r="D43" s="362"/>
+      <c r="E43" s="362"/>
+      <c r="F43" s="362"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4803,13 +4803,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="362" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="362"/>
+      <c r="D47" s="362"/>
+      <c r="E47" s="362"/>
+      <c r="F47" s="362"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4825,13 +4825,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="362" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="362"/>
+      <c r="D50" s="362"/>
+      <c r="E50" s="362"/>
+      <c r="F50" s="362"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4895,13 +4895,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="362" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="362"/>
+      <c r="D58" s="362"/>
+      <c r="E58" s="362"/>
+      <c r="F58" s="362"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4917,13 +4917,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="362" t="s">
         <v>335</v>
       </c>
-      <c r="C61" s="362"/>
-      <c r="D61" s="362"/>
-      <c r="E61" s="362"/>
-      <c r="F61" s="362"/>
+      <c r="C61" s="365"/>
+      <c r="D61" s="365"/>
+      <c r="E61" s="365"/>
+      <c r="F61" s="365"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4939,22 +4939,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="361" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="361"/>
+      <c r="D64" s="361"/>
+      <c r="E64" s="361"/>
+      <c r="F64" s="361"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="361" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="361"/>
+      <c r="D65" s="361"/>
+      <c r="E65" s="361"/>
+      <c r="F65" s="361"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>0.21962475389768649</v>
+        <v>0.22138597886879863</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>4.2163882259347654E-2</v>
+        <v>4.2502004811547714E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -5089,13 +5089,13 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="361" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="361"/>
+      <c r="D80" s="361"/>
+      <c r="E80" s="361"/>
+      <c r="F80" s="361"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="363" t="s">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="C84" s="92">
         <f>F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5148,22 +5148,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="361" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="361"/>
+      <c r="D89" s="361"/>
+      <c r="E89" s="361"/>
+      <c r="F89" s="361"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="361" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="361"/>
+      <c r="D90" s="361"/>
+      <c r="E90" s="361"/>
+      <c r="F90" s="361"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>92.022771883130645</v>
+        <v>73.618217506504507</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5200,13 +5200,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="361" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="361"/>
+      <c r="D97" s="361"/>
+      <c r="E97" s="361"/>
+      <c r="F97" s="361"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5219,13 +5219,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="361"/>
+      <c r="D101" s="361"/>
+      <c r="E101" s="361"/>
+      <c r="F101" s="361"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5347,13 +5347,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="361" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="361"/>
+      <c r="D116" s="361"/>
+      <c r="E116" s="361"/>
+      <c r="F116" s="361"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>17.666666666666668</v>
+        <v>14.133333333333335</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5392,13 +5392,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="362" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="362"/>
+      <c r="D123" s="362"/>
+      <c r="E123" s="362"/>
+      <c r="F123" s="362"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>37.71 CNY</v>
+        <v>28.87 CNY</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>29.79 CNY</v>
+        <v>22.87 CNY</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>26.75 CNY</v>
+        <v>20.55 CNY</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>24.19 CNY</v>
+        <v>18.57 CNY</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>20.16 CNY</v>
+        <v>15.44 CNY</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>26.888151196428591</v>
+        <v>20.647898129891665</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5541,13 +5541,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="366" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="366"/>
+      <c r="D134" s="366"/>
+      <c r="E134" s="366"/>
+      <c r="F134" s="366"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5560,22 +5560,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="364" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="361" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="361"/>
+      <c r="D139" s="361"/>
+      <c r="E139" s="361"/>
+      <c r="F139" s="361"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.7976324747243817</v>
+        <v>1.5828939275903069</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>10.928476836428832</v>
+        <v>6.7728560022605819</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>12.726109311153213</v>
+        <v>8.355749929850889</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.52670195811590226</v>
+        <v>0.59532200918047007</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>2.0691199999999998</v>
+        <v>1.9250796540737376</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>13.766733412571439</v>
+        <v>9.3982240008610205</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>15.835853412571439</v>
+        <v>11.323303654934758</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.41104714500880857</v>
+        <v>0.45160017820205267</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="163" spans="2:4">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>2.8333926664293383</v>
+        <v>2.7565572842642774</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>22.575810229609498</v>
+        <v>16.620743837813862</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>25.409202896038835</v>
+        <v>19.377301122078141</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>5.5003718537040891E-2</v>
+        <v>6.1536384954074319E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>20.934968382149542</v>
+        <v>16.076341260850313</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>23.632551844105855</v>
+        <v>18.773924722806626</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.1210155297728992</v>
+        <v>9.0875682334987329E-2</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5908,13 +5908,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="368" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="361"/>
+      <c r="D179" s="361"/>
+      <c r="E179" s="361"/>
+      <c r="F179" s="361"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5922,13 +5922,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="362" t="s">
+      <c r="B182" s="365" t="s">
         <v>377</v>
       </c>
-      <c r="C182" s="362"/>
-      <c r="D182" s="362"/>
-      <c r="E182" s="362"/>
-      <c r="F182" s="362"/>
+      <c r="C182" s="365"/>
+      <c r="D182" s="365"/>
+      <c r="E182" s="365"/>
+      <c r="F182" s="365"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5951,13 +5951,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="362" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="362"/>
+      <c r="D188" s="362"/>
+      <c r="E188" s="362"/>
+      <c r="F188" s="362"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5965,22 +5965,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="367" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="367"/>
+      <c r="D191" s="367"/>
+      <c r="E191" s="367"/>
+      <c r="F191" s="367"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="367" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="367"/>
+      <c r="D192" s="367"/>
+      <c r="E192" s="367"/>
+      <c r="F192" s="367"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6004,6 +6004,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6020,17 +6031,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13580,12 +13580,12 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.2163882259347654E-2</v>
+        <v>4.2502004811547714E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.2163882259347654E-2</v>
+        <v>4.2502004811547714E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
@@ -14779,50 +14779,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.21962475389768649</v>
+        <v>0.22138597886879863</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.26322018135937419</v>
+        <v>0.26533100879609733</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.26443412171757225</v>
+        <v>0.26655468404088878</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.26794382625475999</v>
+        <v>0.27009253376281739</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>0.28640376157556019</v>
+        <v>0.28870050384962243</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.27182115941777424</v>
+        <v>0.27400096021502984</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.23690409889395794</v>
+        <v>0.23880389118661197</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.20461022179400809</v>
+        <v>0.20625104153574031</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.17762398297942888</v>
+        <v>0.1790483934283417</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>0.20024846132717036</v>
+        <v>0.20185430303789345</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>0.1819627666571525</v>
+        <v>0.18342197088054585</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14836,43 +14836,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14837453043710505</v>
+        <v>0.14956438232513314</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14868663182257236</v>
+        <v>0.14987898652844703</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1769480824329874</v>
+        <v>0.17836707266901775</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16048521303269278</v>
+        <v>0.16177218346599423</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12959100533628043</v>
+        <v>0.13063022751219286</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12771648229105032</v>
+        <v>0.1287406722051726</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11726778744138672</v>
+        <v>0.11820818669913641</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11054707662549534</v>
+        <v>0.11143358084863483</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10402166851707431</v>
+        <v>0.10485584388609656</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6981197386010895E-2</v>
+        <v>9.7758913483733514E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15643,7 +15643,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -15654,16 +15654,16 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1911709.7067522916</v>
+        <v>1529367.7654018332</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366" t="s">
+      <c r="E6" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="F6" s="366"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -15678,8 +15678,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366"/>
-      <c r="F7" s="366"/>
+      <c r="E7" s="369"/>
+      <c r="F7" s="369"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -15694,8 +15694,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="369"/>
+      <c r="F8" s="369"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -15710,8 +15710,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="369"/>
+      <c r="F9" s="369"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>-5459073.1932477076</v>
+        <v>-5841415.1345981676</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>-262.77998452441824</v>
+        <v>-281.18453890104445</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15801,7 +15801,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>-228.15289802637383</v>
+        <v>-254.2678707014849</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15844,11 +15844,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>111508.25957047987</v>
+        <v>109952.33036717086</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15866,11 +15866,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>108402.89461417214</v>
+        <v>105398.80358116503</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15888,11 +15888,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>105384.01017104799</v>
+        <v>101033.85493735623</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15920,11 +15920,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>102449.19786744905</v>
+        <v>96849.674727492806</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -15952,11 +15952,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>99596.116399897961</v>
+        <v>92838.776671808999</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -15984,11 +15984,11 @@
       </c>
       <c r="E26" s="124">
         <f t="shared" si="0"/>
-        <v>0.70496054043967626</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>96822.489667278176</v>
+        <v>88993.984524672152</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -16006,11 +16006,11 @@
       </c>
       <c r="E27" s="124">
         <f t="shared" si="0"/>
-        <v>0.66505711362233599</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>94126.104955030081</v>
+        <v>85308.419234939312</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -16028,11 +16028,11 @@
       </c>
       <c r="E28" s="124">
         <f t="shared" si="0"/>
-        <v>0.62741237134182648</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>91504.811169915076</v>
+        <v>81775.48663805009</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -16050,11 +16050,11 @@
       </c>
       <c r="E29" s="124">
         <f t="shared" si="0"/>
-        <v>0.59189846353002495</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>88956.517123938975</v>
+        <v>78388.865657834802</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -16072,11 +16072,11 @@
       </c>
       <c r="E30" s="124">
         <f t="shared" si="0"/>
-        <v>0.55839477691511785</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>86479.189866066517</v>
+        <v>75142.496996928865</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -16094,11 +16094,11 @@
       </c>
       <c r="E31" s="124">
         <f t="shared" si="0"/>
-        <v>0.52678752539162055</v>
+        <v>0.45134318911764126</v>
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>84070.853060394918</v>
+        <v>72030.572295558071</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -16116,11 +16116,11 @@
       </c>
       <c r="E32" s="124">
         <f t="shared" si="0"/>
-        <v>0.4969693635770005</v>
+        <v>0.41985412941175931</v>
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>81729.58540949384</v>
+        <v>69047.523739298602</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -16138,11 +16138,11 @@
       </c>
       <c r="E33" s="124">
         <f t="shared" si="0"/>
-        <v>0.46883902224245327</v>
+        <v>0.39056198084814819</v>
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>79453.51912165276</v>
+        <v>66188.014097216976</v>
       </c>
       <c r="G33" s="338"/>
       <c r="H33" s="339"/>
@@ -16170,11 +16170,11 @@
       </c>
       <c r="E34" s="124">
         <f t="shared" si="0"/>
-        <v>0.44230096437967292</v>
+        <v>0.36331347055641694</v>
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>77240.838420814121</v>
+        <v>63446.927172567346</v>
       </c>
       <c r="G34" s="338"/>
       <c r="H34" s="339"/>
@@ -16202,11 +16202,11 @@
       </c>
       <c r="E35" s="124">
         <f t="shared" si="0"/>
-        <v>0.41726506073554037</v>
+        <v>0.33796601912224833</v>
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>75089.778098002629</v>
+        <v>60819.358648960078</v>
       </c>
       <c r="G35" s="338"/>
       <c r="H35" s="339"/>
@@ -16234,11 +16234,11 @@
       </c>
       <c r="E36" s="124">
         <f t="shared" si="0"/>
-        <v>0.39364628371277405</v>
+        <v>0.31438699453232405</v>
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>72998.622103095593</v>
+        <v>58300.607315623878</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -16256,11 +16256,11 @@
       </c>
       <c r="E37" s="124">
         <f t="shared" si="0"/>
-        <v>0.37136441859695657</v>
+        <v>0.29245301816960378</v>
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>70965.702175810511</v>
+        <v>55886.166656061781</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -16278,11 +16278,11 @@
       </c>
       <c r="E38" s="124">
         <f t="shared" si="0"/>
-        <v>0.35034379112920433</v>
+        <v>0.27204931922753844</v>
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>68989.396514818276</v>
+        <v>53571.716785051649</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -16300,11 +16300,11 @@
       </c>
       <c r="E39" s="124">
         <f t="shared" si="0"/>
-        <v>0.3305130104992493</v>
+        <v>0.25306913416515198</v>
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>67068.128483919398</v>
+        <v>51353.116719564663</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -16322,11 +16322,11 @@
       </c>
       <c r="E40" s="124">
         <f t="shared" si="0"/>
-        <v>0.31180472688608429</v>
+        <v>0.23541314806060654</v>
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>65200.365354252172</v>
+        <v>49226.396969773545</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -16344,11 +16344,11 @@
       </c>
       <c r="E41" s="124">
         <f t="shared" si="0"/>
-        <v>0.29415540272272095</v>
+        <v>0.21898897494009908</v>
       </c>
       <c r="F41" s="125">
         <f t="shared" si="1"/>
-        <v>63384.617081528188</v>
+        <v>47187.752436893796</v>
       </c>
       <c r="H41" s="120"/>
     </row>
@@ -16366,11 +16366,11 @@
       </c>
       <c r="E42" s="124">
         <f t="shared" si="0"/>
-        <v>0.27750509690822728</v>
+        <v>0.20371067436288287</v>
       </c>
       <c r="F42" s="125">
         <f t="shared" si="1"/>
-        <v>61619.435117320827</v>
+        <v>45233.535605151563</v>
       </c>
       <c r="H42" s="120"/>
     </row>
@@ -16388,11 +16388,11 @@
       </c>
       <c r="E43" s="124">
         <f t="shared" si="0"/>
-        <v>0.26179726123417668</v>
+        <v>0.18949830173291429</v>
       </c>
       <c r="F43" s="125">
         <f t="shared" si="1"/>
-        <v>59903.411253457554</v>
+        <v>43360.250015696663</v>
       </c>
       <c r="H43" s="120"/>
     </row>
@@ -16410,11 +16410,11 @@
       </c>
       <c r="E44" s="124">
         <f t="shared" si="0"/>
-        <v>0.24697854833412897</v>
+        <v>0.17627748998410636</v>
       </c>
       <c r="F44" s="125">
         <f t="shared" si="1"/>
-        <v>58235.176498594403</v>
+        <v>41564.544010784783</v>
       </c>
       <c r="H44" s="120"/>
     </row>
@@ -16432,11 +16432,11 @@
       </c>
       <c r="E45" s="124">
         <f t="shared" si="0"/>
-        <v>0.23299863050389524</v>
+        <v>0.16397906045033148</v>
       </c>
       <c r="F45" s="125">
         <f t="shared" si="1"/>
-        <v>56613.399986076707</v>
+        <v>39843.204737035863</v>
       </c>
       <c r="H45" s="120"/>
     </row>
@@ -16454,11 +16454,11 @@
       </c>
       <c r="E46" s="124">
         <f t="shared" si="0"/>
-        <v>0.21981002877725966</v>
+        <v>0.15253866088402931</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>55036.787912214371</v>
+        <v>38193.152397039477</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -16476,11 +16476,11 @@
       </c>
       <c r="E47" s="124">
         <f t="shared" si="0"/>
-        <v>0.20736795167666003</v>
+        <v>0.14189642872932959</v>
       </c>
       <c r="F47" s="125">
         <f t="shared" si="1"/>
-        <v>53504.082504124774</v>
+        <v>36611.434739022021</v>
       </c>
       <c r="G47" s="338"/>
       <c r="H47" s="339"/>
@@ -16508,11 +16508,11 @@
       </c>
       <c r="E48" s="124">
         <f t="shared" si="0"/>
-        <v>0.1956301430911887</v>
+        <v>0.13199667788774846</v>
       </c>
       <c r="F48" s="125">
         <f t="shared" si="1"/>
-        <v>52014.061016320193</v>
+        <v>35095.221774717116</v>
       </c>
       <c r="G48" s="338"/>
       <c r="H48" s="339"/>
@@ -16540,11 +16540,11 @@
       </c>
       <c r="E49" s="124">
         <f t="shared" si="0"/>
-        <v>0.18455673876527234</v>
+        <v>0.1227876073374404</v>
       </c>
       <c r="F49" s="125">
         <f t="shared" si="1"/>
-        <v>50565.534755238688</v>
+        <v>33641.800715987963</v>
       </c>
       <c r="G49" s="338"/>
       <c r="H49" s="339"/>
@@ -16572,11 +16572,11 @@
       </c>
       <c r="E50" s="124">
         <f t="shared" si="0"/>
-        <v>0.17411013091063426</v>
+        <v>0.11422103008133992</v>
       </c>
       <c r="F50" s="125">
         <f t="shared" si="1"/>
-        <v>49157.348130940874</v>
+        <v>32248.571121142937</v>
       </c>
       <c r="G50" s="338"/>
       <c r="H50" s="339"/>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1969979.2524118114</v>
+        <v>1575983.4019294491</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16604,11 +16604,11 @@
       </c>
       <c r="E51" s="124">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.17411013091063426</v>
+        <v>0.11422103008133992</v>
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>342993.34552865388</v>
+        <v>180010.44755947602</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>2631063.579932001</v>
+        <v>2088543.0088500436</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16640,7 +16640,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>2631063.579932001</v>
+        <v>2088543.0088500436</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16670,19 +16670,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1911709.7067522909</v>
+        <v>1529367.7654018335</v>
       </c>
       <c r="C56" s="123">
-        <v>1968874.0875522024</v>
+        <v>1577864.7869969984</v>
       </c>
       <c r="D56" s="123">
-        <v>1998014.3064496904</v>
+        <v>1602639.2656802249</v>
       </c>
       <c r="E56" s="123">
-        <v>2027537.4569108186</v>
+        <v>1627774.6214795262</v>
       </c>
       <c r="F56" s="123">
-        <v>2087766.0566947917</v>
+        <v>1679159.3762006571</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16691,19 +16691,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>1911709.7067522909</v>
+        <v>1529367.7654018337</v>
       </c>
       <c r="C57" s="123">
-        <v>2022822.2763396518</v>
+        <v>1625955.8069168786</v>
       </c>
       <c r="D57" s="123">
-        <v>2082327.300124404</v>
+        <v>1677787.7537416357</v>
       </c>
       <c r="E57" s="123">
-        <v>2144673.0507178493</v>
+        <v>1732163.1071096794</v>
       </c>
       <c r="F57" s="123">
-        <v>2278563.8621934908</v>
+        <v>1849144.634076274</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16712,19 +16712,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>1911709.7067522905</v>
+        <v>1529367.7654018337</v>
       </c>
       <c r="C58" s="341">
-        <v>2095973.8538441975</v>
+        <v>1686844.6699016364</v>
       </c>
       <c r="D58" s="123">
-        <v>2199626.863069878</v>
+        <v>1775409.2722894626</v>
       </c>
       <c r="E58" s="123">
-        <v>2311958.1806159643</v>
+        <v>1871363.321711286</v>
       </c>
       <c r="F58" s="123">
-        <v>2566089.782987583</v>
+        <v>2088323.0080886288</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16743,19 +16743,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>1911709.7067522905</v>
+        <v>1529367.7654018339</v>
       </c>
       <c r="C59" s="341">
-        <v>2177729.7057453385</v>
+        <v>1750322.3029370341</v>
       </c>
       <c r="D59" s="123">
-        <v>2334315.2883597421</v>
+        <v>1879969.0145700923</v>
       </c>
       <c r="E59" s="123">
-        <v>2509472.5608553481</v>
+        <v>2024670.6115870625</v>
       </c>
       <c r="F59" s="123">
-        <v>2925896.5784820877</v>
+        <v>2367504.2619460779</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16774,19 +16774,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>1911709.7067522905</v>
+        <v>1529367.7654018342</v>
       </c>
       <c r="C60" s="341">
-        <v>2261174.8479017401</v>
+        <v>1810738.3590534206</v>
       </c>
       <c r="D60" s="123">
-        <v>2475707.9738625088</v>
+        <v>1982323.8014684785</v>
       </c>
       <c r="E60" s="123">
-        <v>2722988.8120144377</v>
+        <v>2179209.8284802479</v>
       </c>
       <c r="F60" s="123">
-        <v>3339715.8483383819</v>
+        <v>2666911.6387364082</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16805,19 +16805,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>1911709.70675229</v>
+        <v>1529367.7654018344</v>
       </c>
       <c r="C61" s="341">
-        <v>2341971.4002733147</v>
+        <v>1865280.5333572214</v>
       </c>
       <c r="D61" s="123">
-        <v>2616661.8419397096</v>
+        <v>2077459.6392501646</v>
       </c>
       <c r="E61" s="123">
-        <v>2942473.8289640578</v>
+        <v>2327323.591763041</v>
       </c>
       <c r="F61" s="123">
-        <v>3793896.3810982425</v>
+        <v>2973287.7018133528</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16897,23 +16897,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>-262.77998452441824</v>
+        <v>-281.18453890104445</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>-262.77998452441824</v>
+        <v>-281.18453890104445</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>-262.77998452441824</v>
+        <v>-281.18453890104445</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>-262.77998452441824</v>
+        <v>-281.18453890104445</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>-262.77998452441824</v>
+        <v>-281.18453890104445</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16924,23 +16924,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>-262.77998452441835</v>
+        <v>-281.18453890104439</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>-260.02829855682057</v>
+        <v>-278.85006817073423</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>-258.62559410501149</v>
+        <v>-277.65751461914761</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>-257.20445671654727</v>
+        <v>-276.44758975202438</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>-254.30527036038407</v>
+        <v>-273.97411402227755</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16951,23 +16951,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>-262.77998452441835</v>
+        <v>-281.18453890104439</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>-257.43142840819883</v>
+        <v>-276.53514088858293</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>-254.56707237636843</v>
+        <v>-274.04013895284646</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>-251.56597405873225</v>
+        <v>-271.42270665055793</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>-245.12095599027151</v>
+        <v>-265.79164021167094</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16978,23 +16978,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>-262.77998452441835</v>
+        <v>-281.18453890104439</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>-253.91017677369831</v>
+        <v>-273.60417185658042</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>-248.92069683891299</v>
+        <v>-269.3409931042475</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>-243.51347461612264</v>
+        <v>-264.7221131717875</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>-231.28050096393201</v>
+        <v>-254.2784607402393</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17005,23 +17005,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>-262.77998452441835</v>
+        <v>-281.18453890104439</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>-249.97474657577834</v>
+        <v>-270.54858882330649</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>-242.43728453422608</v>
+        <v>-264.30786632874162</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>-234.00584869770609</v>
+        <v>-257.34245625294153</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>-213.96070677821297</v>
+        <v>-240.83968771574303</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17032,23 +17032,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>-262.77998452441835</v>
+        <v>-281.18453890104439</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>-245.95800007169785</v>
+        <v>-267.6403789991686</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>-235.63115345794014</v>
+        <v>-259.38087810839204</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>-223.72795074889362</v>
+        <v>-249.90349883543763</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>-194.04094796947462</v>
+        <v>-226.42730248947859</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17058,23 +17058,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>-262.77998452441835</v>
+        <v>-281.18453890104439</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>-242.06874707393808</v>
+        <v>-265.01491654205984</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>-228.84614546101528</v>
+        <v>-254.80138391679353</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>-213.16273806247972</v>
+        <v>-242.77383945086521</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>-172.1783443470226</v>
+        <v>-211.67946997944861</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17109,7 +17109,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>-172.1783443470226</v>
+        <v>-211.67946997944861</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -17131,7 +17131,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>-213.16273806247972</v>
+        <v>-242.77383945086521</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>-228.84614546101528</v>
+        <v>-254.80138391679353</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>-242.06874707393808</v>
+        <v>-265.01491654205984</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17200,7 +17200,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>-262.77998452441835</v>
+        <v>-281.18453890104439</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -17414,14 +17414,14 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>367012.83238366671</v>
+        <v>293610.26590693335</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366"/>
-      <c r="F6" s="366"/>
+      <c r="E6" s="369"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>17.666666666666668</v>
+        <v>14.133333333333335</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17483,7 +17483,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>26.886199522956279</v>
+        <v>20.650558298809361</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17526,11 +17526,11 @@
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>21407.519161818927</v>
+        <v>21108.809592119131</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17548,11 +17548,11 @@
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>20811.346644530371</v>
+        <v>20234.616843521326</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17570,11 +17570,11 @@
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>20231.776782957477</v>
+        <v>19396.627603149122</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17592,11 +17592,11 @@
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>19668.347213994242</v>
+        <v>18593.342551762064</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17614,11 +17614,11 @@
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>19120.60845076634</v>
+        <v>17823.324462394587</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17636,11 +17636,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" si="0"/>
-        <v>0.70496054043967626</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" si="1"/>
-        <v>18588.12352404428</v>
+        <v>17085.195628888581</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -17658,11 +17658,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.66505711362233599</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>18070.467633642707</v>
+        <v>16377.635400919806</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -17680,11 +17680,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.62741237134182648</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>17567.227809527809</v>
+        <v>15699.377821107815</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -17702,11 +17702,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.59189846353002495</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>17078.002582362446</v>
+        <v>15049.209359981822</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -17724,11 +17724,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.55839477691511785</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>16602.401663226221</v>
+        <v>14425.966744749841</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -17746,11 +17746,11 @@
       </c>
       <c r="E26" s="124">
         <f t="shared" si="0"/>
-        <v>0.52678752539162055</v>
+        <v>0.45134318911764126</v>
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>16140.045632254889</v>
+        <v>13828.534877986413</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -17768,11 +17768,11 @@
       </c>
       <c r="E27" s="124">
         <f t="shared" si="0"/>
-        <v>0.4969693635770005</v>
+        <v>0.41985412941175931</v>
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>15690.565635950825</v>
+        <v>13255.844842515115</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -17790,11 +17790,11 @@
       </c>
       <c r="E28" s="124">
         <f t="shared" si="0"/>
-        <v>0.46883902224245327</v>
+        <v>0.39056198084814819</v>
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>15253.60309292296</v>
+        <v>12706.871988916077</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -17812,11 +17812,11 @@
       </c>
       <c r="E29" s="124">
         <f t="shared" si="0"/>
-        <v>0.44230096437967292</v>
+        <v>0.36331347055641694</v>
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>14828.80940782154</v>
+        <v>12180.634102236849</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -17834,11 +17834,11 @@
       </c>
       <c r="E30" s="124">
         <f t="shared" si="0"/>
-        <v>0.41726506073554037</v>
+        <v>0.33796601912224833</v>
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>14415.845693239391</v>
+        <v>11676.189644626407</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -17856,11 +17856,11 @@
       </c>
       <c r="E31" s="124">
         <f t="shared" si="0"/>
-        <v>0.39364628371277405</v>
+        <v>0.31438699453232405</v>
       </c>
       <c r="F31" s="125">
         <f t="shared" si="1"/>
-        <v>14014.382499357958</v>
+        <v>11192.636070748134</v>
       </c>
       <c r="H31" s="120"/>
     </row>
@@ -17878,11 +17878,11 @@
       </c>
       <c r="E32" s="124">
         <f t="shared" si="0"/>
-        <v>0.37136441859695657</v>
+        <v>0.29245301816960378</v>
       </c>
       <c r="F32" s="125">
         <f t="shared" si="1"/>
-        <v>13624.099551122257</v>
+        <v>10729.108212957646</v>
       </c>
       <c r="H32" s="120"/>
     </row>
@@ -17900,11 +17900,11 @@
       </c>
       <c r="E33" s="124">
         <f t="shared" si="0"/>
-        <v>0.35034379112920433</v>
+        <v>0.27204931922753844</v>
       </c>
       <c r="F33" s="125">
         <f t="shared" si="1"/>
-        <v>13244.685492735292</v>
+        <v>10284.776733356332</v>
       </c>
       <c r="H33" s="120"/>
     </row>
@@ -17922,11 +17922,11 @@
       </c>
       <c r="E34" s="124">
         <f t="shared" si="0"/>
-        <v>0.3305130104992493</v>
+        <v>0.25306913416515198</v>
       </c>
       <c r="F34" s="125">
         <f t="shared" si="1"/>
-        <v>12875.837639267887</v>
+        <v>9858.8466399509543</v>
       </c>
       <c r="H34" s="120"/>
     </row>
@@ -17944,11 +17944,11 @@
       </c>
       <c r="E35" s="124">
         <f t="shared" si="0"/>
-        <v>0.31180472688608429</v>
+        <v>0.23541314806060654</v>
       </c>
       <c r="F35" s="125">
         <f t="shared" si="1"/>
-        <v>12517.261735185932</v>
+        <v>9450.5558642645501</v>
       </c>
       <c r="H35" s="120"/>
     </row>
@@ -17966,11 +17966,11 @@
       </c>
       <c r="E36" s="124">
         <f t="shared" si="0"/>
-        <v>0.29415540272272095</v>
+        <v>0.21898897494009908</v>
       </c>
       <c r="F36" s="125">
         <f t="shared" si="1"/>
-        <v>12168.671719602291</v>
+        <v>9059.1738978535705</v>
       </c>
       <c r="H36" s="120"/>
     </row>
@@ -17988,11 +17988,11 @@
       </c>
       <c r="E37" s="124">
         <f t="shared" si="0"/>
-        <v>0.27750509690822728</v>
+        <v>0.20371067436288287</v>
       </c>
       <c r="F37" s="125">
         <f t="shared" si="1"/>
-        <v>11829.789498066211</v>
+        <v>8684.0004852918864</v>
       </c>
       <c r="H37" s="120"/>
     </row>
@@ -18010,11 +18010,11 @@
       </c>
       <c r="E38" s="124">
         <f t="shared" si="0"/>
-        <v>0.26179726123417668</v>
+        <v>0.18949830173291429</v>
       </c>
       <c r="F38" s="125">
         <f t="shared" si="1"/>
-        <v>11500.344720708059</v>
+        <v>8324.3643712830581</v>
       </c>
       <c r="H38" s="120"/>
     </row>
@@ -18032,11 +18032,11 @@
       </c>
       <c r="E39" s="124">
         <f t="shared" si="0"/>
-        <v>0.24697854833412897</v>
+        <v>0.17627748998410636</v>
       </c>
       <c r="F39" s="125">
         <f t="shared" si="1"/>
-        <v>11180.074566562458</v>
+        <v>7979.622099659251</v>
       </c>
       <c r="H39" s="120"/>
     </row>
@@ -18054,11 +18054,11 @@
       </c>
       <c r="E40" s="124">
         <f t="shared" si="0"/>
-        <v>0.23299863050389524</v>
+        <v>0.16397906045033148</v>
       </c>
       <c r="F40" s="125">
         <f t="shared" si="1"/>
-        <v>10868.723533897777</v>
+        <v>7649.1568621179877</v>
       </c>
       <c r="H40" s="120"/>
     </row>
@@ -18076,11 +18076,11 @@
       </c>
       <c r="E41" s="124">
         <f t="shared" si="0"/>
-        <v>0.21981002877725966</v>
+        <v>0.15253866088402931</v>
       </c>
       <c r="F41" s="125">
         <f t="shared" si="1"/>
-        <v>10566.043236384656</v>
+        <v>7332.3773946369247</v>
       </c>
       <c r="H41" s="120"/>
     </row>
@@ -18098,11 +18098,11 @@
       </c>
       <c r="E42" s="124">
         <f t="shared" si="0"/>
-        <v>0.20736795167666003</v>
+        <v>0.14189642872932959</v>
       </c>
       <c r="F42" s="125">
         <f t="shared" si="1"/>
-        <v>10271.792204940994</v>
+        <v>7028.7169195920787</v>
       </c>
       <c r="H42" s="120"/>
     </row>
@@ -18120,11 +18120,11 @@
       </c>
       <c r="E43" s="124">
         <f t="shared" si="0"/>
-        <v>0.1956301430911887</v>
+        <v>0.13199667788774846</v>
       </c>
       <c r="F43" s="125">
         <f t="shared" si="1"/>
-        <v>9985.7356950953017</v>
+        <v>6737.6321316868361</v>
       </c>
       <c r="H43" s="120"/>
     </row>
@@ -18142,11 +18142,11 @@
       </c>
       <c r="E44" s="124">
         <f t="shared" si="0"/>
-        <v>0.18455673876527234</v>
+        <v>0.1227876073374404</v>
       </c>
       <c r="F44" s="125">
         <f t="shared" si="1"/>
-        <v>9707.6454997147484</v>
+        <v>6458.6022258773091</v>
       </c>
       <c r="H44" s="120"/>
     </row>
@@ -18164,11 +18164,11 @@
       </c>
       <c r="E45" s="124">
         <f t="shared" si="0"/>
-        <v>0.17411013091063426</v>
+        <v>0.11422103008133992</v>
       </c>
       <c r="F45" s="125">
         <f t="shared" si="1"/>
-        <v>9437.2997669484812</v>
+        <v>6191.127965554856</v>
       </c>
       <c r="H45" s="120"/>
     </row>
@@ -18178,7 +18178,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>685056.05483192916</v>
+        <v>548044.84386554325</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18186,11 +18186,11 @@
       </c>
       <c r="E46" s="124">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.17411013091063426</v>
+        <v>0.11422103008133992</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>119275.19938790983</v>
+        <v>62598.246597089455</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>558542.27767656068</v>
+        <v>429001.12593679567</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18222,7 +18222,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>558542.27767656068</v>
+        <v>429001.12593679567</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18252,19 +18252,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>395557.34013975487</v>
+        <v>314896.53510348545</v>
       </c>
       <c r="C51" s="123">
-        <v>407102.73193324311</v>
+        <v>324632.78979787923</v>
       </c>
       <c r="D51" s="123">
-        <v>412982.55895910517</v>
+        <v>329601.89323091769</v>
       </c>
       <c r="E51" s="123">
-        <v>418935.90174799564</v>
+        <v>334640.2783818054</v>
       </c>
       <c r="F51" s="123">
-        <v>431069.5667946937</v>
+        <v>344930.92431561451</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18273,19 +18273,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>411893.12148566649</v>
+        <v>324807.75509980234</v>
       </c>
       <c r="C52" s="123">
-        <v>434122.28128641954</v>
+        <v>343974.81870769861</v>
       </c>
       <c r="D52" s="123">
-        <v>445994.94588780403</v>
+        <v>354237.56674521696</v>
       </c>
       <c r="E52" s="123">
-        <v>458412.97738689464</v>
+        <v>364988.60169996839</v>
       </c>
       <c r="F52" s="123">
-        <v>485015.1374620148</v>
+        <v>388070.83654506237</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18294,19 +18294,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>419979.67410095019</v>
+        <v>327930.88236902282</v>
       </c>
       <c r="C53" s="123">
-        <v>456414.31205559522</v>
+        <v>358849.94171122112</v>
       </c>
       <c r="D53" s="123">
-        <v>476843.43715630146</v>
+        <v>376195.91009255394</v>
       </c>
       <c r="E53" s="123">
-        <v>498938.63661218865</v>
+        <v>394960.51534962025</v>
       </c>
       <c r="F53" s="123">
-        <v>548786.53106863168</v>
+        <v>437299.16636822606</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18315,19 +18315,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>422622.87185119989</v>
+        <v>327198.81239387486</v>
       </c>
       <c r="C54" s="123">
-        <v>474805.98207637807</v>
+        <v>370289.75939537305</v>
       </c>
       <c r="D54" s="123">
-        <v>505423.61220162653</v>
+        <v>395515.41064299399</v>
       </c>
       <c r="E54" s="123">
-        <v>539606.66257942491</v>
+        <v>423631.32085956045</v>
       </c>
       <c r="F54" s="123">
-        <v>620664.55681896757</v>
+        <v>490120.79863583227</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18336,19 +18336,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>421793.28497020365</v>
+        <v>324452.84082424536</v>
       </c>
       <c r="C55" s="123">
-        <v>489979.72419327294</v>
+        <v>379087.63142746594</v>
       </c>
       <c r="D55" s="123">
-        <v>531713.9127819913</v>
+        <v>412337.2819840071</v>
       </c>
       <c r="E55" s="123">
-        <v>579735.05517070927</v>
+        <v>450444.17586624995</v>
       </c>
       <c r="F55" s="123">
-        <v>699230.82487934455</v>
+        <v>544690.73594877089</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18357,19 +18357,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>418859.3668527056</v>
+        <v>320820.46690892312</v>
       </c>
       <c r="C56" s="123">
-        <v>502498.56829877582</v>
+        <v>385853.69662449375</v>
       </c>
       <c r="D56" s="123">
-        <v>555752.50737602054</v>
+        <v>426860.25447336398</v>
       </c>
       <c r="E56" s="123">
-        <v>618820.83568369201</v>
+        <v>475101.60442852258</v>
       </c>
       <c r="F56" s="123">
-        <v>783315.11625751655</v>
+        <v>599658.94538582163</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18419,23 +18419,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>17.666666666666668</v>
+        <v>14.133333333333335</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>17.666666666666668</v>
+        <v>14.133333333333335</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>17.666666666666668</v>
+        <v>14.133333333333335</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>17.666666666666668</v>
+        <v>14.133333333333335</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>17.666666666666668</v>
+        <v>14.133333333333335</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18446,23 +18446,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>19.040695744657388</v>
+        <v>15.157977131289964</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>19.596449032701553</v>
+        <v>15.626645120772716</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>19.879482580735569</v>
+        <v>15.865839738065848</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>20.166054910974374</v>
+        <v>16.108369325984903</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>20.750125539875192</v>
+        <v>16.603723699063725</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18473,23 +18473,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>19.82704101194242</v>
+        <v>15.635067315842118</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>20.897072143904136</v>
+        <v>16.557700242708059</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>21.468579157965497</v>
+        <v>17.051711712239698</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>22.066338156542585</v>
+        <v>17.569227543045091</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>23.346869661689411</v>
+        <v>18.680322613703829</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18500,23 +18500,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>20.216298326485944</v>
+        <v>15.785403335606178</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>21.970129656264923</v>
+        <v>17.273734714914681</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>22.953513646142746</v>
+        <v>18.108706722332656</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>24.017096412950778</v>
+        <v>19.011966763827939</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>26.416593263449329</v>
+        <v>21.049995869796941</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18527,23 +18527,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>20.343532279817936</v>
+        <v>15.750164142078216</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>22.855437948049211</v>
+        <v>17.824406048232195</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>24.329259618078993</v>
+        <v>19.038677410753461</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>25.974707687979542</v>
+        <v>20.392075357631661</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>29.876540735427092</v>
+        <v>23.592637673355231</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18554,23 +18554,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>20.303598976117318</v>
+        <v>15.617983029821971</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>23.585846861340038</v>
+        <v>18.247903699683501</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>25.59477933820213</v>
+        <v>19.848421287448648</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>27.906342969435457</v>
+        <v>21.682748952634626</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>33.658435935253991</v>
+        <v>26.219436541032881</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18580,23 +18580,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>20.162370798692315</v>
+        <v>15.443133723453277</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>24.188458613162062</v>
+        <v>18.573597539063663</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>26.751910098643489</v>
+        <v>20.547504511084881</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>29.787790686793507</v>
+        <v>22.869668135916577</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>37.705948764800347</v>
+        <v>28.86540678430962</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18631,7 +18631,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>37.705948764800347</v>
+        <v>28.86540678430962</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18653,7 +18653,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>29.787790686793507</v>
+        <v>22.869668135916577</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18676,7 +18676,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>26.751910098643489</v>
+        <v>20.547504511084881</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18699,7 +18699,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>24.188458613162062</v>
+        <v>18.573597539063663</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>20.162370798692315</v>
+        <v>15.443133723453277</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-25.14</v>
+        <v>-24.94</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>27.94815119642859</v>
+        <v>21.707898129891664</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18886,11 +18886,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="368" t="str">
+      <c r="E7" s="371" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 兴业银行(601166.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="368"/>
+      <c r="F7" s="371"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18911,8 +18911,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="368"/>
-      <c r="F8" s="368"/>
+      <c r="E8" s="371"/>
+      <c r="F8" s="371"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18933,8 +18933,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="368"/>
-      <c r="F9" s="368"/>
+      <c r="E9" s="371"/>
+      <c r="F9" s="371"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18944,8 +18944,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="368"/>
-      <c r="F10" s="368"/>
+      <c r="E10" s="371"/>
+      <c r="F10" s="371"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18958,8 +18958,8 @@
       <c r="B11" s="159" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
+      <c r="E11" s="371"/>
+      <c r="F11" s="371"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18977,8 +18977,8 @@
         <v>-5.5054441259114184E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="368"/>
-      <c r="F12" s="368"/>
+      <c r="E12" s="371"/>
+      <c r="F12" s="371"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18995,8 +18995,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.3520092995664894</v>
       </c>
-      <c r="E13" s="368"/>
-      <c r="F13" s="368"/>
+      <c r="E13" s="371"/>
+      <c r="F13" s="371"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19013,8 +19013,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-2.7745066708446342E-2</v>
       </c>
-      <c r="E14" s="368"/>
-      <c r="F14" s="368"/>
+      <c r="E14" s="371"/>
+      <c r="F14" s="371"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -19040,21 +19040,21 @@
       <c r="C18" s="150">
         <v>30</v>
       </c>
-      <c r="E18" s="368" t="s">
+      <c r="E18" s="371" t="s">
         <v>327</v>
       </c>
-      <c r="F18" s="369"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="369"/>
-      <c r="F19" s="369"/>
+      <c r="E19" s="372"/>
+      <c r="F19" s="372"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>302</v>
       </c>
-      <c r="E20" s="369"/>
-      <c r="F20" s="369"/>
+      <c r="E20" s="372"/>
+      <c r="F20" s="372"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -19062,14 +19062,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>25.14</v>
+        <v>24.94</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="369"/>
-      <c r="F21" s="369"/>
+      <c r="E21" s="372"/>
+      <c r="F21" s="372"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -19077,14 +19077,14 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>17.666666666666668</v>
+        <v>14.133333333333335</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="369"/>
-      <c r="F22" s="369"/>
+      <c r="E22" s="372"/>
+      <c r="F22" s="372"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -19104,8 +19104,8 @@
         <v>30</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="367"/>
-      <c r="F25" s="367"/>
+      <c r="E25" s="370"/>
+      <c r="F25" s="370"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -19115,8 +19115,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="367"/>
-      <c r="F26" s="367"/>
+      <c r="E26" s="370"/>
+      <c r="F26" s="370"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -19124,14 +19124,14 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>26.751910098643489</v>
+        <v>20.547504511084881</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="367"/>
-      <c r="F27" s="367"/>
+      <c r="E27" s="370"/>
+      <c r="F27" s="370"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -19141,8 +19141,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="367"/>
-      <c r="F28" s="367"/>
+      <c r="E28" s="370"/>
+      <c r="F28" s="370"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -19162,8 +19162,8 @@
         <v>30</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="367"/>
-      <c r="F31" s="367"/>
+      <c r="E31" s="370"/>
+      <c r="F31" s="370"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -19173,8 +19173,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="367"/>
-      <c r="F32" s="367"/>
+      <c r="E32" s="370"/>
+      <c r="F32" s="370"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -19182,14 +19182,14 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>24.188458613162062</v>
+        <v>18.573597539063663</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="367"/>
-      <c r="F33" s="367"/>
+      <c r="E33" s="370"/>
+      <c r="F33" s="370"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -19199,8 +19199,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="367"/>
-      <c r="F34" s="367"/>
+      <c r="E34" s="370"/>
+      <c r="F34" s="370"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -19220,8 +19220,8 @@
         <v>30</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="367"/>
-      <c r="F37" s="367"/>
+      <c r="E37" s="370"/>
+      <c r="F37" s="370"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -19231,8 +19231,8 @@
         <v>0.04</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="367"/>
-      <c r="F38" s="367"/>
+      <c r="E38" s="370"/>
+      <c r="F38" s="370"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -19240,14 +19240,14 @@
       </c>
   